--- a/docs/crane-statics-validation-22689.xlsx
+++ b/docs/crane-statics-validation-22689.xlsx
@@ -7002,52 +7002,52 @@
     </row>
   </sheetData>
   <dataValidations count="16">
-    <dataValidation sqref="B33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B33" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not an allowed value" error="Pick one of: +X, -X, +Y, -Y" type="list" errorStyle="stop">
       <formula1>"+X,-X,+Y,-Y"</formula1>
     </dataValidation>
-    <dataValidation sqref="A46:A85" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A46:A85" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not an allowed value" error="Pick one of: 1, 0" type="list" errorStyle="stop">
       <formula1>"1,0"</formula1>
     </dataValidation>
-    <dataValidation sqref="C46:C85" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C46:C85" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not an allowed value" error="Pick one of: boom, rear_leg, front_leg, platform" type="list" errorStyle="stop">
       <formula1>"boom,rear_leg,front_leg,platform"</formula1>
     </dataValidation>
-    <dataValidation sqref="D46:D85" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D46:D85" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not an allowed value" error="Pick one of: boom_local, global" type="list" errorStyle="stop">
       <formula1>"boom_local,global"</formula1>
     </dataValidation>
-    <dataValidation sqref="A92:A131" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A92:A131" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not an allowed value" error="Pick one of: 1, 0" type="list" errorStyle="stop">
       <formula1>"1,0"</formula1>
     </dataValidation>
-    <dataValidation sqref="C92:C131" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C92:C131" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not an allowed value" error="Pick one of: boom, rear_leg, front_leg, platform" type="list" errorStyle="stop">
       <formula1>"boom,rear_leg,front_leg,platform"</formula1>
     </dataValidation>
-    <dataValidation sqref="D92:D131" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D92:D131" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not an allowed value" error="Pick one of: boom_local, global" type="list" errorStyle="stop">
       <formula1>"boom_local,global"</formula1>
     </dataValidation>
-    <dataValidation sqref="A138:A217" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A138:A217" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not an allowed value" error="Pick one of: 1, 0" type="list" errorStyle="stop">
       <formula1>"1,0"</formula1>
     </dataValidation>
-    <dataValidation sqref="C138:C217" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C138:C217" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not an allowed value" error="Pick one of: boom, rear_leg, front_leg, platform" type="list" errorStyle="stop">
       <formula1>"boom,rear_leg,front_leg,platform"</formula1>
     </dataValidation>
-    <dataValidation sqref="D138:D217" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D138:D217" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not an allowed value" error="Pick one of: boom_local, global, hanging" type="list" errorStyle="stop">
       <formula1>"boom_local,global,hanging"</formula1>
     </dataValidation>
-    <dataValidation sqref="K138:K217" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K138:K217" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not an allowed value" error="Pick one of: 1, 0" type="list" errorStyle="stop">
       <formula1>"1,0"</formula1>
     </dataValidation>
-    <dataValidation sqref="A224:A283" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A224:A283" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not an allowed value" error="Pick one of: 1, 0" type="list" errorStyle="stop">
       <formula1>"1,0"</formula1>
     </dataValidation>
-    <dataValidation sqref="A290:A297" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A290:A297" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not an allowed value" error="Pick one of: 1, 0" type="list" errorStyle="stop">
       <formula1>"1,0"</formula1>
     </dataValidation>
-    <dataValidation sqref="C290:C297" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C290:C297" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not an allowed value" error="Pick one of: fixed, solve" type="list" errorStyle="stop">
       <formula1>"fixed,solve"</formula1>
     </dataValidation>
-    <dataValidation sqref="A304:A311" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A304:A311" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not an allowed value" error="Pick one of: 1, 0" type="list" errorStyle="stop">
       <formula1>"1,0"</formula1>
     </dataValidation>
-    <dataValidation sqref="O304:O311" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O304:O311" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not an allowed value" error="Pick one of: 1, 0" type="list" errorStyle="stop">
       <formula1>"1,0"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7289,7 +7289,7 @@
         </is>
       </c>
       <c r="B20" s="3">
-        <f>IFERROR(INDEX(Inputs!$D$304:$D$311,MATCH(Inputs!$B$26,Inputs!$B$304:$B$311,0))&amp;"","")</f>
+        <f>IFERROR(INDEX(Inputs!$D$304:$D$311,MATCH(Inputs!$B$26&amp;"",Loads!$B$139:$B$146,0))&amp;"","")</f>
         <v/>
       </c>
       <c r="D20" s="7" t="inlineStr">
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="B23" s="3">
-        <f>IF(Geometry!$B$22&lt;&gt;"",Geometry!$B$22,IFERROR(INDEX(Inputs!$E$304:$E$311,MATCH(Inputs!$B$26,Inputs!$B$304:$B$311,0))&amp;"",""))</f>
+        <f>IF(Geometry!$B$22&lt;&gt;"",Geometry!$B$22,IFERROR(INDEX(Inputs!$E$304:$E$311,MATCH(Inputs!$B$26&amp;"",Loads!$B$139:$B$146,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="D23" s="7" t="inlineStr">
@@ -12493,7 +12493,7 @@
         </is>
       </c>
       <c r="B28" s="3">
-        <f>IFERROR(INDEX(Loads!$C$139:$C$146,MATCH(Inputs!$B$26,Loads!$B$139:$B$146,0))&amp;"","")</f>
+        <f>IFERROR(INDEX(Loads!$C$139:$C$146,MATCH(Inputs!$B$26&amp;"",Loads!$B$139:$B$146,0))&amp;"","")</f>
         <v/>
       </c>
       <c r="D28" s="7" t="inlineStr">
@@ -17058,7 +17058,7 @@
         <v/>
       </c>
       <c r="D139" s="3">
-        <f>IF(AND(Loads!$A$139=1,Loads!$B$139&lt;&gt;"",Loads!$B$139=Inputs!$B$26),1,0)</f>
+        <f>IF(AND(Loads!$A$139=1,Loads!$B$139&lt;&gt;"",Loads!$B$139=Inputs!$B$26&amp;""),1,0)</f>
         <v/>
       </c>
       <c r="E139" s="3">
@@ -17108,7 +17108,7 @@
         <v/>
       </c>
       <c r="D140" s="3">
-        <f>IF(AND(Loads!$A$140=1,Loads!$B$140&lt;&gt;"",Loads!$B$140=Inputs!$B$26),1,0)</f>
+        <f>IF(AND(Loads!$A$140=1,Loads!$B$140&lt;&gt;"",Loads!$B$140=Inputs!$B$26&amp;""),1,0)</f>
         <v/>
       </c>
       <c r="E140" s="3">
@@ -17158,7 +17158,7 @@
         <v/>
       </c>
       <c r="D141" s="3">
-        <f>IF(AND(Loads!$A$141=1,Loads!$B$141&lt;&gt;"",Loads!$B$141=Inputs!$B$26),1,0)</f>
+        <f>IF(AND(Loads!$A$141=1,Loads!$B$141&lt;&gt;"",Loads!$B$141=Inputs!$B$26&amp;""),1,0)</f>
         <v/>
       </c>
       <c r="E141" s="3">
@@ -17208,7 +17208,7 @@
         <v/>
       </c>
       <c r="D142" s="3">
-        <f>IF(AND(Loads!$A$142=1,Loads!$B$142&lt;&gt;"",Loads!$B$142=Inputs!$B$26),1,0)</f>
+        <f>IF(AND(Loads!$A$142=1,Loads!$B$142&lt;&gt;"",Loads!$B$142=Inputs!$B$26&amp;""),1,0)</f>
         <v/>
       </c>
       <c r="E142" s="3">
@@ -17258,7 +17258,7 @@
         <v/>
       </c>
       <c r="D143" s="3">
-        <f>IF(AND(Loads!$A$143=1,Loads!$B$143&lt;&gt;"",Loads!$B$143=Inputs!$B$26),1,0)</f>
+        <f>IF(AND(Loads!$A$143=1,Loads!$B$143&lt;&gt;"",Loads!$B$143=Inputs!$B$26&amp;""),1,0)</f>
         <v/>
       </c>
       <c r="E143" s="3">
@@ -17308,7 +17308,7 @@
         <v/>
       </c>
       <c r="D144" s="3">
-        <f>IF(AND(Loads!$A$144=1,Loads!$B$144&lt;&gt;"",Loads!$B$144=Inputs!$B$26),1,0)</f>
+        <f>IF(AND(Loads!$A$144=1,Loads!$B$144&lt;&gt;"",Loads!$B$144=Inputs!$B$26&amp;""),1,0)</f>
         <v/>
       </c>
       <c r="E144" s="3">
@@ -17358,7 +17358,7 @@
         <v/>
       </c>
       <c r="D145" s="3">
-        <f>IF(AND(Loads!$A$145=1,Loads!$B$145&lt;&gt;"",Loads!$B$145=Inputs!$B$26),1,0)</f>
+        <f>IF(AND(Loads!$A$145=1,Loads!$B$145&lt;&gt;"",Loads!$B$145=Inputs!$B$26&amp;""),1,0)</f>
         <v/>
       </c>
       <c r="E145" s="3">
@@ -17408,7 +17408,7 @@
         <v/>
       </c>
       <c r="D146" s="3">
-        <f>IF(AND(Loads!$A$146=1,Loads!$B$146&lt;&gt;"",Loads!$B$146=Inputs!$B$26),1,0)</f>
+        <f>IF(AND(Loads!$A$146=1,Loads!$B$146&lt;&gt;"",Loads!$B$146=Inputs!$B$26&amp;""),1,0)</f>
         <v/>
       </c>
       <c r="E146" s="3">
@@ -36865,7 +36865,7 @@
         </is>
       </c>
       <c r="B26" s="3">
-        <f>IF(Inputs!$B$26="",0,IFERROR(MATCH(Inputs!$B$26,Loads!$B$139:$B$146,0),0))</f>
+        <f>IF(Inputs!$B$26="",0,IFERROR(MATCH(Inputs!$B$26&amp;"",Loads!$B$139:$B$146,0),0))</f>
         <v/>
       </c>
       <c r="C26" t="inlineStr">
@@ -45570,7 +45570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -45593,7 +45593,7 @@
         </is>
       </c>
       <c r="C3" s="3">
-        <f>SUM(C6:C20)</f>
+        <f>SUM(C6:C22)</f>
         <v/>
       </c>
       <c r="D3" s="3">
@@ -45635,7 +45635,7 @@
         </is>
       </c>
       <c r="C6" s="3">
-        <f>SUM($D$25:$D$30)</f>
+        <f>SUM($D$27:$D$32)</f>
         <v/>
       </c>
       <c r="D6" s="3">
@@ -45646,16 +45646,16 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>duplicate_ids</t>
+          <t>mirror</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Active rows whose id is used by another active row of the same table</t>
+          <t>Inputs tables with rows inserted or deleted (never do that: use spare rows), or a calculation sheet whose rows no longer follow the Inputs rows</t>
         </is>
       </c>
       <c r="C7" s="3">
-        <f>SUMPRODUCT((Inputs!$A$46:$A$85=1)*(Inputs!$B$46:$B$85&lt;&gt;"")*(COUNTIFS(Inputs!$B$46:$B$85,Inputs!$B$46:$B$85,Inputs!$A$46:$A$85,1)&gt;1))+SUMPRODUCT((Inputs!$A$92:$A$131=1)*(Inputs!$B$92:$B$131&lt;&gt;"")*(COUNTIFS(Inputs!$B$92:$B$131,Inputs!$B$92:$B$131,Inputs!$A$92:$A$131,1)&gt;1))+SUMPRODUCT((Inputs!$A$138:$A$217=1)*(Inputs!$B$138:$B$217&lt;&gt;"")*(COUNTIFS(Inputs!$B$138:$B$217,Inputs!$B$138:$B$217,Inputs!$A$138:$A$217,1)&gt;1))+SUMPRODUCT((Inputs!$A$290:$A$297=1)*(Inputs!$B$290:$B$297&lt;&gt;"")*(COUNTIFS(Inputs!$B$290:$B$297,Inputs!$B$290:$B$297,Inputs!$A$290:$A$297,1)&gt;1))+SUMPRODUCT((Inputs!$A$304:$A$311=1)*(Inputs!$B$304:$B$311&lt;&gt;"")*(COUNTIFS(Inputs!$B$304:$B$311,Inputs!$B$304:$B$311,Inputs!$A$304:$A$311,1)&gt;1))</f>
+        <f>IFERROR(1*(ROWS(Inputs!$A$46:$A$85)&lt;&gt;40)+1*(SUM(Inputs!$A$46:$A$85)&lt;&gt;SUM(Loads!$A$33:$A$72)),1)+IFERROR(1*(ROWS(Inputs!$A$46:$A$85)&lt;&gt;40)+1*(SUM(Inputs!$A$46:$A$85)&lt;&gt;SUM(OutOfPlane!$A$39:$A$78)),1)+IFERROR(1*(ROWS(Inputs!$A$92:$A$131)&lt;&gt;40)+1*(SUM(Inputs!$A$92:$A$131)&lt;&gt;SUM(Loads!$A$79:$A$118)),1)+IFERROR(1*(ROWS(Inputs!$A$92:$A$131)&lt;&gt;40)+1*(SUM(Inputs!$A$92:$A$131)&lt;&gt;SUM(OutOfPlane!$A$171:$A$210)),1)+IFERROR(1*(ROWS(Inputs!$A$138:$A$217)&lt;&gt;80)+1*(SUM(Inputs!$A$138:$A$217)&lt;&gt;SUM(Geometry!$A$58:$A$137)),1)+IFERROR(1*(ROWS(Inputs!$A$138:$A$217)&lt;&gt;80)+1*(SUM(Inputs!$A$138:$A$217)&lt;&gt;SUM(Loads!$A$219:$A$298)),1)+IFERROR(1*(ROWS(Inputs!$A$138:$A$217)&lt;&gt;80)+1*(SUM(Inputs!$A$138:$A$217)&lt;&gt;SUM(OutOfPlane!$A$85:$A$164)),1)+IFERROR(1*(ROWS(Inputs!$A$224:$A$283)&lt;&gt;60)+1*(SUM(Inputs!$A$224:$A$283)&lt;&gt;SUM(Loads!$A$153:$A$212)),1)+IFERROR(1*(ROWS(Inputs!$A$290:$A$297)&lt;&gt;8)+1*(SUM(Inputs!$A$290:$A$297)&lt;&gt;SUM(Loads!$A$125:$A$132)),1)+IFERROR(1*(ROWS(Inputs!$A$304:$A$311)&lt;&gt;8)+1*(SUM(Inputs!$A$304:$A$311)&lt;&gt;SUM(Loads!$A$139:$A$146)),1)+IFERROR(1*(ROWS(Inputs!$A$304:$A$311)&lt;&gt;8)+1*(SUM(Inputs!$A$304:$A$311)&lt;&gt;SUM(Results!$A$19:$A$26)),1)</f>
         <v/>
       </c>
       <c r="D7" s="3">
@@ -45666,16 +45666,16 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>blank_ids</t>
+          <t>duplicate_ids</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Active rows with a blank id (or blank rope id on a segment)</t>
+          <t>Active node, rope or hoist rows whose id is used by another active row of the same table (mass-point and wind-area ids are labels only)</t>
         </is>
       </c>
       <c r="C8" s="3">
-        <f>SUMPRODUCT((Inputs!$A$46:$A$85=1)*(Inputs!$B$46:$B$85=""))+SUMPRODUCT((Inputs!$A$92:$A$131=1)*(Inputs!$B$92:$B$131=""))+SUMPRODUCT((Inputs!$A$138:$A$217=1)*(Inputs!$B$138:$B$217=""))+SUMPRODUCT((Inputs!$A$290:$A$297=1)*(Inputs!$B$290:$B$297=""))+SUMPRODUCT((Inputs!$A$304:$A$311=1)*(Inputs!$B$304:$B$311=""))+SUMPRODUCT((Inputs!$A$224:$A$283=1)*(Inputs!$B$224:$B$283=""))</f>
+        <f>SUMPRODUCT((Inputs!$A$138:$A$217=1)*(Inputs!$B$138:$B$217&lt;&gt;"")*(COUNTIFS(Inputs!$B$138:$B$217,Inputs!$B$138:$B$217,Inputs!$A$138:$A$217,1)&gt;1))+SUMPRODUCT((Inputs!$A$290:$A$297=1)*(Inputs!$B$290:$B$297&lt;&gt;"")*(COUNTIFS(Inputs!$B$290:$B$297,Inputs!$B$290:$B$297,Inputs!$A$290:$A$297,1)&gt;1))+SUMPRODUCT((Inputs!$A$304:$A$311=1)*(Inputs!$B$304:$B$311&lt;&gt;"")*(COUNTIFS(Inputs!$B$304:$B$311,Inputs!$B$304:$B$311,Inputs!$A$304:$A$311,1)&gt;1))</f>
         <v/>
       </c>
       <c r="D8" s="3">
@@ -45686,16 +45686,16 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>node_references</t>
+          <t>blank_ids</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>References to a missing or inactive node (segment ends, hoist hook/support nodes, hanging nodes' parent)</t>
+          <t>Active rows with a blank id (or blank rope id on a segment)</t>
         </is>
       </c>
       <c r="C9" s="3">
-        <f>SUMPRODUCT((Inputs!$A$224:$A$283=1)*(COUNTIFS(Inputs!$B$138:$B$217,Inputs!$C$224:$C$283,Inputs!$A$138:$A$217,1)=0))+SUMPRODUCT((Inputs!$A$224:$A$283=1)*(COUNTIFS(Inputs!$B$138:$B$217,Inputs!$D$224:$D$283,Inputs!$A$138:$A$217,1)=0))+SUMPRODUCT((Inputs!$A$304:$A$311=1)*(COUNTIFS(Inputs!$B$138:$B$217,Inputs!$D$304:$D$311,Inputs!$A$138:$A$217,1)=0))+SUMPRODUCT((Inputs!$A$304:$A$311=1)*(Inputs!$E$304:$E$311&lt;&gt;"")*(COUNTIFS(Inputs!$B$138:$B$217,Inputs!$E$304:$E$311,Inputs!$A$138:$A$217,1)=0))+SUMPRODUCT((Inputs!$A$138:$A$217=1)*(Inputs!$D$138:$D$217="hanging")*(COUNTIFS(Inputs!$B$138:$B$217,Inputs!$I$138:$I$217,Inputs!$A$138:$A$217,1)=0))</f>
+        <f>SUMPRODUCT((Inputs!$A$46:$A$85=1)*(Inputs!$B$46:$B$85=""))+SUMPRODUCT((Inputs!$A$92:$A$131=1)*(Inputs!$B$92:$B$131=""))+SUMPRODUCT((Inputs!$A$138:$A$217=1)*(Inputs!$B$138:$B$217=""))+SUMPRODUCT((Inputs!$A$290:$A$297=1)*(Inputs!$B$290:$B$297=""))+SUMPRODUCT((Inputs!$A$304:$A$311=1)*(Inputs!$B$304:$B$311=""))+SUMPRODUCT((Inputs!$A$224:$A$283=1)*(Inputs!$B$224:$B$283=""))</f>
         <v/>
       </c>
       <c r="D9" s="3">
@@ -45706,16 +45706,16 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>rope_references</t>
+          <t>invalid_values</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Segments or hoists referencing a missing or inactive rope</t>
+          <t>Cells outside their allowed values: Active not blank/0/1; on active rows a 1/0 column not 0/1, or a body, frame or role not one of its list choices (a typo drops the row)</t>
         </is>
       </c>
       <c r="C10" s="3">
-        <f>SUMPRODUCT((Inputs!$A$224:$A$283=1)*(COUNTIFS(Inputs!$B$290:$B$297,Inputs!$B$224:$B$283,Inputs!$A$290:$A$297,1)=0))+SUMPRODUCT((Inputs!$A$304:$A$311=1)*(COUNTIFS(Inputs!$B$290:$B$297,Inputs!$C$304:$C$311,Inputs!$A$290:$A$297,1)=0))</f>
+        <f>SUMPRODUCT(1*(Inputs!$A$46:$A$85&lt;&gt;"")*(Inputs!$A$46:$A$85&lt;&gt;0)*(Inputs!$A$46:$A$85&lt;&gt;1))+SUMPRODUCT(1*(Inputs!$A$46:$A$85=1)*(Inputs!$C$46:$C$85&lt;&gt;"boom")*(Inputs!$C$46:$C$85&lt;&gt;"rear_leg")*(Inputs!$C$46:$C$85&lt;&gt;"front_leg")*(Inputs!$C$46:$C$85&lt;&gt;"platform"))+SUMPRODUCT(1*(Inputs!$A$46:$A$85=1)*(Inputs!$D$46:$D$85&lt;&gt;"boom_local")*(Inputs!$D$46:$D$85&lt;&gt;"global"))+SUMPRODUCT(1*(Inputs!$A$92:$A$131&lt;&gt;"")*(Inputs!$A$92:$A$131&lt;&gt;0)*(Inputs!$A$92:$A$131&lt;&gt;1))+SUMPRODUCT(1*(Inputs!$A$92:$A$131=1)*(Inputs!$C$92:$C$131&lt;&gt;"boom")*(Inputs!$C$92:$C$131&lt;&gt;"rear_leg")*(Inputs!$C$92:$C$131&lt;&gt;"front_leg")*(Inputs!$C$92:$C$131&lt;&gt;"platform"))+SUMPRODUCT(1*(Inputs!$A$92:$A$131=1)*(Inputs!$D$92:$D$131&lt;&gt;"boom_local")*(Inputs!$D$92:$D$131&lt;&gt;"global"))+SUMPRODUCT(1*(Inputs!$A$138:$A$217&lt;&gt;"")*(Inputs!$A$138:$A$217&lt;&gt;0)*(Inputs!$A$138:$A$217&lt;&gt;1))+SUMPRODUCT(1*(Inputs!$A$138:$A$217=1)*(Inputs!$C$138:$C$217&lt;&gt;"boom")*(Inputs!$C$138:$C$217&lt;&gt;"rear_leg")*(Inputs!$C$138:$C$217&lt;&gt;"front_leg")*(Inputs!$C$138:$C$217&lt;&gt;"platform"))+SUMPRODUCT(1*(Inputs!$A$138:$A$217=1)*(Inputs!$D$138:$D$217&lt;&gt;"boom_local")*(Inputs!$D$138:$D$217&lt;&gt;"global")*(Inputs!$D$138:$D$217&lt;&gt;"hanging"))+SUMPRODUCT(1*(Inputs!$A$138:$A$217=1)*(Inputs!$K$138:$K$217&lt;&gt;"")*(Inputs!$K$138:$K$217&lt;&gt;0)*(Inputs!$K$138:$K$217&lt;&gt;1))+SUMPRODUCT(1*(Inputs!$A$224:$A$283&lt;&gt;"")*(Inputs!$A$224:$A$283&lt;&gt;0)*(Inputs!$A$224:$A$283&lt;&gt;1))+SUMPRODUCT(1*(Inputs!$A$290:$A$297&lt;&gt;"")*(Inputs!$A$290:$A$297&lt;&gt;0)*(Inputs!$A$290:$A$297&lt;&gt;1))+SUMPRODUCT(1*(Inputs!$A$290:$A$297=1)*(Inputs!$C$290:$C$297&lt;&gt;"fixed")*(Inputs!$C$290:$C$297&lt;&gt;"solve"))+SUMPRODUCT(1*(Inputs!$A$304:$A$311&lt;&gt;"")*(Inputs!$A$304:$A$311&lt;&gt;0)*(Inputs!$A$304:$A$311&lt;&gt;1))+SUMPRODUCT(1*(Inputs!$A$304:$A$311=1)*(Inputs!$O$304:$O$311&lt;&gt;"")*(Inputs!$O$304:$O$311&lt;&gt;0)*(Inputs!$O$304:$O$311&lt;&gt;1))</f>
         <v/>
       </c>
       <c r="D10" s="3">
@@ -45726,16 +45726,16 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>hoist_without_segments</t>
+          <t>node_references</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Active hoists whose rope has no active segment</t>
+          <t>References to a missing or inactive node (segment ends, hoist hook/support nodes, hanging nodes' parent)</t>
         </is>
       </c>
       <c r="C11" s="3">
-        <f>SUMPRODUCT((Inputs!$A$304:$A$311=1)*(COUNTIFS(Inputs!$B$224:$B$283,Inputs!$C$304:$C$311,Inputs!$A$224:$A$283,1)=0))</f>
+        <f>SUMPRODUCT((Inputs!$A$224:$A$283=1)*(COUNTIFS(Inputs!$B$138:$B$217,Inputs!$C$224:$C$283,Inputs!$A$138:$A$217,1)=0))+SUMPRODUCT((Inputs!$A$224:$A$283=1)*(COUNTIFS(Inputs!$B$138:$B$217,Inputs!$D$224:$D$283,Inputs!$A$138:$A$217,1)=0))+SUMPRODUCT((Inputs!$A$304:$A$311=1)*(COUNTIFS(Inputs!$B$138:$B$217,Inputs!$D$304:$D$311,Inputs!$A$138:$A$217,1)=0))+SUMPRODUCT((Inputs!$A$304:$A$311=1)*(Inputs!$E$304:$E$311&lt;&gt;"")*(COUNTIFS(Inputs!$B$138:$B$217,Inputs!$E$304:$E$311,Inputs!$A$138:$A$217,1)=0))+SUMPRODUCT((Inputs!$A$138:$A$217=1)*(Inputs!$D$138:$D$217="hanging")*(COUNTIFS(Inputs!$B$138:$B$217,Inputs!$I$138:$I$217,Inputs!$A$138:$A$217,1)=0))</f>
         <v/>
       </c>
       <c r="D11" s="3">
@@ -45746,16 +45746,16 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>multiple_solve_ropes</t>
+          <t>rope_references</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Active solve ropes beyond the first (exactly one is allowed)</t>
+          <t>Segments or hoists referencing a missing or inactive rope</t>
         </is>
       </c>
       <c r="C12" s="3">
-        <f>MAX(0,COUNTIFS(Inputs!$A$290:$A$297,1,Inputs!$C$290:$C$297,"solve")-1)</f>
+        <f>SUMPRODUCT((Inputs!$A$224:$A$283=1)*(COUNTIFS(Inputs!$B$290:$B$297,Inputs!$B$224:$B$283,Inputs!$A$290:$A$297,1)=0))+SUMPRODUCT((Inputs!$A$304:$A$311=1)*(COUNTIFS(Inputs!$B$290:$B$297,Inputs!$C$304:$C$311,Inputs!$A$290:$A$297,1)=0))</f>
         <v/>
       </c>
       <c r="D12" s="3">
@@ -45766,16 +45766,16 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>no_solve_rope</t>
+          <t>hoist_without_segments</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1 if no active rope has role solve (the app shows no results then)</t>
+          <t>Active hoists whose rope has no active segment</t>
         </is>
       </c>
       <c r="C13" s="3">
-        <f>IF(COUNTIFS(Inputs!$A$290:$A$297,1,Inputs!$C$290:$C$297,"solve")=0,1,0)</f>
+        <f>SUMPRODUCT((Inputs!$A$304:$A$311=1)*(COUNTIFS(Inputs!$B$224:$B$283,Inputs!$C$304:$C$311,Inputs!$A$224:$A$283,1)=0))</f>
         <v/>
       </c>
       <c r="D13" s="3">
@@ -45786,16 +45786,16 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>scene_hoist</t>
+          <t>multiple_solve_ropes</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1 if the scene hoist is not an active hoist with a fixed rope</t>
+          <t>Active solve ropes beyond the first (exactly one is allowed)</t>
         </is>
       </c>
       <c r="C14" s="3">
-        <f>IF(COUNTIFS(Inputs!$B$304:$B$311,Inputs!$B$26,Inputs!$A$304:$A$311,1)=0,1,IF(COUNTIFS(Inputs!$B$290:$B$297,INDEX(Inputs!$C$304:$C$311,MATCH(Inputs!$B$26,Inputs!$B$304:$B$311,0)),Inputs!$A$290:$A$297,1,Inputs!$C$290:$C$297,"fixed")=0,1,0))</f>
+        <f>MAX(0,COUNTIFS(Inputs!$A$290:$A$297,1,Inputs!$C$290:$C$297,"solve")-1)</f>
         <v/>
       </c>
       <c r="D14" s="3">
@@ -45806,16 +45806,16 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>wind_direction</t>
+          <t>no_solve_rope</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1 if the scene wind direction is not +X, -X, +Y or -Y</t>
+          <t>1 if no active rope has role solve (the app shows no results then)</t>
         </is>
       </c>
       <c r="C15" s="3">
-        <f>IF(OR(Inputs!$B$33="+X",Inputs!$B$33="-X",Inputs!$B$33="+Y",Inputs!$B$33="-Y"),0,1)</f>
+        <f>IF(COUNTIFS(Inputs!$A$290:$A$297,1,Inputs!$C$290:$C$297,"solve")=0,1,0)</f>
         <v/>
       </c>
       <c r="D15" s="3">
@@ -45826,16 +45826,16 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>fixed_nodes_missing</t>
+          <t>scene_hoist</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fixed structure node ids with no active node row</t>
+          <t>1 if the scene hoist is not an active hoist with a fixed rope</t>
         </is>
       </c>
       <c r="C16" s="3">
-        <f>COUNTIF($B$34:$B$42,0)</f>
+        <f>IF(COUNTIFS(Inputs!$B$304:$B$311,Inputs!$B$26,Inputs!$A$304:$A$311,1)=0,1,IF(COUNTIFS(Inputs!$B$290:$B$297,IFERROR(INDEX(Inputs!$C$304:$C$311,MATCH(Inputs!$B$26&amp;"",Loads!$B$139:$B$146,0)),""),Inputs!$A$290:$A$297,1,Inputs!$C$290:$C$297,"fixed")=0,1,0))</f>
         <v/>
       </c>
       <c r="D16" s="3">
@@ -45846,16 +45846,16 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>hanging_chain</t>
+          <t>wind_direction</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hanging nodes whose parent is itself hanging (only one level is resolved)</t>
+          <t>1 if the scene wind direction is not +X, -X, +Y or -Y</t>
         </is>
       </c>
       <c r="C17" s="3">
-        <f>SUMPRODUCT((Inputs!$A$138:$A$217=1)*(Inputs!$D$138:$D$217="hanging")*(COUNTIFS(Inputs!$B$138:$B$217,Inputs!$I$138:$I$217,Inputs!$D$138:$D$217,"hanging",Inputs!$A$138:$A$217,1)&gt;0))</f>
+        <f>IF(OR(Inputs!$B$33="+X",Inputs!$B$33="-X",Inputs!$B$33="+Y",Inputs!$B$33="-Y"),0,1)</f>
         <v/>
       </c>
       <c r="D17" s="3">
@@ -45866,16 +45866,16 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>singular_matrix</t>
+          <t>fixed_nodes_missing</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Singular Statics systems (boom 3x3, leg frame 6x6); the boom one is singular without a solve rope</t>
+          <t>Fixed structure node ids with no active node row</t>
         </is>
       </c>
       <c r="C18" s="3">
-        <f>Statics!$B$41+Statics!$B$62</f>
+        <f>COUNTIF($B$36:$B$44,0)</f>
         <v/>
       </c>
       <c r="D18" s="3">
@@ -45886,16 +45886,16 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>zero_boom_width</t>
+          <t>hanging_chain</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1 if the boom width is not &gt; 0 (the app rejects it; the out-of-plane split divides by it, so Results shows a message)</t>
+          <t>Hanging nodes whose parent is itself hanging (only one level is resolved)</t>
         </is>
       </c>
       <c r="C19" s="3">
-        <f>IF(OutOfPlane!$B$21=1,0,1)</f>
+        <f>SUMPRODUCT((Inputs!$A$138:$A$217=1)*(Inputs!$D$138:$D$217="hanging")*(COUNTIFS(Inputs!$B$138:$B$217,Inputs!$I$138:$I$217,Inputs!$D$138:$D$217,"hanging",Inputs!$A$138:$A$217,1)&gt;0))</f>
         <v/>
       </c>
       <c r="D19" s="3">
@@ -45906,16 +45906,16 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>invalid_bearing_diameter</t>
+          <t>singular_matrix</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1 if the slewing bearing diameter is typed but not a number &gt; 0 (blank is allowed and hides the bearing line-load rows)</t>
+          <t>Singular Statics systems (boom 3x3, leg frame 6x6); the boom one is singular without a solve rope</t>
         </is>
       </c>
       <c r="C20" s="3">
-        <f>IF(Inputs!$B$13="",0,IF(ISNUMBER(Inputs!$B$13),IF(Inputs!$B$13&gt;0,0,1),1))</f>
+        <f>Statics!$B$41+Statics!$B$62</f>
         <v/>
       </c>
       <c r="D20" s="3">
@@ -45923,85 +45923,87 @@
         <v/>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>zero_boom_width</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1 if the boom width is not &gt; 0 (the app rejects it; the out-of-plane split divides by it, so Results shows a message)</t>
+        </is>
+      </c>
+      <c r="C21" s="3">
+        <f>IF(OutOfPlane!$B$21=1,0,1)</f>
+        <v/>
+      </c>
+      <c r="D21" s="3">
+        <f>IF(C21=0,"OK","CHECK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>invalid_bearing_diameter</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1 if the slewing bearing diameter is typed but not a number &gt; 0 (blank is allowed and hides the bearing line-load rows)</t>
+        </is>
+      </c>
+      <c r="C22" s="3">
+        <f>IF(Inputs!$B$13="",0,IF(ISNUMBER(Inputs!$B$13),IF(Inputs!$B$13&gt;0,0,1),1))</f>
+        <v/>
+      </c>
+      <c r="D22" s="3">
+        <f>IF(C22=0,"OK","CHECK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>Overflow per table</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>Table</t>
         </is>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B26" s="10" t="inlineStr">
         <is>
           <t>Not written</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C26" s="10" t="inlineStr">
         <is>
           <t>Typed in guard row</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
+      <c r="D26" s="10" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>mass_points</t>
-        </is>
-      </c>
-      <c r="B25" s="3">
-        <f>Inputs!$G$43</f>
-        <v/>
-      </c>
-      <c r="C25" s="3">
-        <f>COUNTA(Inputs!$A$86:$K$86)</f>
-        <v/>
-      </c>
-      <c r="D25" s="3">
-        <f>B25+C25</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>wind_areas</t>
-        </is>
-      </c>
-      <c r="B26" s="3">
-        <f>Inputs!$G$89</f>
-        <v/>
-      </c>
-      <c r="C26" s="3">
-        <f>COUNTA(Inputs!$A$132:$K$132)</f>
-        <v/>
-      </c>
-      <c r="D26" s="3">
-        <f>B26+C26</f>
-        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>nodes</t>
+          <t>mass_points</t>
         </is>
       </c>
       <c r="B27" s="3">
-        <f>Inputs!$G$135</f>
+        <f>Inputs!$G$43</f>
         <v/>
       </c>
       <c r="C27" s="3">
-        <f>COUNTA(Inputs!$A$218:$K$218)</f>
+        <f>COUNTA(Inputs!$A$86:$K$86)</f>
         <v/>
       </c>
       <c r="D27" s="3">
@@ -46012,15 +46014,15 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>segments</t>
+          <t>wind_areas</t>
         </is>
       </c>
       <c r="B28" s="3">
-        <f>Inputs!$G$221</f>
+        <f>Inputs!$G$89</f>
         <v/>
       </c>
       <c r="C28" s="3">
-        <f>COUNTA(Inputs!$A$284:$E$284)</f>
+        <f>COUNTA(Inputs!$A$132:$K$132)</f>
         <v/>
       </c>
       <c r="D28" s="3">
@@ -46031,15 +46033,15 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ropes</t>
+          <t>nodes</t>
         </is>
       </c>
       <c r="B29" s="3">
-        <f>Inputs!$G$287</f>
+        <f>Inputs!$G$135</f>
         <v/>
       </c>
       <c r="C29" s="3">
-        <f>COUNTA(Inputs!$A$298:$C$298)</f>
+        <f>COUNTA(Inputs!$A$218:$K$218)</f>
         <v/>
       </c>
       <c r="D29" s="3">
@@ -46050,15 +46052,15 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>hoists</t>
+          <t>segments</t>
         </is>
       </c>
       <c r="B30" s="3">
-        <f>Inputs!$G$301</f>
+        <f>Inputs!$G$221</f>
         <v/>
       </c>
       <c r="C30" s="3">
-        <f>COUNTA(Inputs!$A$312:$Q$312)</f>
+        <f>COUNTA(Inputs!$A$284:$E$284)</f>
         <v/>
       </c>
       <c r="D30" s="3">
@@ -46066,39 +46068,55 @@
         <v/>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ropes</t>
+        </is>
+      </c>
+      <c r="B31" s="3">
+        <f>Inputs!$G$287</f>
+        <v/>
+      </c>
+      <c r="C31" s="3">
+        <f>COUNTA(Inputs!$A$298:$C$298)</f>
+        <v/>
+      </c>
+      <c r="D31" s="3">
+        <f>B31+C31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>hoists</t>
+        </is>
+      </c>
+      <c r="B32" s="3">
+        <f>Inputs!$G$301</f>
+        <v/>
+      </c>
+      <c r="C32" s="3">
+        <f>COUNTA(Inputs!$A$312:$Q$312)</f>
+        <v/>
+      </c>
+      <c r="D32" s="3">
+        <f>B32+C32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>Fixed structure nodes (active rows with this id)</t>
         </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>boom_heel</t>
-        </is>
-      </c>
-      <c r="B34" s="3">
-        <f>COUNTIFS(Inputs!$B$138:$B$217,A34,Inputs!$A$138:$A$217,1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>platform_heel</t>
-        </is>
-      </c>
-      <c r="B35" s="3">
-        <f>COUNTIFS(Inputs!$B$138:$B$217,A35,Inputs!$A$138:$A$217,1)</f>
-        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>rear_top</t>
+          <t>boom_heel</t>
         </is>
       </c>
       <c r="B36" s="3">
@@ -46109,7 +46127,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>front_top</t>
+          <t>platform_heel</t>
         </is>
       </c>
       <c r="B37" s="3">
@@ -46120,7 +46138,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>rear_base</t>
+          <t>rear_top</t>
         </is>
       </c>
       <c r="B38" s="3">
@@ -46131,7 +46149,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>platform_rear</t>
+          <t>front_top</t>
         </is>
       </c>
       <c r="B39" s="3">
@@ -46142,7 +46160,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>front_base</t>
+          <t>rear_base</t>
         </is>
       </c>
       <c r="B40" s="3">
@@ -46153,7 +46171,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>platform_front</t>
+          <t>platform_rear</t>
         </is>
       </c>
       <c r="B41" s="3">
@@ -46164,7 +46182,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>platform_base</t>
+          <t>front_base</t>
         </is>
       </c>
       <c r="B42" s="3">
@@ -46172,8 +46190,30 @@
         <v/>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>platform_front</t>
+        </is>
+      </c>
+      <c r="B43" s="3">
+        <f>COUNTIFS(Inputs!$B$138:$B$217,A43,Inputs!$A$138:$A$217,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>platform_base</t>
+        </is>
+      </c>
+      <c r="B44" s="3">
+        <f>COUNTIFS(Inputs!$B$138:$B$217,A44,Inputs!$A$138:$A$217,1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="C6:C20">
+  <conditionalFormatting sqref="C6:C22">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>

--- a/docs/crane-statics-validation-22689.xlsx
+++ b/docs/crane-statics-validation-22689.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -563,7 +563,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>z: up. y: lateral, completing a right-handed x-y-z frame.</t>
+          <t>z: up. y: lateral, completing a right-handed x-y-z frame: +y points to port (left, looking along +x).</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Force = sign x 0.5 rho Cd A V^2 / 1000 (kN). X wind uses 'Area for X wind', Y wind uses 'Area for Y wind'. X wind: areas of body 'boom' are scaled by |sin theta|; Y wind: boom-local areas are (the in-plane solver and the out-of-plane pass test this differently; identical when boom areas are boom-local).</t>
+          <t>Force = sign x 0.5 rho Cd A V^2 / 1000 (kN). X wind uses 'Area for X wind', Y wind uses 'Area for Y wind'. X wind: areas of body 'boom' are scaled by |sin theta| (the boom's projection seen along x). Y wind: every area is used in full at any boom angle (the boom's side face does not turn with luffing).</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -806,136 +806,124 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Fx, Fz and My of every support (heel point, hinges, platform base) are support reactions opposing the applied loads: weight gives positive Fz; a +X vessel acceleration gives positive Fx.</t>
+          <t>Every reported reaction is the force (or moment) the support exerts on the crane, opposing the applied loads: weight gives positive Fz; a +X vessel acceleration gives positive Fx. This holds for Fx, Fz and My of every support (heel point, hinges, platform base) and for platform base Fy and Mx: a +Y wind gives negative Fy, and Mx = -(applied Mx about platform_heel).</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>scripts/excel_workbook/reference.py</t>
+          <t>scripts/excel_workbook/reference.py; calculation/engine.py</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Possible app sign bug, replicated: platform base Fy and Mx carry the sign of the applied loads, not of the reaction (a +Y wind gives positive Fy, and Mx = -z Fy).</t>
+          <t>Left/right: +Y is port, so heel_left is the +Y side. heel_left = 0.5 total - M / boom width, heel_right = 0.5 total + M / boom width (Fz uses Mx, Fx uses Mz), with M the applied-load moment about the heel: Mx = y Fz - z Fy, Mz = x_rel Fy - y Fx. A mass at +Y loads heel_left. The heel moments include every mass and wind area of the crane.</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>scripts/excel_workbook/reference.py</t>
+          <t>scripts/excel_workbook/reference.py; calculation/engine.py</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Possible app sign bug, replicated: heel_left behaves as the -Y side. heel_left = 0.5 total + M / boom width, heel_right = 0.5 total - M / boom width (Fz uses Mx, Fx uses Mz), with M the applied-load moment about the heel: Mx = y Fz - z Fy, Mz = x_rel Fy - y Fx. A mass at +Y loads heel_right. The heel moments include every mass and wind area of the crane.</t>
-        </is>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>scripts/excel_workbook/reference.py; calculation/engine.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
           <t>Pinned connections (heel, hinges) carry no moment.</t>
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>Out-of-plane pass</t>
+        </is>
+      </c>
+    </row>
     <row r="45">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>Out-of-plane pass</t>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Y loads are not part of the in-plane solve. Moments of the applied loads are taken about the support-group origins boom_heel (heel), front_base, rear_base and platform_heel (platform base): Mx = y Fz - (z - oz) Fy, Mz = (x - ox) Fy - y Fx. Rope self-weight and idle hook blocks sit at y = 0; wind and the side force at y = 0.</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>calculation/engine.py _out_of_plane_variants</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Y loads are not part of the in-plane solve. Moments of the applied loads are taken about the support-group origins boom_heel (heel), front_base, rear_base and platform_heel (platform base): Mx = y Fz - (z - oz) Fy, Mz = (x - ox) Fy - y Fx. Rope self-weight and idle hook blocks sit at y = 0; wind and the side force at y = 0.</t>
+          <t>The side force acts at the support node's kinematic position (before the tackle moves the hook).</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>calculation/engine.py _out_of_plane_variants</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>The side force acts at the support node's kinematic position (before the tackle moves the hook).</t>
-        </is>
-      </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
           <t>calculation/engine.py _out_of_plane_geometry</t>
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>Statics</t>
+        </is>
+      </c>
+    </row>
     <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>Statics</t>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unknowns are the forces the supports exert on the body solved for: (Hx, Hz) of the heel on the boom, R_rb and R_fb of the leg bases on the legs, R_top of the top joint on the front leg (the rear leg gets -R_top). Moment equations are about the origin (M = x Fz - z Fx). The platform resultant is (r_g_x, r_g_z, m_g) = -(platform loads - the boom and leg reactions).</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>calculation/solver/crane_solver.py _run_statics, _reactions_from_raw</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Unknowns are the forces the supports exert on the body solved for: (Hx, Hz) of the heel on the boom, R_rb and R_fb of the leg bases on the legs, R_top of the top joint on the front leg (the rear leg gets -R_top). Moment equations are about the origin (M = x Fz - z Fx). The platform resultant is (r_g_x, r_g_z, m_g) = -(platform loads - the boom and leg reactions).</t>
+          <t>A system counts as singular when |det A| &lt;= 1e-12 x the product of its row norms or MINVERSE fails (the app uses the same test, is_ill_conditioned). Results then show the reason instead of numbers.</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>calculation/solver/crane_solver.py _run_statics, _reactions_from_raw</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>A system counts as singular when |det A| &lt;= 1e-12 x the product of its row norms or MINVERSE fails (the app: np.linalg.solve raising, exactly singular only). Results then show the reason instead of numbers.</t>
-        </is>
-      </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
           <t>calculation/solver/crane_solver.py _run_statics</t>
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>Tables</t>
+        </is>
+      </c>
+    </row>
     <row r="53">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>Tables</t>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Every table has a fixed number of rows with an Active column (1 = in use, 0 = spare). Spare rows keep Active = 0 and every other cell blank; they change no result. Keep each table's red guard row blank; rows that do not fit are counted on Checks.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Every table has a fixed number of rows with an Active column (1 = in use, 0 = spare). Spare rows keep Active = 0 and every other cell blank; they change no result. Keep each table's red guard row blank; rows that do not fit are counted on Checks.</t>
+          <t>Ids are matched case-insensitively by Excel and must not contain * ? ~.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Ids are matched case-insensitively by Excel and must not contain * ? ~.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
           <t>The nine fixed node ids (boom_heel, platform_heel, rear_top, front_top, rear_base, platform_rear, front_base, platform_front, platform_base) take their x/z from the structure points by formula.</t>
         </is>
       </c>
-      <c r="B56" s="7" t="inlineStr">
+      <c r="B55" s="7" t="inlineStr">
         <is>
           <t>data/models.py</t>
         </is>
@@ -12389,7 +12377,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>|sin(boom angle)| (body boom areas)</t>
+          <t>|sin(boom angle)| (body boom areas, X wind only)</t>
         </is>
       </c>
       <c r="B23" s="3">
@@ -34949,7 +34937,7 @@
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>Each system A x = b is solved with MMULT(MINVERSE(A), b) (a legacy array formula). The app calls np.linalg.solve and gives no result when it raises (an exactly singular matrix). Here a matrix is flagged singular when |det A| &lt;= 1e-12 x the product of its row norms (Hadamard bound), or when MINVERSE fails; the solution column then reads 0 and Results shows a message.</t>
+          <t>Each system A x = b is solved with MMULT(MINVERSE(A), b) (a legacy array formula). A matrix is flagged singular when |det A| &lt;= 1e-12 x the product of its row norms (Hadamard bound), or when MINVERSE fails -- the app's own test (crane_solver is_ill_conditioned), where it gives no result; the solution column then reads 0 and Results shows a message.</t>
         </is>
       </c>
     </row>
@@ -36529,7 +36517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N242"/>
+  <dimension ref="A1:N241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -36565,7 +36553,7 @@
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>Y loads: every mass point and every lumped mass (rope self-weight, idle hook blocks; y = 0) carries Fy = -m (ay' - roll' (z - z_ref)) (crane-frame ay' = Geometry solver_ay, roll' = roll_accel_crane); Y wind Fy = sign q Cd A_y scale (scale = |sin(boom angle)| for boom-local areas only); the sidelead force sin(sidelead) x hook load acts in +y at the scene hoist's support node (its hook node if the support is missing), at its kinematic position (before the tackle moves the hook).</t>
+          <t>Y loads: every mass point and every lumped mass (rope self-weight, idle hook blocks; y = 0) carries Fy = -m (ay' - roll' (z - z_ref)) (crane-frame ay' = Geometry solver_ay, roll' = roll_accel_crane); Y wind Fy = sign q Cd A_y (the full Y area at any boom angle; only X wind on boom areas is scaled by |sin(boom angle)|); the sidelead force sin(sidelead) x hook load acts in +y at the scene hoist's support node (its hook node if the support is missing), at its kinematic position (before the tackle moves the hook).</t>
         </is>
       </c>
     </row>
@@ -36579,14 +36567,14 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>Split (as the app, possibly an app sign bug): left = 0.5 total + M / boom width, right = 0.5 total - M / boom width, Fx using Mz and Fz using Mx; total = the in-plane reaction (Statics). So heel_left behaves as the -Y side.</t>
+          <t>Split: left (+Y, port) = 0.5 total - M / boom width, right (-Y, starboard) = 0.5 total + M / boom width, Fx using Mz and Fz using Mx; total = the in-plane reaction (Statics). A mass at +Y loads the left side.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>Platform base Fy = the sum of all applied Fy, Mx = Mx of the applied loads about platform_heel: the sign of the loads, not of a reaction (as the app). The front/rear leg splits are shown but the Scene does not report them.</t>
+          <t>Platform base Fy and Mx are support reactions (the force the support exerts on the crane), like Fx, Fz and My: Fy = -(sum of all applied Fy), Mx = -(Mx of the applied loads about platform_heel). The front/rear leg splits are shown but the Scene does not report them.</t>
         </is>
       </c>
     </row>
@@ -36712,27 +36700,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>|sin(boom angle)| (boom-local areas)</t>
+          <t>Hook load</t>
         </is>
       </c>
       <c r="B17" s="3">
-        <f>Loads!$B$23</f>
-        <v/>
+        <f>Loads!$B$24</f>
+        <v/>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>kN</t>
+        </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>boom_wind_scale  -- Loads</t>
+          <t>hook_kN  -- scene value</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Hook load</t>
+          <t>Side force sin(sidelead) x hook load</t>
         </is>
       </c>
       <c r="B18" s="3">
-        <f>Loads!$B$24</f>
+        <f>SIN(RADIANS(Inputs!$B$31))*OutOfPlane!$B$17</f>
         <v/>
       </c>
       <c r="C18" t="inlineStr">
@@ -36742,179 +36735,179 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>hook_kN  -- scene value</t>
+          <t>sidelead_kN  -- +y</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Side force sin(sidelead) x hook load</t>
+          <t>Boom width (heel left/right spacing)</t>
         </is>
       </c>
       <c r="B19" s="3">
-        <f>SIN(RADIANS(Inputs!$B$31))*OutOfPlane!$B$18</f>
+        <f>Inputs!$B$12+0</f>
         <v/>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>kN</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>sidelead_kN  -- +y</t>
+          <t>boom_width_m  -- Inputs structure</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Boom width (heel left/right spacing)</t>
+          <t>Boom width &gt; 0</t>
         </is>
       </c>
       <c r="B20" s="3">
-        <f>Inputs!$B$12+0</f>
+        <f>IF(OutOfPlane!$B$19&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>1/0</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>boom_width_m  -- Inputs structure</t>
+          <t>width_ok  -- 0 trips check zero_boom_width</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Boom width &gt; 0</t>
+          <t>Slewing bearing diameter</t>
         </is>
       </c>
       <c r="B21" s="3">
-        <f>IF(OutOfPlane!$B$20&gt;0,1,0)</f>
+        <f>Inputs!$B$13+0</f>
         <v/>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1/0</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>width_ok  -- 0 trips check zero_boom_width</t>
+          <t>bearing_d_m  -- Inputs structure; may be blank</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Slewing bearing diameter</t>
+          <t>Bearing diameter &gt; 0</t>
         </is>
       </c>
       <c r="B22" s="3">
-        <f>Inputs!$B$13+0</f>
+        <f>IF(OutOfPlane!$B$21&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>1/0</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>bearing_d_m  -- Inputs structure; may be blank</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Bearing diameter &gt; 0</t>
-        </is>
-      </c>
-      <c r="B23" s="3">
-        <f>IF(OutOfPlane!$B$22&gt;0,1,0)</f>
-        <v/>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>1/0</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
           <t>bearing_ok  -- 0: bearing rows are n/a</t>
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Sidelead force (scene hoist)</t>
+        </is>
+      </c>
+    </row>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>Sidelead force (scene hoist)</t>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Row of the scene hoist in hoists</t>
+        </is>
+      </c>
+      <c r="B25" s="3">
+        <f>IF(Inputs!$B$26="",0,IFERROR(MATCH(Inputs!$B$26&amp;"",Loads!$B$139:$B$146,0),0))</f>
+        <v/>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>hoist_row  -- 0 = missing</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Row of the scene hoist in hoists</t>
+          <t>Its support node</t>
         </is>
       </c>
       <c r="B26" s="3">
-        <f>IF(Inputs!$B$26="",0,IFERROR(MATCH(Inputs!$B$26&amp;"",Loads!$B$139:$B$146,0),0))</f>
-        <v/>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>row</t>
-        </is>
+        <f>IF(OutOfPlane!$B$25&gt;0,INDEX(Inputs!$E$304:$E$311,OutOfPlane!$B$25)&amp;"","")</f>
+        <v/>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>hoist_row  -- 0 = missing</t>
+          <t>support_id  -- Inputs hoists support_node_id</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Its support node</t>
+          <t>Its hook node (fallback)</t>
         </is>
       </c>
       <c r="B27" s="3">
-        <f>IF(OutOfPlane!$B$26&gt;0,INDEX(Inputs!$E$304:$E$311,OutOfPlane!$B$26)&amp;"","")</f>
+        <f>IF(OutOfPlane!$B$25&gt;0,INDEX(Inputs!$D$304:$D$311,OutOfPlane!$B$25)&amp;"","")</f>
         <v/>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>support_id  -- Inputs hoists support_node_id</t>
+          <t>hook_id  -- Inputs hoists load_node_id</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Its hook node (fallback)</t>
+          <t>Row of the support node in nodes</t>
         </is>
       </c>
       <c r="B28" s="3">
-        <f>IF(OutOfPlane!$B$26&gt;0,INDEX(Inputs!$D$304:$D$311,OutOfPlane!$B$26)&amp;"","")</f>
-        <v/>
+        <f>IF(OutOfPlane!$B$26="",0,IFERROR(MATCH(OutOfPlane!$B$26,Geometry!$B$58:$B$137,0),0))</f>
+        <v/>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>hook_id  -- Inputs hoists load_node_id</t>
+          <t>support_row  -- 0 = missing</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Row of the support node in nodes</t>
+          <t>Row of the hook node in nodes</t>
         </is>
       </c>
       <c r="B29" s="3">
@@ -36928,18 +36921,18 @@
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>support_row  -- 0 = missing</t>
+          <t>hook_row  -- 0 = missing</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Row of the hook node in nodes</t>
+          <t>Row of the node the side force acts at</t>
         </is>
       </c>
       <c r="B30" s="3">
-        <f>IF(OutOfPlane!$B$28="",0,IFERROR(MATCH(OutOfPlane!$B$28,Geometry!$B$58:$B$137,0),0))</f>
+        <f>IF(OutOfPlane!$B$28&gt;0,OutOfPlane!$B$28,OutOfPlane!$B$29)</f>
         <v/>
       </c>
       <c r="C30" t="inlineStr">
@@ -36949,39 +36942,39 @@
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>hook_row  -- 0 = missing</t>
+          <t>node_row  -- support, else hook</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Row of the node the side force acts at</t>
+          <t>Its x (kinematics)</t>
         </is>
       </c>
       <c r="B31" s="3">
-        <f>IF(OutOfPlane!$B$29&gt;0,OutOfPlane!$B$29,OutOfPlane!$B$30)</f>
+        <f>IF(OutOfPlane!$B$30&gt;0,INDEX(Geometry!$H$58:$H$137,OutOfPlane!$B$30),0)</f>
         <v/>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>row</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>node_row  -- support, else hook</t>
+          <t>x_m  -- Geometry x_kin_m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Its x (kinematics)</t>
+          <t>Its z (kinematics)</t>
         </is>
       </c>
       <c r="B32" s="3">
-        <f>IF(OutOfPlane!$B$31&gt;0,INDEX(Geometry!$H$58:$H$137,OutOfPlane!$B$31),0)</f>
+        <f>IF(OutOfPlane!$B$30&gt;0,INDEX(Geometry!$I$58:$I$137,OutOfPlane!$B$30),0)</f>
         <v/>
       </c>
       <c r="C32" t="inlineStr">
@@ -36991,198 +36984,219 @@
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>x_m  -- Geometry x_kin_m</t>
+          <t>z_m  -- Geometry z_kin_m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Its z (kinematics)</t>
+          <t>Side force Fy</t>
         </is>
       </c>
       <c r="B33" s="3">
-        <f>IF(OutOfPlane!$B$31&gt;0,INDEX(Geometry!$I$58:$I$137,OutOfPlane!$B$31),0)</f>
+        <f>IF(OutOfPlane!$B$30&gt;0,OutOfPlane!$B$18,0)</f>
         <v/>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kN</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>z_m  -- Geometry z_kin_m</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Side force Fy</t>
-        </is>
-      </c>
-      <c r="B34" s="3">
-        <f>IF(OutOfPlane!$B$31&gt;0,OutOfPlane!$B$19,0)</f>
-        <v/>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>kN</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
           <t>fy_kN  -- 0 if no node</t>
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Mass points (row i = Inputs mass points row i)</t>
+        </is>
+      </c>
+    </row>
     <row r="36">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>Mass points (row i = Inputs mass points row i)</t>
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>Active [1/0]</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>Body</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>Frame</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>x global [m]</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>y (boom-local v, else y) [m]</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>z global [m]</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
+          <t>Mass [t]</t>
+        </is>
+      </c>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t>Fx = weight + inertia [kN]</t>
+        </is>
+      </c>
+      <c r="I36" s="8" t="inlineStr">
+        <is>
+          <t>Fz = weight + inertia [kN]</t>
+        </is>
+      </c>
+      <c r="J36" s="8" t="inlineStr">
+        <is>
+          <t>Fy = -m (ay' - roll' (z - z_ref)) [kN]</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="inlineStr">
-        <is>
-          <t>Active [1/0]</t>
-        </is>
-      </c>
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>Body</t>
-        </is>
-      </c>
-      <c r="C37" s="8" t="inlineStr">
-        <is>
-          <t>Frame</t>
-        </is>
-      </c>
-      <c r="D37" s="8" t="inlineStr">
-        <is>
-          <t>x global [m]</t>
-        </is>
-      </c>
-      <c r="E37" s="8" t="inlineStr">
-        <is>
-          <t>y (boom-local v, else y) [m]</t>
-        </is>
-      </c>
-      <c r="F37" s="8" t="inlineStr">
-        <is>
-          <t>z global [m]</t>
-        </is>
-      </c>
-      <c r="G37" s="8" t="inlineStr">
-        <is>
-          <t>Mass [t]</t>
-        </is>
-      </c>
-      <c r="H37" s="8" t="inlineStr">
-        <is>
-          <t>Fx = weight + inertia [kN]</t>
-        </is>
-      </c>
-      <c r="I37" s="8" t="inlineStr">
-        <is>
-          <t>Fz = weight + inertia [kN]</t>
-        </is>
-      </c>
-      <c r="J37" s="8" t="inlineStr">
-        <is>
-          <t>Fy = -m (ay' - roll' (z - z_ref)) [kN]</t>
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>active (from Inputs)</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>frame</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>x_m (Loads)</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>y_m</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>z_m (Loads)</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>mass_t</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>fx_kN (Loads)</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>fz_kN (Loads)</t>
+        </is>
+      </c>
+      <c r="J37" s="7" t="inlineStr">
+        <is>
+          <t>fy_kN</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>active (from Inputs)</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>body</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>frame</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>x_m (Loads)</t>
-        </is>
-      </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t>y_m</t>
-        </is>
-      </c>
-      <c r="F38" s="7" t="inlineStr">
-        <is>
-          <t>z_m (Loads)</t>
-        </is>
-      </c>
-      <c r="G38" s="7" t="inlineStr">
-        <is>
-          <t>mass_t</t>
-        </is>
-      </c>
-      <c r="H38" s="7" t="inlineStr">
-        <is>
-          <t>fx_kN (Loads)</t>
-        </is>
-      </c>
-      <c r="I38" s="7" t="inlineStr">
-        <is>
-          <t>fz_kN (Loads)</t>
-        </is>
-      </c>
-      <c r="J38" s="7" t="inlineStr">
-        <is>
-          <t>fy_kN</t>
-        </is>
+      <c r="A38" s="3">
+        <f>Inputs!$A$46</f>
+        <v/>
+      </c>
+      <c r="B38" s="3">
+        <f>Loads!$B$33</f>
+        <v/>
+      </c>
+      <c r="C38" s="3">
+        <f>IF(OutOfPlane!$A$38=1,Inputs!$D$46&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="D38" s="3">
+        <f>Loads!$C$33</f>
+        <v/>
+      </c>
+      <c r="E38" s="3">
+        <f>IF(OutOfPlane!$A$38=1,IF(OutOfPlane!$C$38="boom_local",Inputs!$G$46,Inputs!$J$46)+0,0)</f>
+        <v/>
+      </c>
+      <c r="F38" s="3">
+        <f>Loads!$D$33</f>
+        <v/>
+      </c>
+      <c r="G38" s="3">
+        <f>Loads!$E$33</f>
+        <v/>
+      </c>
+      <c r="H38" s="3">
+        <f>Loads!$L$33</f>
+        <v/>
+      </c>
+      <c r="I38" s="3">
+        <f>Loads!$M$33</f>
+        <v/>
+      </c>
+      <c r="J38" s="3">
+        <f>-OutOfPlane!$G$38*(OutOfPlane!$B$13-OutOfPlane!$B$14*(OutOfPlane!$F$38-OutOfPlane!$B$12))</f>
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3">
-        <f>Inputs!$A$46</f>
+        <f>Inputs!$A$47</f>
         <v/>
       </c>
       <c r="B39" s="3">
-        <f>Loads!$B$33</f>
+        <f>Loads!$B$34</f>
         <v/>
       </c>
       <c r="C39" s="3">
-        <f>IF(OutOfPlane!$A$39=1,Inputs!$D$46&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$39=1,Inputs!$D$47&amp;"","")</f>
         <v/>
       </c>
       <c r="D39" s="3">
-        <f>Loads!$C$33</f>
+        <f>Loads!$C$34</f>
         <v/>
       </c>
       <c r="E39" s="3">
-        <f>IF(OutOfPlane!$A$39=1,IF(OutOfPlane!$C$39="boom_local",Inputs!$G$46,Inputs!$J$46)+0,0)</f>
+        <f>IF(OutOfPlane!$A$39=1,IF(OutOfPlane!$C$39="boom_local",Inputs!$G$47,Inputs!$J$47)+0,0)</f>
         <v/>
       </c>
       <c r="F39" s="3">
-        <f>Loads!$D$33</f>
+        <f>Loads!$D$34</f>
         <v/>
       </c>
       <c r="G39" s="3">
-        <f>Loads!$E$33</f>
+        <f>Loads!$E$34</f>
         <v/>
       </c>
       <c r="H39" s="3">
-        <f>Loads!$L$33</f>
+        <f>Loads!$L$34</f>
         <v/>
       </c>
       <c r="I39" s="3">
-        <f>Loads!$M$33</f>
+        <f>Loads!$M$34</f>
         <v/>
       </c>
       <c r="J39" s="3">
@@ -37192,39 +37206,39 @@
     </row>
     <row r="40">
       <c r="A40" s="3">
-        <f>Inputs!$A$47</f>
+        <f>Inputs!$A$48</f>
         <v/>
       </c>
       <c r="B40" s="3">
-        <f>Loads!$B$34</f>
+        <f>Loads!$B$35</f>
         <v/>
       </c>
       <c r="C40" s="3">
-        <f>IF(OutOfPlane!$A$40=1,Inputs!$D$47&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$40=1,Inputs!$D$48&amp;"","")</f>
         <v/>
       </c>
       <c r="D40" s="3">
-        <f>Loads!$C$34</f>
+        <f>Loads!$C$35</f>
         <v/>
       </c>
       <c r="E40" s="3">
-        <f>IF(OutOfPlane!$A$40=1,IF(OutOfPlane!$C$40="boom_local",Inputs!$G$47,Inputs!$J$47)+0,0)</f>
+        <f>IF(OutOfPlane!$A$40=1,IF(OutOfPlane!$C$40="boom_local",Inputs!$G$48,Inputs!$J$48)+0,0)</f>
         <v/>
       </c>
       <c r="F40" s="3">
-        <f>Loads!$D$34</f>
+        <f>Loads!$D$35</f>
         <v/>
       </c>
       <c r="G40" s="3">
-        <f>Loads!$E$34</f>
+        <f>Loads!$E$35</f>
         <v/>
       </c>
       <c r="H40" s="3">
-        <f>Loads!$L$34</f>
+        <f>Loads!$L$35</f>
         <v/>
       </c>
       <c r="I40" s="3">
-        <f>Loads!$M$34</f>
+        <f>Loads!$M$35</f>
         <v/>
       </c>
       <c r="J40" s="3">
@@ -37234,39 +37248,39 @@
     </row>
     <row r="41">
       <c r="A41" s="3">
-        <f>Inputs!$A$48</f>
+        <f>Inputs!$A$49</f>
         <v/>
       </c>
       <c r="B41" s="3">
-        <f>Loads!$B$35</f>
+        <f>Loads!$B$36</f>
         <v/>
       </c>
       <c r="C41" s="3">
-        <f>IF(OutOfPlane!$A$41=1,Inputs!$D$48&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$41=1,Inputs!$D$49&amp;"","")</f>
         <v/>
       </c>
       <c r="D41" s="3">
-        <f>Loads!$C$35</f>
+        <f>Loads!$C$36</f>
         <v/>
       </c>
       <c r="E41" s="3">
-        <f>IF(OutOfPlane!$A$41=1,IF(OutOfPlane!$C$41="boom_local",Inputs!$G$48,Inputs!$J$48)+0,0)</f>
+        <f>IF(OutOfPlane!$A$41=1,IF(OutOfPlane!$C$41="boom_local",Inputs!$G$49,Inputs!$J$49)+0,0)</f>
         <v/>
       </c>
       <c r="F41" s="3">
-        <f>Loads!$D$35</f>
+        <f>Loads!$D$36</f>
         <v/>
       </c>
       <c r="G41" s="3">
-        <f>Loads!$E$35</f>
+        <f>Loads!$E$36</f>
         <v/>
       </c>
       <c r="H41" s="3">
-        <f>Loads!$L$35</f>
+        <f>Loads!$L$36</f>
         <v/>
       </c>
       <c r="I41" s="3">
-        <f>Loads!$M$35</f>
+        <f>Loads!$M$36</f>
         <v/>
       </c>
       <c r="J41" s="3">
@@ -37276,39 +37290,39 @@
     </row>
     <row r="42">
       <c r="A42" s="3">
-        <f>Inputs!$A$49</f>
+        <f>Inputs!$A$50</f>
         <v/>
       </c>
       <c r="B42" s="3">
-        <f>Loads!$B$36</f>
+        <f>Loads!$B$37</f>
         <v/>
       </c>
       <c r="C42" s="3">
-        <f>IF(OutOfPlane!$A$42=1,Inputs!$D$49&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$42=1,Inputs!$D$50&amp;"","")</f>
         <v/>
       </c>
       <c r="D42" s="3">
-        <f>Loads!$C$36</f>
+        <f>Loads!$C$37</f>
         <v/>
       </c>
       <c r="E42" s="3">
-        <f>IF(OutOfPlane!$A$42=1,IF(OutOfPlane!$C$42="boom_local",Inputs!$G$49,Inputs!$J$49)+0,0)</f>
+        <f>IF(OutOfPlane!$A$42=1,IF(OutOfPlane!$C$42="boom_local",Inputs!$G$50,Inputs!$J$50)+0,0)</f>
         <v/>
       </c>
       <c r="F42" s="3">
-        <f>Loads!$D$36</f>
+        <f>Loads!$D$37</f>
         <v/>
       </c>
       <c r="G42" s="3">
-        <f>Loads!$E$36</f>
+        <f>Loads!$E$37</f>
         <v/>
       </c>
       <c r="H42" s="3">
-        <f>Loads!$L$36</f>
+        <f>Loads!$L$37</f>
         <v/>
       </c>
       <c r="I42" s="3">
-        <f>Loads!$M$36</f>
+        <f>Loads!$M$37</f>
         <v/>
       </c>
       <c r="J42" s="3">
@@ -37318,39 +37332,39 @@
     </row>
     <row r="43">
       <c r="A43" s="3">
-        <f>Inputs!$A$50</f>
+        <f>Inputs!$A$51</f>
         <v/>
       </c>
       <c r="B43" s="3">
-        <f>Loads!$B$37</f>
+        <f>Loads!$B$38</f>
         <v/>
       </c>
       <c r="C43" s="3">
-        <f>IF(OutOfPlane!$A$43=1,Inputs!$D$50&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$43=1,Inputs!$D$51&amp;"","")</f>
         <v/>
       </c>
       <c r="D43" s="3">
-        <f>Loads!$C$37</f>
+        <f>Loads!$C$38</f>
         <v/>
       </c>
       <c r="E43" s="3">
-        <f>IF(OutOfPlane!$A$43=1,IF(OutOfPlane!$C$43="boom_local",Inputs!$G$50,Inputs!$J$50)+0,0)</f>
+        <f>IF(OutOfPlane!$A$43=1,IF(OutOfPlane!$C$43="boom_local",Inputs!$G$51,Inputs!$J$51)+0,0)</f>
         <v/>
       </c>
       <c r="F43" s="3">
-        <f>Loads!$D$37</f>
+        <f>Loads!$D$38</f>
         <v/>
       </c>
       <c r="G43" s="3">
-        <f>Loads!$E$37</f>
+        <f>Loads!$E$38</f>
         <v/>
       </c>
       <c r="H43" s="3">
-        <f>Loads!$L$37</f>
+        <f>Loads!$L$38</f>
         <v/>
       </c>
       <c r="I43" s="3">
-        <f>Loads!$M$37</f>
+        <f>Loads!$M$38</f>
         <v/>
       </c>
       <c r="J43" s="3">
@@ -37360,39 +37374,39 @@
     </row>
     <row r="44">
       <c r="A44" s="3">
-        <f>Inputs!$A$51</f>
+        <f>Inputs!$A$52</f>
         <v/>
       </c>
       <c r="B44" s="3">
-        <f>Loads!$B$38</f>
+        <f>Loads!$B$39</f>
         <v/>
       </c>
       <c r="C44" s="3">
-        <f>IF(OutOfPlane!$A$44=1,Inputs!$D$51&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$44=1,Inputs!$D$52&amp;"","")</f>
         <v/>
       </c>
       <c r="D44" s="3">
-        <f>Loads!$C$38</f>
+        <f>Loads!$C$39</f>
         <v/>
       </c>
       <c r="E44" s="3">
-        <f>IF(OutOfPlane!$A$44=1,IF(OutOfPlane!$C$44="boom_local",Inputs!$G$51,Inputs!$J$51)+0,0)</f>
+        <f>IF(OutOfPlane!$A$44=1,IF(OutOfPlane!$C$44="boom_local",Inputs!$G$52,Inputs!$J$52)+0,0)</f>
         <v/>
       </c>
       <c r="F44" s="3">
-        <f>Loads!$D$38</f>
+        <f>Loads!$D$39</f>
         <v/>
       </c>
       <c r="G44" s="3">
-        <f>Loads!$E$38</f>
+        <f>Loads!$E$39</f>
         <v/>
       </c>
       <c r="H44" s="3">
-        <f>Loads!$L$38</f>
+        <f>Loads!$L$39</f>
         <v/>
       </c>
       <c r="I44" s="3">
-        <f>Loads!$M$38</f>
+        <f>Loads!$M$39</f>
         <v/>
       </c>
       <c r="J44" s="3">
@@ -37402,39 +37416,39 @@
     </row>
     <row r="45">
       <c r="A45" s="3">
-        <f>Inputs!$A$52</f>
+        <f>Inputs!$A$53</f>
         <v/>
       </c>
       <c r="B45" s="3">
-        <f>Loads!$B$39</f>
+        <f>Loads!$B$40</f>
         <v/>
       </c>
       <c r="C45" s="3">
-        <f>IF(OutOfPlane!$A$45=1,Inputs!$D$52&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$45=1,Inputs!$D$53&amp;"","")</f>
         <v/>
       </c>
       <c r="D45" s="3">
-        <f>Loads!$C$39</f>
+        <f>Loads!$C$40</f>
         <v/>
       </c>
       <c r="E45" s="3">
-        <f>IF(OutOfPlane!$A$45=1,IF(OutOfPlane!$C$45="boom_local",Inputs!$G$52,Inputs!$J$52)+0,0)</f>
+        <f>IF(OutOfPlane!$A$45=1,IF(OutOfPlane!$C$45="boom_local",Inputs!$G$53,Inputs!$J$53)+0,0)</f>
         <v/>
       </c>
       <c r="F45" s="3">
-        <f>Loads!$D$39</f>
+        <f>Loads!$D$40</f>
         <v/>
       </c>
       <c r="G45" s="3">
-        <f>Loads!$E$39</f>
+        <f>Loads!$E$40</f>
         <v/>
       </c>
       <c r="H45" s="3">
-        <f>Loads!$L$39</f>
+        <f>Loads!$L$40</f>
         <v/>
       </c>
       <c r="I45" s="3">
-        <f>Loads!$M$39</f>
+        <f>Loads!$M$40</f>
         <v/>
       </c>
       <c r="J45" s="3">
@@ -37444,39 +37458,39 @@
     </row>
     <row r="46">
       <c r="A46" s="3">
-        <f>Inputs!$A$53</f>
+        <f>Inputs!$A$54</f>
         <v/>
       </c>
       <c r="B46" s="3">
-        <f>Loads!$B$40</f>
+        <f>Loads!$B$41</f>
         <v/>
       </c>
       <c r="C46" s="3">
-        <f>IF(OutOfPlane!$A$46=1,Inputs!$D$53&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$46=1,Inputs!$D$54&amp;"","")</f>
         <v/>
       </c>
       <c r="D46" s="3">
-        <f>Loads!$C$40</f>
+        <f>Loads!$C$41</f>
         <v/>
       </c>
       <c r="E46" s="3">
-        <f>IF(OutOfPlane!$A$46=1,IF(OutOfPlane!$C$46="boom_local",Inputs!$G$53,Inputs!$J$53)+0,0)</f>
+        <f>IF(OutOfPlane!$A$46=1,IF(OutOfPlane!$C$46="boom_local",Inputs!$G$54,Inputs!$J$54)+0,0)</f>
         <v/>
       </c>
       <c r="F46" s="3">
-        <f>Loads!$D$40</f>
+        <f>Loads!$D$41</f>
         <v/>
       </c>
       <c r="G46" s="3">
-        <f>Loads!$E$40</f>
+        <f>Loads!$E$41</f>
         <v/>
       </c>
       <c r="H46" s="3">
-        <f>Loads!$L$40</f>
+        <f>Loads!$L$41</f>
         <v/>
       </c>
       <c r="I46" s="3">
-        <f>Loads!$M$40</f>
+        <f>Loads!$M$41</f>
         <v/>
       </c>
       <c r="J46" s="3">
@@ -37486,39 +37500,39 @@
     </row>
     <row r="47">
       <c r="A47" s="3">
-        <f>Inputs!$A$54</f>
+        <f>Inputs!$A$55</f>
         <v/>
       </c>
       <c r="B47" s="3">
-        <f>Loads!$B$41</f>
+        <f>Loads!$B$42</f>
         <v/>
       </c>
       <c r="C47" s="3">
-        <f>IF(OutOfPlane!$A$47=1,Inputs!$D$54&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$47=1,Inputs!$D$55&amp;"","")</f>
         <v/>
       </c>
       <c r="D47" s="3">
-        <f>Loads!$C$41</f>
+        <f>Loads!$C$42</f>
         <v/>
       </c>
       <c r="E47" s="3">
-        <f>IF(OutOfPlane!$A$47=1,IF(OutOfPlane!$C$47="boom_local",Inputs!$G$54,Inputs!$J$54)+0,0)</f>
+        <f>IF(OutOfPlane!$A$47=1,IF(OutOfPlane!$C$47="boom_local",Inputs!$G$55,Inputs!$J$55)+0,0)</f>
         <v/>
       </c>
       <c r="F47" s="3">
-        <f>Loads!$D$41</f>
+        <f>Loads!$D$42</f>
         <v/>
       </c>
       <c r="G47" s="3">
-        <f>Loads!$E$41</f>
+        <f>Loads!$E$42</f>
         <v/>
       </c>
       <c r="H47" s="3">
-        <f>Loads!$L$41</f>
+        <f>Loads!$L$42</f>
         <v/>
       </c>
       <c r="I47" s="3">
-        <f>Loads!$M$41</f>
+        <f>Loads!$M$42</f>
         <v/>
       </c>
       <c r="J47" s="3">
@@ -37528,39 +37542,39 @@
     </row>
     <row r="48">
       <c r="A48" s="3">
-        <f>Inputs!$A$55</f>
+        <f>Inputs!$A$56</f>
         <v/>
       </c>
       <c r="B48" s="3">
-        <f>Loads!$B$42</f>
+        <f>Loads!$B$43</f>
         <v/>
       </c>
       <c r="C48" s="3">
-        <f>IF(OutOfPlane!$A$48=1,Inputs!$D$55&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$48=1,Inputs!$D$56&amp;"","")</f>
         <v/>
       </c>
       <c r="D48" s="3">
-        <f>Loads!$C$42</f>
+        <f>Loads!$C$43</f>
         <v/>
       </c>
       <c r="E48" s="3">
-        <f>IF(OutOfPlane!$A$48=1,IF(OutOfPlane!$C$48="boom_local",Inputs!$G$55,Inputs!$J$55)+0,0)</f>
+        <f>IF(OutOfPlane!$A$48=1,IF(OutOfPlane!$C$48="boom_local",Inputs!$G$56,Inputs!$J$56)+0,0)</f>
         <v/>
       </c>
       <c r="F48" s="3">
-        <f>Loads!$D$42</f>
+        <f>Loads!$D$43</f>
         <v/>
       </c>
       <c r="G48" s="3">
-        <f>Loads!$E$42</f>
+        <f>Loads!$E$43</f>
         <v/>
       </c>
       <c r="H48" s="3">
-        <f>Loads!$L$42</f>
+        <f>Loads!$L$43</f>
         <v/>
       </c>
       <c r="I48" s="3">
-        <f>Loads!$M$42</f>
+        <f>Loads!$M$43</f>
         <v/>
       </c>
       <c r="J48" s="3">
@@ -37570,39 +37584,39 @@
     </row>
     <row r="49">
       <c r="A49" s="3">
-        <f>Inputs!$A$56</f>
+        <f>Inputs!$A$57</f>
         <v/>
       </c>
       <c r="B49" s="3">
-        <f>Loads!$B$43</f>
+        <f>Loads!$B$44</f>
         <v/>
       </c>
       <c r="C49" s="3">
-        <f>IF(OutOfPlane!$A$49=1,Inputs!$D$56&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$49=1,Inputs!$D$57&amp;"","")</f>
         <v/>
       </c>
       <c r="D49" s="3">
-        <f>Loads!$C$43</f>
+        <f>Loads!$C$44</f>
         <v/>
       </c>
       <c r="E49" s="3">
-        <f>IF(OutOfPlane!$A$49=1,IF(OutOfPlane!$C$49="boom_local",Inputs!$G$56,Inputs!$J$56)+0,0)</f>
+        <f>IF(OutOfPlane!$A$49=1,IF(OutOfPlane!$C$49="boom_local",Inputs!$G$57,Inputs!$J$57)+0,0)</f>
         <v/>
       </c>
       <c r="F49" s="3">
-        <f>Loads!$D$43</f>
+        <f>Loads!$D$44</f>
         <v/>
       </c>
       <c r="G49" s="3">
-        <f>Loads!$E$43</f>
+        <f>Loads!$E$44</f>
         <v/>
       </c>
       <c r="H49" s="3">
-        <f>Loads!$L$43</f>
+        <f>Loads!$L$44</f>
         <v/>
       </c>
       <c r="I49" s="3">
-        <f>Loads!$M$43</f>
+        <f>Loads!$M$44</f>
         <v/>
       </c>
       <c r="J49" s="3">
@@ -37612,39 +37626,39 @@
     </row>
     <row r="50">
       <c r="A50" s="3">
-        <f>Inputs!$A$57</f>
+        <f>Inputs!$A$58</f>
         <v/>
       </c>
       <c r="B50" s="3">
-        <f>Loads!$B$44</f>
+        <f>Loads!$B$45</f>
         <v/>
       </c>
       <c r="C50" s="3">
-        <f>IF(OutOfPlane!$A$50=1,Inputs!$D$57&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$50=1,Inputs!$D$58&amp;"","")</f>
         <v/>
       </c>
       <c r="D50" s="3">
-        <f>Loads!$C$44</f>
+        <f>Loads!$C$45</f>
         <v/>
       </c>
       <c r="E50" s="3">
-        <f>IF(OutOfPlane!$A$50=1,IF(OutOfPlane!$C$50="boom_local",Inputs!$G$57,Inputs!$J$57)+0,0)</f>
+        <f>IF(OutOfPlane!$A$50=1,IF(OutOfPlane!$C$50="boom_local",Inputs!$G$58,Inputs!$J$58)+0,0)</f>
         <v/>
       </c>
       <c r="F50" s="3">
-        <f>Loads!$D$44</f>
+        <f>Loads!$D$45</f>
         <v/>
       </c>
       <c r="G50" s="3">
-        <f>Loads!$E$44</f>
+        <f>Loads!$E$45</f>
         <v/>
       </c>
       <c r="H50" s="3">
-        <f>Loads!$L$44</f>
+        <f>Loads!$L$45</f>
         <v/>
       </c>
       <c r="I50" s="3">
-        <f>Loads!$M$44</f>
+        <f>Loads!$M$45</f>
         <v/>
       </c>
       <c r="J50" s="3">
@@ -37654,39 +37668,39 @@
     </row>
     <row r="51">
       <c r="A51" s="3">
-        <f>Inputs!$A$58</f>
+        <f>Inputs!$A$59</f>
         <v/>
       </c>
       <c r="B51" s="3">
-        <f>Loads!$B$45</f>
+        <f>Loads!$B$46</f>
         <v/>
       </c>
       <c r="C51" s="3">
-        <f>IF(OutOfPlane!$A$51=1,Inputs!$D$58&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$51=1,Inputs!$D$59&amp;"","")</f>
         <v/>
       </c>
       <c r="D51" s="3">
-        <f>Loads!$C$45</f>
+        <f>Loads!$C$46</f>
         <v/>
       </c>
       <c r="E51" s="3">
-        <f>IF(OutOfPlane!$A$51=1,IF(OutOfPlane!$C$51="boom_local",Inputs!$G$58,Inputs!$J$58)+0,0)</f>
+        <f>IF(OutOfPlane!$A$51=1,IF(OutOfPlane!$C$51="boom_local",Inputs!$G$59,Inputs!$J$59)+0,0)</f>
         <v/>
       </c>
       <c r="F51" s="3">
-        <f>Loads!$D$45</f>
+        <f>Loads!$D$46</f>
         <v/>
       </c>
       <c r="G51" s="3">
-        <f>Loads!$E$45</f>
+        <f>Loads!$E$46</f>
         <v/>
       </c>
       <c r="H51" s="3">
-        <f>Loads!$L$45</f>
+        <f>Loads!$L$46</f>
         <v/>
       </c>
       <c r="I51" s="3">
-        <f>Loads!$M$45</f>
+        <f>Loads!$M$46</f>
         <v/>
       </c>
       <c r="J51" s="3">
@@ -37696,39 +37710,39 @@
     </row>
     <row r="52">
       <c r="A52" s="3">
-        <f>Inputs!$A$59</f>
+        <f>Inputs!$A$60</f>
         <v/>
       </c>
       <c r="B52" s="3">
-        <f>Loads!$B$46</f>
+        <f>Loads!$B$47</f>
         <v/>
       </c>
       <c r="C52" s="3">
-        <f>IF(OutOfPlane!$A$52=1,Inputs!$D$59&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$52=1,Inputs!$D$60&amp;"","")</f>
         <v/>
       </c>
       <c r="D52" s="3">
-        <f>Loads!$C$46</f>
+        <f>Loads!$C$47</f>
         <v/>
       </c>
       <c r="E52" s="3">
-        <f>IF(OutOfPlane!$A$52=1,IF(OutOfPlane!$C$52="boom_local",Inputs!$G$59,Inputs!$J$59)+0,0)</f>
+        <f>IF(OutOfPlane!$A$52=1,IF(OutOfPlane!$C$52="boom_local",Inputs!$G$60,Inputs!$J$60)+0,0)</f>
         <v/>
       </c>
       <c r="F52" s="3">
-        <f>Loads!$D$46</f>
+        <f>Loads!$D$47</f>
         <v/>
       </c>
       <c r="G52" s="3">
-        <f>Loads!$E$46</f>
+        <f>Loads!$E$47</f>
         <v/>
       </c>
       <c r="H52" s="3">
-        <f>Loads!$L$46</f>
+        <f>Loads!$L$47</f>
         <v/>
       </c>
       <c r="I52" s="3">
-        <f>Loads!$M$46</f>
+        <f>Loads!$M$47</f>
         <v/>
       </c>
       <c r="J52" s="3">
@@ -37738,39 +37752,39 @@
     </row>
     <row r="53">
       <c r="A53" s="3">
-        <f>Inputs!$A$60</f>
+        <f>Inputs!$A$61</f>
         <v/>
       </c>
       <c r="B53" s="3">
-        <f>Loads!$B$47</f>
+        <f>Loads!$B$48</f>
         <v/>
       </c>
       <c r="C53" s="3">
-        <f>IF(OutOfPlane!$A$53=1,Inputs!$D$60&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$53=1,Inputs!$D$61&amp;"","")</f>
         <v/>
       </c>
       <c r="D53" s="3">
-        <f>Loads!$C$47</f>
+        <f>Loads!$C$48</f>
         <v/>
       </c>
       <c r="E53" s="3">
-        <f>IF(OutOfPlane!$A$53=1,IF(OutOfPlane!$C$53="boom_local",Inputs!$G$60,Inputs!$J$60)+0,0)</f>
+        <f>IF(OutOfPlane!$A$53=1,IF(OutOfPlane!$C$53="boom_local",Inputs!$G$61,Inputs!$J$61)+0,0)</f>
         <v/>
       </c>
       <c r="F53" s="3">
-        <f>Loads!$D$47</f>
+        <f>Loads!$D$48</f>
         <v/>
       </c>
       <c r="G53" s="3">
-        <f>Loads!$E$47</f>
+        <f>Loads!$E$48</f>
         <v/>
       </c>
       <c r="H53" s="3">
-        <f>Loads!$L$47</f>
+        <f>Loads!$L$48</f>
         <v/>
       </c>
       <c r="I53" s="3">
-        <f>Loads!$M$47</f>
+        <f>Loads!$M$48</f>
         <v/>
       </c>
       <c r="J53" s="3">
@@ -37780,39 +37794,39 @@
     </row>
     <row r="54">
       <c r="A54" s="3">
-        <f>Inputs!$A$61</f>
+        <f>Inputs!$A$62</f>
         <v/>
       </c>
       <c r="B54" s="3">
-        <f>Loads!$B$48</f>
+        <f>Loads!$B$49</f>
         <v/>
       </c>
       <c r="C54" s="3">
-        <f>IF(OutOfPlane!$A$54=1,Inputs!$D$61&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$54=1,Inputs!$D$62&amp;"","")</f>
         <v/>
       </c>
       <c r="D54" s="3">
-        <f>Loads!$C$48</f>
+        <f>Loads!$C$49</f>
         <v/>
       </c>
       <c r="E54" s="3">
-        <f>IF(OutOfPlane!$A$54=1,IF(OutOfPlane!$C$54="boom_local",Inputs!$G$61,Inputs!$J$61)+0,0)</f>
+        <f>IF(OutOfPlane!$A$54=1,IF(OutOfPlane!$C$54="boom_local",Inputs!$G$62,Inputs!$J$62)+0,0)</f>
         <v/>
       </c>
       <c r="F54" s="3">
-        <f>Loads!$D$48</f>
+        <f>Loads!$D$49</f>
         <v/>
       </c>
       <c r="G54" s="3">
-        <f>Loads!$E$48</f>
+        <f>Loads!$E$49</f>
         <v/>
       </c>
       <c r="H54" s="3">
-        <f>Loads!$L$48</f>
+        <f>Loads!$L$49</f>
         <v/>
       </c>
       <c r="I54" s="3">
-        <f>Loads!$M$48</f>
+        <f>Loads!$M$49</f>
         <v/>
       </c>
       <c r="J54" s="3">
@@ -37822,39 +37836,39 @@
     </row>
     <row r="55">
       <c r="A55" s="3">
-        <f>Inputs!$A$62</f>
+        <f>Inputs!$A$63</f>
         <v/>
       </c>
       <c r="B55" s="3">
-        <f>Loads!$B$49</f>
+        <f>Loads!$B$50</f>
         <v/>
       </c>
       <c r="C55" s="3">
-        <f>IF(OutOfPlane!$A$55=1,Inputs!$D$62&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$55=1,Inputs!$D$63&amp;"","")</f>
         <v/>
       </c>
       <c r="D55" s="3">
-        <f>Loads!$C$49</f>
+        <f>Loads!$C$50</f>
         <v/>
       </c>
       <c r="E55" s="3">
-        <f>IF(OutOfPlane!$A$55=1,IF(OutOfPlane!$C$55="boom_local",Inputs!$G$62,Inputs!$J$62)+0,0)</f>
+        <f>IF(OutOfPlane!$A$55=1,IF(OutOfPlane!$C$55="boom_local",Inputs!$G$63,Inputs!$J$63)+0,0)</f>
         <v/>
       </c>
       <c r="F55" s="3">
-        <f>Loads!$D$49</f>
+        <f>Loads!$D$50</f>
         <v/>
       </c>
       <c r="G55" s="3">
-        <f>Loads!$E$49</f>
+        <f>Loads!$E$50</f>
         <v/>
       </c>
       <c r="H55" s="3">
-        <f>Loads!$L$49</f>
+        <f>Loads!$L$50</f>
         <v/>
       </c>
       <c r="I55" s="3">
-        <f>Loads!$M$49</f>
+        <f>Loads!$M$50</f>
         <v/>
       </c>
       <c r="J55" s="3">
@@ -37864,39 +37878,39 @@
     </row>
     <row r="56">
       <c r="A56" s="3">
-        <f>Inputs!$A$63</f>
+        <f>Inputs!$A$64</f>
         <v/>
       </c>
       <c r="B56" s="3">
-        <f>Loads!$B$50</f>
+        <f>Loads!$B$51</f>
         <v/>
       </c>
       <c r="C56" s="3">
-        <f>IF(OutOfPlane!$A$56=1,Inputs!$D$63&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$56=1,Inputs!$D$64&amp;"","")</f>
         <v/>
       </c>
       <c r="D56" s="3">
-        <f>Loads!$C$50</f>
+        <f>Loads!$C$51</f>
         <v/>
       </c>
       <c r="E56" s="3">
-        <f>IF(OutOfPlane!$A$56=1,IF(OutOfPlane!$C$56="boom_local",Inputs!$G$63,Inputs!$J$63)+0,0)</f>
+        <f>IF(OutOfPlane!$A$56=1,IF(OutOfPlane!$C$56="boom_local",Inputs!$G$64,Inputs!$J$64)+0,0)</f>
         <v/>
       </c>
       <c r="F56" s="3">
-        <f>Loads!$D$50</f>
+        <f>Loads!$D$51</f>
         <v/>
       </c>
       <c r="G56" s="3">
-        <f>Loads!$E$50</f>
+        <f>Loads!$E$51</f>
         <v/>
       </c>
       <c r="H56" s="3">
-        <f>Loads!$L$50</f>
+        <f>Loads!$L$51</f>
         <v/>
       </c>
       <c r="I56" s="3">
-        <f>Loads!$M$50</f>
+        <f>Loads!$M$51</f>
         <v/>
       </c>
       <c r="J56" s="3">
@@ -37906,39 +37920,39 @@
     </row>
     <row r="57">
       <c r="A57" s="3">
-        <f>Inputs!$A$64</f>
+        <f>Inputs!$A$65</f>
         <v/>
       </c>
       <c r="B57" s="3">
-        <f>Loads!$B$51</f>
+        <f>Loads!$B$52</f>
         <v/>
       </c>
       <c r="C57" s="3">
-        <f>IF(OutOfPlane!$A$57=1,Inputs!$D$64&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$57=1,Inputs!$D$65&amp;"","")</f>
         <v/>
       </c>
       <c r="D57" s="3">
-        <f>Loads!$C$51</f>
+        <f>Loads!$C$52</f>
         <v/>
       </c>
       <c r="E57" s="3">
-        <f>IF(OutOfPlane!$A$57=1,IF(OutOfPlane!$C$57="boom_local",Inputs!$G$64,Inputs!$J$64)+0,0)</f>
+        <f>IF(OutOfPlane!$A$57=1,IF(OutOfPlane!$C$57="boom_local",Inputs!$G$65,Inputs!$J$65)+0,0)</f>
         <v/>
       </c>
       <c r="F57" s="3">
-        <f>Loads!$D$51</f>
+        <f>Loads!$D$52</f>
         <v/>
       </c>
       <c r="G57" s="3">
-        <f>Loads!$E$51</f>
+        <f>Loads!$E$52</f>
         <v/>
       </c>
       <c r="H57" s="3">
-        <f>Loads!$L$51</f>
+        <f>Loads!$L$52</f>
         <v/>
       </c>
       <c r="I57" s="3">
-        <f>Loads!$M$51</f>
+        <f>Loads!$M$52</f>
         <v/>
       </c>
       <c r="J57" s="3">
@@ -37948,39 +37962,39 @@
     </row>
     <row r="58">
       <c r="A58" s="3">
-        <f>Inputs!$A$65</f>
+        <f>Inputs!$A$66</f>
         <v/>
       </c>
       <c r="B58" s="3">
-        <f>Loads!$B$52</f>
+        <f>Loads!$B$53</f>
         <v/>
       </c>
       <c r="C58" s="3">
-        <f>IF(OutOfPlane!$A$58=1,Inputs!$D$65&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$58=1,Inputs!$D$66&amp;"","")</f>
         <v/>
       </c>
       <c r="D58" s="3">
-        <f>Loads!$C$52</f>
+        <f>Loads!$C$53</f>
         <v/>
       </c>
       <c r="E58" s="3">
-        <f>IF(OutOfPlane!$A$58=1,IF(OutOfPlane!$C$58="boom_local",Inputs!$G$65,Inputs!$J$65)+0,0)</f>
+        <f>IF(OutOfPlane!$A$58=1,IF(OutOfPlane!$C$58="boom_local",Inputs!$G$66,Inputs!$J$66)+0,0)</f>
         <v/>
       </c>
       <c r="F58" s="3">
-        <f>Loads!$D$52</f>
+        <f>Loads!$D$53</f>
         <v/>
       </c>
       <c r="G58" s="3">
-        <f>Loads!$E$52</f>
+        <f>Loads!$E$53</f>
         <v/>
       </c>
       <c r="H58" s="3">
-        <f>Loads!$L$52</f>
+        <f>Loads!$L$53</f>
         <v/>
       </c>
       <c r="I58" s="3">
-        <f>Loads!$M$52</f>
+        <f>Loads!$M$53</f>
         <v/>
       </c>
       <c r="J58" s="3">
@@ -37990,39 +38004,39 @@
     </row>
     <row r="59">
       <c r="A59" s="3">
-        <f>Inputs!$A$66</f>
+        <f>Inputs!$A$67</f>
         <v/>
       </c>
       <c r="B59" s="3">
-        <f>Loads!$B$53</f>
+        <f>Loads!$B$54</f>
         <v/>
       </c>
       <c r="C59" s="3">
-        <f>IF(OutOfPlane!$A$59=1,Inputs!$D$66&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$59=1,Inputs!$D$67&amp;"","")</f>
         <v/>
       </c>
       <c r="D59" s="3">
-        <f>Loads!$C$53</f>
+        <f>Loads!$C$54</f>
         <v/>
       </c>
       <c r="E59" s="3">
-        <f>IF(OutOfPlane!$A$59=1,IF(OutOfPlane!$C$59="boom_local",Inputs!$G$66,Inputs!$J$66)+0,0)</f>
+        <f>IF(OutOfPlane!$A$59=1,IF(OutOfPlane!$C$59="boom_local",Inputs!$G$67,Inputs!$J$67)+0,0)</f>
         <v/>
       </c>
       <c r="F59" s="3">
-        <f>Loads!$D$53</f>
+        <f>Loads!$D$54</f>
         <v/>
       </c>
       <c r="G59" s="3">
-        <f>Loads!$E$53</f>
+        <f>Loads!$E$54</f>
         <v/>
       </c>
       <c r="H59" s="3">
-        <f>Loads!$L$53</f>
+        <f>Loads!$L$54</f>
         <v/>
       </c>
       <c r="I59" s="3">
-        <f>Loads!$M$53</f>
+        <f>Loads!$M$54</f>
         <v/>
       </c>
       <c r="J59" s="3">
@@ -38032,39 +38046,39 @@
     </row>
     <row r="60">
       <c r="A60" s="3">
-        <f>Inputs!$A$67</f>
+        <f>Inputs!$A$68</f>
         <v/>
       </c>
       <c r="B60" s="3">
-        <f>Loads!$B$54</f>
+        <f>Loads!$B$55</f>
         <v/>
       </c>
       <c r="C60" s="3">
-        <f>IF(OutOfPlane!$A$60=1,Inputs!$D$67&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$60=1,Inputs!$D$68&amp;"","")</f>
         <v/>
       </c>
       <c r="D60" s="3">
-        <f>Loads!$C$54</f>
+        <f>Loads!$C$55</f>
         <v/>
       </c>
       <c r="E60" s="3">
-        <f>IF(OutOfPlane!$A$60=1,IF(OutOfPlane!$C$60="boom_local",Inputs!$G$67,Inputs!$J$67)+0,0)</f>
+        <f>IF(OutOfPlane!$A$60=1,IF(OutOfPlane!$C$60="boom_local",Inputs!$G$68,Inputs!$J$68)+0,0)</f>
         <v/>
       </c>
       <c r="F60" s="3">
-        <f>Loads!$D$54</f>
+        <f>Loads!$D$55</f>
         <v/>
       </c>
       <c r="G60" s="3">
-        <f>Loads!$E$54</f>
+        <f>Loads!$E$55</f>
         <v/>
       </c>
       <c r="H60" s="3">
-        <f>Loads!$L$54</f>
+        <f>Loads!$L$55</f>
         <v/>
       </c>
       <c r="I60" s="3">
-        <f>Loads!$M$54</f>
+        <f>Loads!$M$55</f>
         <v/>
       </c>
       <c r="J60" s="3">
@@ -38074,39 +38088,39 @@
     </row>
     <row r="61">
       <c r="A61" s="3">
-        <f>Inputs!$A$68</f>
+        <f>Inputs!$A$69</f>
         <v/>
       </c>
       <c r="B61" s="3">
-        <f>Loads!$B$55</f>
+        <f>Loads!$B$56</f>
         <v/>
       </c>
       <c r="C61" s="3">
-        <f>IF(OutOfPlane!$A$61=1,Inputs!$D$68&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$61=1,Inputs!$D$69&amp;"","")</f>
         <v/>
       </c>
       <c r="D61" s="3">
-        <f>Loads!$C$55</f>
+        <f>Loads!$C$56</f>
         <v/>
       </c>
       <c r="E61" s="3">
-        <f>IF(OutOfPlane!$A$61=1,IF(OutOfPlane!$C$61="boom_local",Inputs!$G$68,Inputs!$J$68)+0,0)</f>
+        <f>IF(OutOfPlane!$A$61=1,IF(OutOfPlane!$C$61="boom_local",Inputs!$G$69,Inputs!$J$69)+0,0)</f>
         <v/>
       </c>
       <c r="F61" s="3">
-        <f>Loads!$D$55</f>
+        <f>Loads!$D$56</f>
         <v/>
       </c>
       <c r="G61" s="3">
-        <f>Loads!$E$55</f>
+        <f>Loads!$E$56</f>
         <v/>
       </c>
       <c r="H61" s="3">
-        <f>Loads!$L$55</f>
+        <f>Loads!$L$56</f>
         <v/>
       </c>
       <c r="I61" s="3">
-        <f>Loads!$M$55</f>
+        <f>Loads!$M$56</f>
         <v/>
       </c>
       <c r="J61" s="3">
@@ -38116,39 +38130,39 @@
     </row>
     <row r="62">
       <c r="A62" s="3">
-        <f>Inputs!$A$69</f>
+        <f>Inputs!$A$70</f>
         <v/>
       </c>
       <c r="B62" s="3">
-        <f>Loads!$B$56</f>
+        <f>Loads!$B$57</f>
         <v/>
       </c>
       <c r="C62" s="3">
-        <f>IF(OutOfPlane!$A$62=1,Inputs!$D$69&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$62=1,Inputs!$D$70&amp;"","")</f>
         <v/>
       </c>
       <c r="D62" s="3">
-        <f>Loads!$C$56</f>
+        <f>Loads!$C$57</f>
         <v/>
       </c>
       <c r="E62" s="3">
-        <f>IF(OutOfPlane!$A$62=1,IF(OutOfPlane!$C$62="boom_local",Inputs!$G$69,Inputs!$J$69)+0,0)</f>
+        <f>IF(OutOfPlane!$A$62=1,IF(OutOfPlane!$C$62="boom_local",Inputs!$G$70,Inputs!$J$70)+0,0)</f>
         <v/>
       </c>
       <c r="F62" s="3">
-        <f>Loads!$D$56</f>
+        <f>Loads!$D$57</f>
         <v/>
       </c>
       <c r="G62" s="3">
-        <f>Loads!$E$56</f>
+        <f>Loads!$E$57</f>
         <v/>
       </c>
       <c r="H62" s="3">
-        <f>Loads!$L$56</f>
+        <f>Loads!$L$57</f>
         <v/>
       </c>
       <c r="I62" s="3">
-        <f>Loads!$M$56</f>
+        <f>Loads!$M$57</f>
         <v/>
       </c>
       <c r="J62" s="3">
@@ -38158,39 +38172,39 @@
     </row>
     <row r="63">
       <c r="A63" s="3">
-        <f>Inputs!$A$70</f>
+        <f>Inputs!$A$71</f>
         <v/>
       </c>
       <c r="B63" s="3">
-        <f>Loads!$B$57</f>
+        <f>Loads!$B$58</f>
         <v/>
       </c>
       <c r="C63" s="3">
-        <f>IF(OutOfPlane!$A$63=1,Inputs!$D$70&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$63=1,Inputs!$D$71&amp;"","")</f>
         <v/>
       </c>
       <c r="D63" s="3">
-        <f>Loads!$C$57</f>
+        <f>Loads!$C$58</f>
         <v/>
       </c>
       <c r="E63" s="3">
-        <f>IF(OutOfPlane!$A$63=1,IF(OutOfPlane!$C$63="boom_local",Inputs!$G$70,Inputs!$J$70)+0,0)</f>
+        <f>IF(OutOfPlane!$A$63=1,IF(OutOfPlane!$C$63="boom_local",Inputs!$G$71,Inputs!$J$71)+0,0)</f>
         <v/>
       </c>
       <c r="F63" s="3">
-        <f>Loads!$D$57</f>
+        <f>Loads!$D$58</f>
         <v/>
       </c>
       <c r="G63" s="3">
-        <f>Loads!$E$57</f>
+        <f>Loads!$E$58</f>
         <v/>
       </c>
       <c r="H63" s="3">
-        <f>Loads!$L$57</f>
+        <f>Loads!$L$58</f>
         <v/>
       </c>
       <c r="I63" s="3">
-        <f>Loads!$M$57</f>
+        <f>Loads!$M$58</f>
         <v/>
       </c>
       <c r="J63" s="3">
@@ -38200,39 +38214,39 @@
     </row>
     <row r="64">
       <c r="A64" s="3">
-        <f>Inputs!$A$71</f>
+        <f>Inputs!$A$72</f>
         <v/>
       </c>
       <c r="B64" s="3">
-        <f>Loads!$B$58</f>
+        <f>Loads!$B$59</f>
         <v/>
       </c>
       <c r="C64" s="3">
-        <f>IF(OutOfPlane!$A$64=1,Inputs!$D$71&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$64=1,Inputs!$D$72&amp;"","")</f>
         <v/>
       </c>
       <c r="D64" s="3">
-        <f>Loads!$C$58</f>
+        <f>Loads!$C$59</f>
         <v/>
       </c>
       <c r="E64" s="3">
-        <f>IF(OutOfPlane!$A$64=1,IF(OutOfPlane!$C$64="boom_local",Inputs!$G$71,Inputs!$J$71)+0,0)</f>
+        <f>IF(OutOfPlane!$A$64=1,IF(OutOfPlane!$C$64="boom_local",Inputs!$G$72,Inputs!$J$72)+0,0)</f>
         <v/>
       </c>
       <c r="F64" s="3">
-        <f>Loads!$D$58</f>
+        <f>Loads!$D$59</f>
         <v/>
       </c>
       <c r="G64" s="3">
-        <f>Loads!$E$58</f>
+        <f>Loads!$E$59</f>
         <v/>
       </c>
       <c r="H64" s="3">
-        <f>Loads!$L$58</f>
+        <f>Loads!$L$59</f>
         <v/>
       </c>
       <c r="I64" s="3">
-        <f>Loads!$M$58</f>
+        <f>Loads!$M$59</f>
         <v/>
       </c>
       <c r="J64" s="3">
@@ -38242,39 +38256,39 @@
     </row>
     <row r="65">
       <c r="A65" s="3">
-        <f>Inputs!$A$72</f>
+        <f>Inputs!$A$73</f>
         <v/>
       </c>
       <c r="B65" s="3">
-        <f>Loads!$B$59</f>
+        <f>Loads!$B$60</f>
         <v/>
       </c>
       <c r="C65" s="3">
-        <f>IF(OutOfPlane!$A$65=1,Inputs!$D$72&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$65=1,Inputs!$D$73&amp;"","")</f>
         <v/>
       </c>
       <c r="D65" s="3">
-        <f>Loads!$C$59</f>
+        <f>Loads!$C$60</f>
         <v/>
       </c>
       <c r="E65" s="3">
-        <f>IF(OutOfPlane!$A$65=1,IF(OutOfPlane!$C$65="boom_local",Inputs!$G$72,Inputs!$J$72)+0,0)</f>
+        <f>IF(OutOfPlane!$A$65=1,IF(OutOfPlane!$C$65="boom_local",Inputs!$G$73,Inputs!$J$73)+0,0)</f>
         <v/>
       </c>
       <c r="F65" s="3">
-        <f>Loads!$D$59</f>
+        <f>Loads!$D$60</f>
         <v/>
       </c>
       <c r="G65" s="3">
-        <f>Loads!$E$59</f>
+        <f>Loads!$E$60</f>
         <v/>
       </c>
       <c r="H65" s="3">
-        <f>Loads!$L$59</f>
+        <f>Loads!$L$60</f>
         <v/>
       </c>
       <c r="I65" s="3">
-        <f>Loads!$M$59</f>
+        <f>Loads!$M$60</f>
         <v/>
       </c>
       <c r="J65" s="3">
@@ -38284,39 +38298,39 @@
     </row>
     <row r="66">
       <c r="A66" s="3">
-        <f>Inputs!$A$73</f>
+        <f>Inputs!$A$74</f>
         <v/>
       </c>
       <c r="B66" s="3">
-        <f>Loads!$B$60</f>
+        <f>Loads!$B$61</f>
         <v/>
       </c>
       <c r="C66" s="3">
-        <f>IF(OutOfPlane!$A$66=1,Inputs!$D$73&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$66=1,Inputs!$D$74&amp;"","")</f>
         <v/>
       </c>
       <c r="D66" s="3">
-        <f>Loads!$C$60</f>
+        <f>Loads!$C$61</f>
         <v/>
       </c>
       <c r="E66" s="3">
-        <f>IF(OutOfPlane!$A$66=1,IF(OutOfPlane!$C$66="boom_local",Inputs!$G$73,Inputs!$J$73)+0,0)</f>
+        <f>IF(OutOfPlane!$A$66=1,IF(OutOfPlane!$C$66="boom_local",Inputs!$G$74,Inputs!$J$74)+0,0)</f>
         <v/>
       </c>
       <c r="F66" s="3">
-        <f>Loads!$D$60</f>
+        <f>Loads!$D$61</f>
         <v/>
       </c>
       <c r="G66" s="3">
-        <f>Loads!$E$60</f>
+        <f>Loads!$E$61</f>
         <v/>
       </c>
       <c r="H66" s="3">
-        <f>Loads!$L$60</f>
+        <f>Loads!$L$61</f>
         <v/>
       </c>
       <c r="I66" s="3">
-        <f>Loads!$M$60</f>
+        <f>Loads!$M$61</f>
         <v/>
       </c>
       <c r="J66" s="3">
@@ -38326,39 +38340,39 @@
     </row>
     <row r="67">
       <c r="A67" s="3">
-        <f>Inputs!$A$74</f>
+        <f>Inputs!$A$75</f>
         <v/>
       </c>
       <c r="B67" s="3">
-        <f>Loads!$B$61</f>
+        <f>Loads!$B$62</f>
         <v/>
       </c>
       <c r="C67" s="3">
-        <f>IF(OutOfPlane!$A$67=1,Inputs!$D$74&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$67=1,Inputs!$D$75&amp;"","")</f>
         <v/>
       </c>
       <c r="D67" s="3">
-        <f>Loads!$C$61</f>
+        <f>Loads!$C$62</f>
         <v/>
       </c>
       <c r="E67" s="3">
-        <f>IF(OutOfPlane!$A$67=1,IF(OutOfPlane!$C$67="boom_local",Inputs!$G$74,Inputs!$J$74)+0,0)</f>
+        <f>IF(OutOfPlane!$A$67=1,IF(OutOfPlane!$C$67="boom_local",Inputs!$G$75,Inputs!$J$75)+0,0)</f>
         <v/>
       </c>
       <c r="F67" s="3">
-        <f>Loads!$D$61</f>
+        <f>Loads!$D$62</f>
         <v/>
       </c>
       <c r="G67" s="3">
-        <f>Loads!$E$61</f>
+        <f>Loads!$E$62</f>
         <v/>
       </c>
       <c r="H67" s="3">
-        <f>Loads!$L$61</f>
+        <f>Loads!$L$62</f>
         <v/>
       </c>
       <c r="I67" s="3">
-        <f>Loads!$M$61</f>
+        <f>Loads!$M$62</f>
         <v/>
       </c>
       <c r="J67" s="3">
@@ -38368,39 +38382,39 @@
     </row>
     <row r="68">
       <c r="A68" s="3">
-        <f>Inputs!$A$75</f>
+        <f>Inputs!$A$76</f>
         <v/>
       </c>
       <c r="B68" s="3">
-        <f>Loads!$B$62</f>
+        <f>Loads!$B$63</f>
         <v/>
       </c>
       <c r="C68" s="3">
-        <f>IF(OutOfPlane!$A$68=1,Inputs!$D$75&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$68=1,Inputs!$D$76&amp;"","")</f>
         <v/>
       </c>
       <c r="D68" s="3">
-        <f>Loads!$C$62</f>
+        <f>Loads!$C$63</f>
         <v/>
       </c>
       <c r="E68" s="3">
-        <f>IF(OutOfPlane!$A$68=1,IF(OutOfPlane!$C$68="boom_local",Inputs!$G$75,Inputs!$J$75)+0,0)</f>
+        <f>IF(OutOfPlane!$A$68=1,IF(OutOfPlane!$C$68="boom_local",Inputs!$G$76,Inputs!$J$76)+0,0)</f>
         <v/>
       </c>
       <c r="F68" s="3">
-        <f>Loads!$D$62</f>
+        <f>Loads!$D$63</f>
         <v/>
       </c>
       <c r="G68" s="3">
-        <f>Loads!$E$62</f>
+        <f>Loads!$E$63</f>
         <v/>
       </c>
       <c r="H68" s="3">
-        <f>Loads!$L$62</f>
+        <f>Loads!$L$63</f>
         <v/>
       </c>
       <c r="I68" s="3">
-        <f>Loads!$M$62</f>
+        <f>Loads!$M$63</f>
         <v/>
       </c>
       <c r="J68" s="3">
@@ -38410,39 +38424,39 @@
     </row>
     <row r="69">
       <c r="A69" s="3">
-        <f>Inputs!$A$76</f>
+        <f>Inputs!$A$77</f>
         <v/>
       </c>
       <c r="B69" s="3">
-        <f>Loads!$B$63</f>
+        <f>Loads!$B$64</f>
         <v/>
       </c>
       <c r="C69" s="3">
-        <f>IF(OutOfPlane!$A$69=1,Inputs!$D$76&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$69=1,Inputs!$D$77&amp;"","")</f>
         <v/>
       </c>
       <c r="D69" s="3">
-        <f>Loads!$C$63</f>
+        <f>Loads!$C$64</f>
         <v/>
       </c>
       <c r="E69" s="3">
-        <f>IF(OutOfPlane!$A$69=1,IF(OutOfPlane!$C$69="boom_local",Inputs!$G$76,Inputs!$J$76)+0,0)</f>
+        <f>IF(OutOfPlane!$A$69=1,IF(OutOfPlane!$C$69="boom_local",Inputs!$G$77,Inputs!$J$77)+0,0)</f>
         <v/>
       </c>
       <c r="F69" s="3">
-        <f>Loads!$D$63</f>
+        <f>Loads!$D$64</f>
         <v/>
       </c>
       <c r="G69" s="3">
-        <f>Loads!$E$63</f>
+        <f>Loads!$E$64</f>
         <v/>
       </c>
       <c r="H69" s="3">
-        <f>Loads!$L$63</f>
+        <f>Loads!$L$64</f>
         <v/>
       </c>
       <c r="I69" s="3">
-        <f>Loads!$M$63</f>
+        <f>Loads!$M$64</f>
         <v/>
       </c>
       <c r="J69" s="3">
@@ -38452,39 +38466,39 @@
     </row>
     <row r="70">
       <c r="A70" s="3">
-        <f>Inputs!$A$77</f>
+        <f>Inputs!$A$78</f>
         <v/>
       </c>
       <c r="B70" s="3">
-        <f>Loads!$B$64</f>
+        <f>Loads!$B$65</f>
         <v/>
       </c>
       <c r="C70" s="3">
-        <f>IF(OutOfPlane!$A$70=1,Inputs!$D$77&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$70=1,Inputs!$D$78&amp;"","")</f>
         <v/>
       </c>
       <c r="D70" s="3">
-        <f>Loads!$C$64</f>
+        <f>Loads!$C$65</f>
         <v/>
       </c>
       <c r="E70" s="3">
-        <f>IF(OutOfPlane!$A$70=1,IF(OutOfPlane!$C$70="boom_local",Inputs!$G$77,Inputs!$J$77)+0,0)</f>
+        <f>IF(OutOfPlane!$A$70=1,IF(OutOfPlane!$C$70="boom_local",Inputs!$G$78,Inputs!$J$78)+0,0)</f>
         <v/>
       </c>
       <c r="F70" s="3">
-        <f>Loads!$D$64</f>
+        <f>Loads!$D$65</f>
         <v/>
       </c>
       <c r="G70" s="3">
-        <f>Loads!$E$64</f>
+        <f>Loads!$E$65</f>
         <v/>
       </c>
       <c r="H70" s="3">
-        <f>Loads!$L$64</f>
+        <f>Loads!$L$65</f>
         <v/>
       </c>
       <c r="I70" s="3">
-        <f>Loads!$M$64</f>
+        <f>Loads!$M$65</f>
         <v/>
       </c>
       <c r="J70" s="3">
@@ -38494,39 +38508,39 @@
     </row>
     <row r="71">
       <c r="A71" s="3">
-        <f>Inputs!$A$78</f>
+        <f>Inputs!$A$79</f>
         <v/>
       </c>
       <c r="B71" s="3">
-        <f>Loads!$B$65</f>
+        <f>Loads!$B$66</f>
         <v/>
       </c>
       <c r="C71" s="3">
-        <f>IF(OutOfPlane!$A$71=1,Inputs!$D$78&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$71=1,Inputs!$D$79&amp;"","")</f>
         <v/>
       </c>
       <c r="D71" s="3">
-        <f>Loads!$C$65</f>
+        <f>Loads!$C$66</f>
         <v/>
       </c>
       <c r="E71" s="3">
-        <f>IF(OutOfPlane!$A$71=1,IF(OutOfPlane!$C$71="boom_local",Inputs!$G$78,Inputs!$J$78)+0,0)</f>
+        <f>IF(OutOfPlane!$A$71=1,IF(OutOfPlane!$C$71="boom_local",Inputs!$G$79,Inputs!$J$79)+0,0)</f>
         <v/>
       </c>
       <c r="F71" s="3">
-        <f>Loads!$D$65</f>
+        <f>Loads!$D$66</f>
         <v/>
       </c>
       <c r="G71" s="3">
-        <f>Loads!$E$65</f>
+        <f>Loads!$E$66</f>
         <v/>
       </c>
       <c r="H71" s="3">
-        <f>Loads!$L$65</f>
+        <f>Loads!$L$66</f>
         <v/>
       </c>
       <c r="I71" s="3">
-        <f>Loads!$M$65</f>
+        <f>Loads!$M$66</f>
         <v/>
       </c>
       <c r="J71" s="3">
@@ -38536,39 +38550,39 @@
     </row>
     <row r="72">
       <c r="A72" s="3">
-        <f>Inputs!$A$79</f>
+        <f>Inputs!$A$80</f>
         <v/>
       </c>
       <c r="B72" s="3">
-        <f>Loads!$B$66</f>
+        <f>Loads!$B$67</f>
         <v/>
       </c>
       <c r="C72" s="3">
-        <f>IF(OutOfPlane!$A$72=1,Inputs!$D$79&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$72=1,Inputs!$D$80&amp;"","")</f>
         <v/>
       </c>
       <c r="D72" s="3">
-        <f>Loads!$C$66</f>
+        <f>Loads!$C$67</f>
         <v/>
       </c>
       <c r="E72" s="3">
-        <f>IF(OutOfPlane!$A$72=1,IF(OutOfPlane!$C$72="boom_local",Inputs!$G$79,Inputs!$J$79)+0,0)</f>
+        <f>IF(OutOfPlane!$A$72=1,IF(OutOfPlane!$C$72="boom_local",Inputs!$G$80,Inputs!$J$80)+0,0)</f>
         <v/>
       </c>
       <c r="F72" s="3">
-        <f>Loads!$D$66</f>
+        <f>Loads!$D$67</f>
         <v/>
       </c>
       <c r="G72" s="3">
-        <f>Loads!$E$66</f>
+        <f>Loads!$E$67</f>
         <v/>
       </c>
       <c r="H72" s="3">
-        <f>Loads!$L$66</f>
+        <f>Loads!$L$67</f>
         <v/>
       </c>
       <c r="I72" s="3">
-        <f>Loads!$M$66</f>
+        <f>Loads!$M$67</f>
         <v/>
       </c>
       <c r="J72" s="3">
@@ -38578,39 +38592,39 @@
     </row>
     <row r="73">
       <c r="A73" s="3">
-        <f>Inputs!$A$80</f>
+        <f>Inputs!$A$81</f>
         <v/>
       </c>
       <c r="B73" s="3">
-        <f>Loads!$B$67</f>
+        <f>Loads!$B$68</f>
         <v/>
       </c>
       <c r="C73" s="3">
-        <f>IF(OutOfPlane!$A$73=1,Inputs!$D$80&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$73=1,Inputs!$D$81&amp;"","")</f>
         <v/>
       </c>
       <c r="D73" s="3">
-        <f>Loads!$C$67</f>
+        <f>Loads!$C$68</f>
         <v/>
       </c>
       <c r="E73" s="3">
-        <f>IF(OutOfPlane!$A$73=1,IF(OutOfPlane!$C$73="boom_local",Inputs!$G$80,Inputs!$J$80)+0,0)</f>
+        <f>IF(OutOfPlane!$A$73=1,IF(OutOfPlane!$C$73="boom_local",Inputs!$G$81,Inputs!$J$81)+0,0)</f>
         <v/>
       </c>
       <c r="F73" s="3">
-        <f>Loads!$D$67</f>
+        <f>Loads!$D$68</f>
         <v/>
       </c>
       <c r="G73" s="3">
-        <f>Loads!$E$67</f>
+        <f>Loads!$E$68</f>
         <v/>
       </c>
       <c r="H73" s="3">
-        <f>Loads!$L$67</f>
+        <f>Loads!$L$68</f>
         <v/>
       </c>
       <c r="I73" s="3">
-        <f>Loads!$M$67</f>
+        <f>Loads!$M$68</f>
         <v/>
       </c>
       <c r="J73" s="3">
@@ -38620,39 +38634,39 @@
     </row>
     <row r="74">
       <c r="A74" s="3">
-        <f>Inputs!$A$81</f>
+        <f>Inputs!$A$82</f>
         <v/>
       </c>
       <c r="B74" s="3">
-        <f>Loads!$B$68</f>
+        <f>Loads!$B$69</f>
         <v/>
       </c>
       <c r="C74" s="3">
-        <f>IF(OutOfPlane!$A$74=1,Inputs!$D$81&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$74=1,Inputs!$D$82&amp;"","")</f>
         <v/>
       </c>
       <c r="D74" s="3">
-        <f>Loads!$C$68</f>
+        <f>Loads!$C$69</f>
         <v/>
       </c>
       <c r="E74" s="3">
-        <f>IF(OutOfPlane!$A$74=1,IF(OutOfPlane!$C$74="boom_local",Inputs!$G$81,Inputs!$J$81)+0,0)</f>
+        <f>IF(OutOfPlane!$A$74=1,IF(OutOfPlane!$C$74="boom_local",Inputs!$G$82,Inputs!$J$82)+0,0)</f>
         <v/>
       </c>
       <c r="F74" s="3">
-        <f>Loads!$D$68</f>
+        <f>Loads!$D$69</f>
         <v/>
       </c>
       <c r="G74" s="3">
-        <f>Loads!$E$68</f>
+        <f>Loads!$E$69</f>
         <v/>
       </c>
       <c r="H74" s="3">
-        <f>Loads!$L$68</f>
+        <f>Loads!$L$69</f>
         <v/>
       </c>
       <c r="I74" s="3">
-        <f>Loads!$M$68</f>
+        <f>Loads!$M$69</f>
         <v/>
       </c>
       <c r="J74" s="3">
@@ -38662,39 +38676,39 @@
     </row>
     <row r="75">
       <c r="A75" s="3">
-        <f>Inputs!$A$82</f>
+        <f>Inputs!$A$83</f>
         <v/>
       </c>
       <c r="B75" s="3">
-        <f>Loads!$B$69</f>
+        <f>Loads!$B$70</f>
         <v/>
       </c>
       <c r="C75" s="3">
-        <f>IF(OutOfPlane!$A$75=1,Inputs!$D$82&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$75=1,Inputs!$D$83&amp;"","")</f>
         <v/>
       </c>
       <c r="D75" s="3">
-        <f>Loads!$C$69</f>
+        <f>Loads!$C$70</f>
         <v/>
       </c>
       <c r="E75" s="3">
-        <f>IF(OutOfPlane!$A$75=1,IF(OutOfPlane!$C$75="boom_local",Inputs!$G$82,Inputs!$J$82)+0,0)</f>
+        <f>IF(OutOfPlane!$A$75=1,IF(OutOfPlane!$C$75="boom_local",Inputs!$G$83,Inputs!$J$83)+0,0)</f>
         <v/>
       </c>
       <c r="F75" s="3">
-        <f>Loads!$D$69</f>
+        <f>Loads!$D$70</f>
         <v/>
       </c>
       <c r="G75" s="3">
-        <f>Loads!$E$69</f>
+        <f>Loads!$E$70</f>
         <v/>
       </c>
       <c r="H75" s="3">
-        <f>Loads!$L$69</f>
+        <f>Loads!$L$70</f>
         <v/>
       </c>
       <c r="I75" s="3">
-        <f>Loads!$M$69</f>
+        <f>Loads!$M$70</f>
         <v/>
       </c>
       <c r="J75" s="3">
@@ -38704,39 +38718,39 @@
     </row>
     <row r="76">
       <c r="A76" s="3">
-        <f>Inputs!$A$83</f>
+        <f>Inputs!$A$84</f>
         <v/>
       </c>
       <c r="B76" s="3">
-        <f>Loads!$B$70</f>
+        <f>Loads!$B$71</f>
         <v/>
       </c>
       <c r="C76" s="3">
-        <f>IF(OutOfPlane!$A$76=1,Inputs!$D$83&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$76=1,Inputs!$D$84&amp;"","")</f>
         <v/>
       </c>
       <c r="D76" s="3">
-        <f>Loads!$C$70</f>
+        <f>Loads!$C$71</f>
         <v/>
       </c>
       <c r="E76" s="3">
-        <f>IF(OutOfPlane!$A$76=1,IF(OutOfPlane!$C$76="boom_local",Inputs!$G$83,Inputs!$J$83)+0,0)</f>
+        <f>IF(OutOfPlane!$A$76=1,IF(OutOfPlane!$C$76="boom_local",Inputs!$G$84,Inputs!$J$84)+0,0)</f>
         <v/>
       </c>
       <c r="F76" s="3">
-        <f>Loads!$D$70</f>
+        <f>Loads!$D$71</f>
         <v/>
       </c>
       <c r="G76" s="3">
-        <f>Loads!$E$70</f>
+        <f>Loads!$E$71</f>
         <v/>
       </c>
       <c r="H76" s="3">
-        <f>Loads!$L$70</f>
+        <f>Loads!$L$71</f>
         <v/>
       </c>
       <c r="I76" s="3">
-        <f>Loads!$M$70</f>
+        <f>Loads!$M$71</f>
         <v/>
       </c>
       <c r="J76" s="3">
@@ -38746,39 +38760,39 @@
     </row>
     <row r="77">
       <c r="A77" s="3">
-        <f>Inputs!$A$84</f>
+        <f>Inputs!$A$85</f>
         <v/>
       </c>
       <c r="B77" s="3">
-        <f>Loads!$B$71</f>
+        <f>Loads!$B$72</f>
         <v/>
       </c>
       <c r="C77" s="3">
-        <f>IF(OutOfPlane!$A$77=1,Inputs!$D$84&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$77=1,Inputs!$D$85&amp;"","")</f>
         <v/>
       </c>
       <c r="D77" s="3">
-        <f>Loads!$C$71</f>
+        <f>Loads!$C$72</f>
         <v/>
       </c>
       <c r="E77" s="3">
-        <f>IF(OutOfPlane!$A$77=1,IF(OutOfPlane!$C$77="boom_local",Inputs!$G$84,Inputs!$J$84)+0,0)</f>
+        <f>IF(OutOfPlane!$A$77=1,IF(OutOfPlane!$C$77="boom_local",Inputs!$G$85,Inputs!$J$85)+0,0)</f>
         <v/>
       </c>
       <c r="F77" s="3">
-        <f>Loads!$D$71</f>
+        <f>Loads!$D$72</f>
         <v/>
       </c>
       <c r="G77" s="3">
-        <f>Loads!$E$71</f>
+        <f>Loads!$E$72</f>
         <v/>
       </c>
       <c r="H77" s="3">
-        <f>Loads!$L$71</f>
+        <f>Loads!$L$72</f>
         <v/>
       </c>
       <c r="I77" s="3">
-        <f>Loads!$M$71</f>
+        <f>Loads!$M$72</f>
         <v/>
       </c>
       <c r="J77" s="3">
@@ -38786,162 +38800,154 @@
         <v/>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="3">
-        <f>Inputs!$A$85</f>
-        <v/>
-      </c>
-      <c r="B78" s="3">
-        <f>Loads!$B$72</f>
-        <v/>
-      </c>
-      <c r="C78" s="3">
-        <f>IF(OutOfPlane!$A$78=1,Inputs!$D$85&amp;"","")</f>
-        <v/>
-      </c>
-      <c r="D78" s="3">
-        <f>Loads!$C$72</f>
-        <v/>
-      </c>
-      <c r="E78" s="3">
-        <f>IF(OutOfPlane!$A$78=1,IF(OutOfPlane!$C$78="boom_local",Inputs!$G$85,Inputs!$J$85)+0,0)</f>
-        <v/>
-      </c>
-      <c r="F78" s="3">
-        <f>Loads!$D$72</f>
-        <v/>
-      </c>
-      <c r="G78" s="3">
-        <f>Loads!$E$72</f>
-        <v/>
-      </c>
-      <c r="H78" s="3">
-        <f>Loads!$L$72</f>
-        <v/>
-      </c>
-      <c r="I78" s="3">
-        <f>Loads!$M$72</f>
-        <v/>
-      </c>
-      <c r="J78" s="3">
-        <f>-OutOfPlane!$G$78*(OutOfPlane!$B$13-OutOfPlane!$B$14*(OutOfPlane!$F$78-OutOfPlane!$B$12))</f>
-        <v/>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>Lumped masses at nodes (row i = Inputs nodes row i)</t>
+        </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>Lumped masses at nodes (row i = Inputs nodes row i)</t>
+      <c r="A82" s="8" t="inlineStr">
+        <is>
+          <t>Active [1/0]</t>
+        </is>
+      </c>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t>Node id</t>
+        </is>
+      </c>
+      <c r="C82" s="8" t="inlineStr">
+        <is>
+          <t>x global [m]</t>
+        </is>
+      </c>
+      <c r="D82" s="8" t="inlineStr">
+        <is>
+          <t>z global [m]</t>
+        </is>
+      </c>
+      <c r="E82" s="8" t="inlineStr">
+        <is>
+          <t>Rope self-weight at node [t]</t>
+        </is>
+      </c>
+      <c r="F82" s="8" t="inlineStr">
+        <is>
+          <t>Idle hook block mass [t]</t>
+        </is>
+      </c>
+      <c r="G82" s="8" t="inlineStr">
+        <is>
+          <t>Lumped mass [t]</t>
+        </is>
+      </c>
+      <c r="H82" s="8" t="inlineStr">
+        <is>
+          <t>Fy = -m (ay' - roll' (z - z_ref)) [kN]</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="8" t="inlineStr">
-        <is>
-          <t>Active [1/0]</t>
-        </is>
-      </c>
-      <c r="B83" s="8" t="inlineStr">
-        <is>
-          <t>Node id</t>
-        </is>
-      </c>
-      <c r="C83" s="8" t="inlineStr">
-        <is>
-          <t>x global [m]</t>
-        </is>
-      </c>
-      <c r="D83" s="8" t="inlineStr">
-        <is>
-          <t>z global [m]</t>
-        </is>
-      </c>
-      <c r="E83" s="8" t="inlineStr">
-        <is>
-          <t>Rope self-weight at node [t]</t>
-        </is>
-      </c>
-      <c r="F83" s="8" t="inlineStr">
-        <is>
-          <t>Idle hook block mass [t]</t>
-        </is>
-      </c>
-      <c r="G83" s="8" t="inlineStr">
-        <is>
-          <t>Lumped mass [t]</t>
-        </is>
-      </c>
-      <c r="H83" s="8" t="inlineStr">
-        <is>
-          <t>Fy = -m (ay' - roll' (z - z_ref)) [kN]</t>
+      <c r="A83" s="7" t="inlineStr">
+        <is>
+          <t>active (from Inputs)</t>
+        </is>
+      </c>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t>x_m (Loads (with the tackle))</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>z_m</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>rope_t (Loads rope_mass_t)</t>
+        </is>
+      </c>
+      <c r="F83" s="7" t="inlineStr">
+        <is>
+          <t>idle_t (Loads idle_mass_t)</t>
+        </is>
+      </c>
+      <c r="G83" s="7" t="inlineStr">
+        <is>
+          <t>mass_t</t>
+        </is>
+      </c>
+      <c r="H83" s="7" t="inlineStr">
+        <is>
+          <t>fy_kN</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="7" t="inlineStr">
-        <is>
-          <t>active (from Inputs)</t>
-        </is>
-      </c>
-      <c r="B84" s="7" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C84" s="7" t="inlineStr">
-        <is>
-          <t>x_m (Loads (with the tackle))</t>
-        </is>
-      </c>
-      <c r="D84" s="7" t="inlineStr">
-        <is>
-          <t>z_m</t>
-        </is>
-      </c>
-      <c r="E84" s="7" t="inlineStr">
-        <is>
-          <t>rope_t (Loads rope_mass_t)</t>
-        </is>
-      </c>
-      <c r="F84" s="7" t="inlineStr">
-        <is>
-          <t>idle_t (Loads idle_mass_t)</t>
-        </is>
-      </c>
-      <c r="G84" s="7" t="inlineStr">
-        <is>
-          <t>mass_t</t>
-        </is>
-      </c>
-      <c r="H84" s="7" t="inlineStr">
-        <is>
-          <t>fy_kN</t>
-        </is>
+      <c r="A84" s="3">
+        <f>Inputs!$A$138</f>
+        <v/>
+      </c>
+      <c r="B84" s="3">
+        <f>Loads!$B$219</f>
+        <v/>
+      </c>
+      <c r="C84" s="3">
+        <f>Loads!$D$219</f>
+        <v/>
+      </c>
+      <c r="D84" s="3">
+        <f>Loads!$E$219</f>
+        <v/>
+      </c>
+      <c r="E84" s="3">
+        <f>Loads!$H$219</f>
+        <v/>
+      </c>
+      <c r="F84" s="3">
+        <f>Loads!$L$219</f>
+        <v/>
+      </c>
+      <c r="G84" s="3">
+        <f>OutOfPlane!$E$84+OutOfPlane!$F$84</f>
+        <v/>
+      </c>
+      <c r="H84" s="3">
+        <f>-OutOfPlane!$G$84*(OutOfPlane!$B$13-OutOfPlane!$B$14*(OutOfPlane!$D$84-OutOfPlane!$B$12))</f>
+        <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3">
-        <f>Inputs!$A$138</f>
+        <f>Inputs!$A$139</f>
         <v/>
       </c>
       <c r="B85" s="3">
-        <f>Loads!$B$219</f>
+        <f>Loads!$B$220</f>
         <v/>
       </c>
       <c r="C85" s="3">
-        <f>Loads!$D$219</f>
+        <f>Loads!$D$220</f>
         <v/>
       </c>
       <c r="D85" s="3">
-        <f>Loads!$E$219</f>
+        <f>Loads!$E$220</f>
         <v/>
       </c>
       <c r="E85" s="3">
-        <f>Loads!$H$219</f>
+        <f>Loads!$H$220</f>
         <v/>
       </c>
       <c r="F85" s="3">
-        <f>Loads!$L$219</f>
+        <f>Loads!$L$220</f>
         <v/>
       </c>
       <c r="G85" s="3">
@@ -38955,27 +38961,27 @@
     </row>
     <row r="86">
       <c r="A86" s="3">
-        <f>Inputs!$A$139</f>
+        <f>Inputs!$A$140</f>
         <v/>
       </c>
       <c r="B86" s="3">
-        <f>Loads!$B$220</f>
+        <f>Loads!$B$221</f>
         <v/>
       </c>
       <c r="C86" s="3">
-        <f>Loads!$D$220</f>
+        <f>Loads!$D$221</f>
         <v/>
       </c>
       <c r="D86" s="3">
-        <f>Loads!$E$220</f>
+        <f>Loads!$E$221</f>
         <v/>
       </c>
       <c r="E86" s="3">
-        <f>Loads!$H$220</f>
+        <f>Loads!$H$221</f>
         <v/>
       </c>
       <c r="F86" s="3">
-        <f>Loads!$L$220</f>
+        <f>Loads!$L$221</f>
         <v/>
       </c>
       <c r="G86" s="3">
@@ -38989,27 +38995,27 @@
     </row>
     <row r="87">
       <c r="A87" s="3">
-        <f>Inputs!$A$140</f>
+        <f>Inputs!$A$141</f>
         <v/>
       </c>
       <c r="B87" s="3">
-        <f>Loads!$B$221</f>
+        <f>Loads!$B$222</f>
         <v/>
       </c>
       <c r="C87" s="3">
-        <f>Loads!$D$221</f>
+        <f>Loads!$D$222</f>
         <v/>
       </c>
       <c r="D87" s="3">
-        <f>Loads!$E$221</f>
+        <f>Loads!$E$222</f>
         <v/>
       </c>
       <c r="E87" s="3">
-        <f>Loads!$H$221</f>
+        <f>Loads!$H$222</f>
         <v/>
       </c>
       <c r="F87" s="3">
-        <f>Loads!$L$221</f>
+        <f>Loads!$L$222</f>
         <v/>
       </c>
       <c r="G87" s="3">
@@ -39023,27 +39029,27 @@
     </row>
     <row r="88">
       <c r="A88" s="3">
-        <f>Inputs!$A$141</f>
+        <f>Inputs!$A$142</f>
         <v/>
       </c>
       <c r="B88" s="3">
-        <f>Loads!$B$222</f>
+        <f>Loads!$B$223</f>
         <v/>
       </c>
       <c r="C88" s="3">
-        <f>Loads!$D$222</f>
+        <f>Loads!$D$223</f>
         <v/>
       </c>
       <c r="D88" s="3">
-        <f>Loads!$E$222</f>
+        <f>Loads!$E$223</f>
         <v/>
       </c>
       <c r="E88" s="3">
-        <f>Loads!$H$222</f>
+        <f>Loads!$H$223</f>
         <v/>
       </c>
       <c r="F88" s="3">
-        <f>Loads!$L$222</f>
+        <f>Loads!$L$223</f>
         <v/>
       </c>
       <c r="G88" s="3">
@@ -39057,27 +39063,27 @@
     </row>
     <row r="89">
       <c r="A89" s="3">
-        <f>Inputs!$A$142</f>
+        <f>Inputs!$A$143</f>
         <v/>
       </c>
       <c r="B89" s="3">
-        <f>Loads!$B$223</f>
+        <f>Loads!$B$224</f>
         <v/>
       </c>
       <c r="C89" s="3">
-        <f>Loads!$D$223</f>
+        <f>Loads!$D$224</f>
         <v/>
       </c>
       <c r="D89" s="3">
-        <f>Loads!$E$223</f>
+        <f>Loads!$E$224</f>
         <v/>
       </c>
       <c r="E89" s="3">
-        <f>Loads!$H$223</f>
+        <f>Loads!$H$224</f>
         <v/>
       </c>
       <c r="F89" s="3">
-        <f>Loads!$L$223</f>
+        <f>Loads!$L$224</f>
         <v/>
       </c>
       <c r="G89" s="3">
@@ -39091,27 +39097,27 @@
     </row>
     <row r="90">
       <c r="A90" s="3">
-        <f>Inputs!$A$143</f>
+        <f>Inputs!$A$144</f>
         <v/>
       </c>
       <c r="B90" s="3">
-        <f>Loads!$B$224</f>
+        <f>Loads!$B$225</f>
         <v/>
       </c>
       <c r="C90" s="3">
-        <f>Loads!$D$224</f>
+        <f>Loads!$D$225</f>
         <v/>
       </c>
       <c r="D90" s="3">
-        <f>Loads!$E$224</f>
+        <f>Loads!$E$225</f>
         <v/>
       </c>
       <c r="E90" s="3">
-        <f>Loads!$H$224</f>
+        <f>Loads!$H$225</f>
         <v/>
       </c>
       <c r="F90" s="3">
-        <f>Loads!$L$224</f>
+        <f>Loads!$L$225</f>
         <v/>
       </c>
       <c r="G90" s="3">
@@ -39125,27 +39131,27 @@
     </row>
     <row r="91">
       <c r="A91" s="3">
-        <f>Inputs!$A$144</f>
+        <f>Inputs!$A$145</f>
         <v/>
       </c>
       <c r="B91" s="3">
-        <f>Loads!$B$225</f>
+        <f>Loads!$B$226</f>
         <v/>
       </c>
       <c r="C91" s="3">
-        <f>Loads!$D$225</f>
+        <f>Loads!$D$226</f>
         <v/>
       </c>
       <c r="D91" s="3">
-        <f>Loads!$E$225</f>
+        <f>Loads!$E$226</f>
         <v/>
       </c>
       <c r="E91" s="3">
-        <f>Loads!$H$225</f>
+        <f>Loads!$H$226</f>
         <v/>
       </c>
       <c r="F91" s="3">
-        <f>Loads!$L$225</f>
+        <f>Loads!$L$226</f>
         <v/>
       </c>
       <c r="G91" s="3">
@@ -39159,27 +39165,27 @@
     </row>
     <row r="92">
       <c r="A92" s="3">
-        <f>Inputs!$A$145</f>
+        <f>Inputs!$A$146</f>
         <v/>
       </c>
       <c r="B92" s="3">
-        <f>Loads!$B$226</f>
+        <f>Loads!$B$227</f>
         <v/>
       </c>
       <c r="C92" s="3">
-        <f>Loads!$D$226</f>
+        <f>Loads!$D$227</f>
         <v/>
       </c>
       <c r="D92" s="3">
-        <f>Loads!$E$226</f>
+        <f>Loads!$E$227</f>
         <v/>
       </c>
       <c r="E92" s="3">
-        <f>Loads!$H$226</f>
+        <f>Loads!$H$227</f>
         <v/>
       </c>
       <c r="F92" s="3">
-        <f>Loads!$L$226</f>
+        <f>Loads!$L$227</f>
         <v/>
       </c>
       <c r="G92" s="3">
@@ -39193,27 +39199,27 @@
     </row>
     <row r="93">
       <c r="A93" s="3">
-        <f>Inputs!$A$146</f>
+        <f>Inputs!$A$147</f>
         <v/>
       </c>
       <c r="B93" s="3">
-        <f>Loads!$B$227</f>
+        <f>Loads!$B$228</f>
         <v/>
       </c>
       <c r="C93" s="3">
-        <f>Loads!$D$227</f>
+        <f>Loads!$D$228</f>
         <v/>
       </c>
       <c r="D93" s="3">
-        <f>Loads!$E$227</f>
+        <f>Loads!$E$228</f>
         <v/>
       </c>
       <c r="E93" s="3">
-        <f>Loads!$H$227</f>
+        <f>Loads!$H$228</f>
         <v/>
       </c>
       <c r="F93" s="3">
-        <f>Loads!$L$227</f>
+        <f>Loads!$L$228</f>
         <v/>
       </c>
       <c r="G93" s="3">
@@ -39227,27 +39233,27 @@
     </row>
     <row r="94">
       <c r="A94" s="3">
-        <f>Inputs!$A$147</f>
+        <f>Inputs!$A$148</f>
         <v/>
       </c>
       <c r="B94" s="3">
-        <f>Loads!$B$228</f>
+        <f>Loads!$B$229</f>
         <v/>
       </c>
       <c r="C94" s="3">
-        <f>Loads!$D$228</f>
+        <f>Loads!$D$229</f>
         <v/>
       </c>
       <c r="D94" s="3">
-        <f>Loads!$E$228</f>
+        <f>Loads!$E$229</f>
         <v/>
       </c>
       <c r="E94" s="3">
-        <f>Loads!$H$228</f>
+        <f>Loads!$H$229</f>
         <v/>
       </c>
       <c r="F94" s="3">
-        <f>Loads!$L$228</f>
+        <f>Loads!$L$229</f>
         <v/>
       </c>
       <c r="G94" s="3">
@@ -39261,27 +39267,27 @@
     </row>
     <row r="95">
       <c r="A95" s="3">
-        <f>Inputs!$A$148</f>
+        <f>Inputs!$A$149</f>
         <v/>
       </c>
       <c r="B95" s="3">
-        <f>Loads!$B$229</f>
+        <f>Loads!$B$230</f>
         <v/>
       </c>
       <c r="C95" s="3">
-        <f>Loads!$D$229</f>
+        <f>Loads!$D$230</f>
         <v/>
       </c>
       <c r="D95" s="3">
-        <f>Loads!$E$229</f>
+        <f>Loads!$E$230</f>
         <v/>
       </c>
       <c r="E95" s="3">
-        <f>Loads!$H$229</f>
+        <f>Loads!$H$230</f>
         <v/>
       </c>
       <c r="F95" s="3">
-        <f>Loads!$L$229</f>
+        <f>Loads!$L$230</f>
         <v/>
       </c>
       <c r="G95" s="3">
@@ -39295,27 +39301,27 @@
     </row>
     <row r="96">
       <c r="A96" s="3">
-        <f>Inputs!$A$149</f>
+        <f>Inputs!$A$150</f>
         <v/>
       </c>
       <c r="B96" s="3">
-        <f>Loads!$B$230</f>
+        <f>Loads!$B$231</f>
         <v/>
       </c>
       <c r="C96" s="3">
-        <f>Loads!$D$230</f>
+        <f>Loads!$D$231</f>
         <v/>
       </c>
       <c r="D96" s="3">
-        <f>Loads!$E$230</f>
+        <f>Loads!$E$231</f>
         <v/>
       </c>
       <c r="E96" s="3">
-        <f>Loads!$H$230</f>
+        <f>Loads!$H$231</f>
         <v/>
       </c>
       <c r="F96" s="3">
-        <f>Loads!$L$230</f>
+        <f>Loads!$L$231</f>
         <v/>
       </c>
       <c r="G96" s="3">
@@ -39329,27 +39335,27 @@
     </row>
     <row r="97">
       <c r="A97" s="3">
-        <f>Inputs!$A$150</f>
+        <f>Inputs!$A$151</f>
         <v/>
       </c>
       <c r="B97" s="3">
-        <f>Loads!$B$231</f>
+        <f>Loads!$B$232</f>
         <v/>
       </c>
       <c r="C97" s="3">
-        <f>Loads!$D$231</f>
+        <f>Loads!$D$232</f>
         <v/>
       </c>
       <c r="D97" s="3">
-        <f>Loads!$E$231</f>
+        <f>Loads!$E$232</f>
         <v/>
       </c>
       <c r="E97" s="3">
-        <f>Loads!$H$231</f>
+        <f>Loads!$H$232</f>
         <v/>
       </c>
       <c r="F97" s="3">
-        <f>Loads!$L$231</f>
+        <f>Loads!$L$232</f>
         <v/>
       </c>
       <c r="G97" s="3">
@@ -39363,27 +39369,27 @@
     </row>
     <row r="98">
       <c r="A98" s="3">
-        <f>Inputs!$A$151</f>
+        <f>Inputs!$A$152</f>
         <v/>
       </c>
       <c r="B98" s="3">
-        <f>Loads!$B$232</f>
+        <f>Loads!$B$233</f>
         <v/>
       </c>
       <c r="C98" s="3">
-        <f>Loads!$D$232</f>
+        <f>Loads!$D$233</f>
         <v/>
       </c>
       <c r="D98" s="3">
-        <f>Loads!$E$232</f>
+        <f>Loads!$E$233</f>
         <v/>
       </c>
       <c r="E98" s="3">
-        <f>Loads!$H$232</f>
+        <f>Loads!$H$233</f>
         <v/>
       </c>
       <c r="F98" s="3">
-        <f>Loads!$L$232</f>
+        <f>Loads!$L$233</f>
         <v/>
       </c>
       <c r="G98" s="3">
@@ -39397,27 +39403,27 @@
     </row>
     <row r="99">
       <c r="A99" s="3">
-        <f>Inputs!$A$152</f>
+        <f>Inputs!$A$153</f>
         <v/>
       </c>
       <c r="B99" s="3">
-        <f>Loads!$B$233</f>
+        <f>Loads!$B$234</f>
         <v/>
       </c>
       <c r="C99" s="3">
-        <f>Loads!$D$233</f>
+        <f>Loads!$D$234</f>
         <v/>
       </c>
       <c r="D99" s="3">
-        <f>Loads!$E$233</f>
+        <f>Loads!$E$234</f>
         <v/>
       </c>
       <c r="E99" s="3">
-        <f>Loads!$H$233</f>
+        <f>Loads!$H$234</f>
         <v/>
       </c>
       <c r="F99" s="3">
-        <f>Loads!$L$233</f>
+        <f>Loads!$L$234</f>
         <v/>
       </c>
       <c r="G99" s="3">
@@ -39431,27 +39437,27 @@
     </row>
     <row r="100">
       <c r="A100" s="3">
-        <f>Inputs!$A$153</f>
+        <f>Inputs!$A$154</f>
         <v/>
       </c>
       <c r="B100" s="3">
-        <f>Loads!$B$234</f>
+        <f>Loads!$B$235</f>
         <v/>
       </c>
       <c r="C100" s="3">
-        <f>Loads!$D$234</f>
+        <f>Loads!$D$235</f>
         <v/>
       </c>
       <c r="D100" s="3">
-        <f>Loads!$E$234</f>
+        <f>Loads!$E$235</f>
         <v/>
       </c>
       <c r="E100" s="3">
-        <f>Loads!$H$234</f>
+        <f>Loads!$H$235</f>
         <v/>
       </c>
       <c r="F100" s="3">
-        <f>Loads!$L$234</f>
+        <f>Loads!$L$235</f>
         <v/>
       </c>
       <c r="G100" s="3">
@@ -39465,27 +39471,27 @@
     </row>
     <row r="101">
       <c r="A101" s="3">
-        <f>Inputs!$A$154</f>
+        <f>Inputs!$A$155</f>
         <v/>
       </c>
       <c r="B101" s="3">
-        <f>Loads!$B$235</f>
+        <f>Loads!$B$236</f>
         <v/>
       </c>
       <c r="C101" s="3">
-        <f>Loads!$D$235</f>
+        <f>Loads!$D$236</f>
         <v/>
       </c>
       <c r="D101" s="3">
-        <f>Loads!$E$235</f>
+        <f>Loads!$E$236</f>
         <v/>
       </c>
       <c r="E101" s="3">
-        <f>Loads!$H$235</f>
+        <f>Loads!$H$236</f>
         <v/>
       </c>
       <c r="F101" s="3">
-        <f>Loads!$L$235</f>
+        <f>Loads!$L$236</f>
         <v/>
       </c>
       <c r="G101" s="3">
@@ -39499,27 +39505,27 @@
     </row>
     <row r="102">
       <c r="A102" s="3">
-        <f>Inputs!$A$155</f>
+        <f>Inputs!$A$156</f>
         <v/>
       </c>
       <c r="B102" s="3">
-        <f>Loads!$B$236</f>
+        <f>Loads!$B$237</f>
         <v/>
       </c>
       <c r="C102" s="3">
-        <f>Loads!$D$236</f>
+        <f>Loads!$D$237</f>
         <v/>
       </c>
       <c r="D102" s="3">
-        <f>Loads!$E$236</f>
+        <f>Loads!$E$237</f>
         <v/>
       </c>
       <c r="E102" s="3">
-        <f>Loads!$H$236</f>
+        <f>Loads!$H$237</f>
         <v/>
       </c>
       <c r="F102" s="3">
-        <f>Loads!$L$236</f>
+        <f>Loads!$L$237</f>
         <v/>
       </c>
       <c r="G102" s="3">
@@ -39533,27 +39539,27 @@
     </row>
     <row r="103">
       <c r="A103" s="3">
-        <f>Inputs!$A$156</f>
+        <f>Inputs!$A$157</f>
         <v/>
       </c>
       <c r="B103" s="3">
-        <f>Loads!$B$237</f>
+        <f>Loads!$B$238</f>
         <v/>
       </c>
       <c r="C103" s="3">
-        <f>Loads!$D$237</f>
+        <f>Loads!$D$238</f>
         <v/>
       </c>
       <c r="D103" s="3">
-        <f>Loads!$E$237</f>
+        <f>Loads!$E$238</f>
         <v/>
       </c>
       <c r="E103" s="3">
-        <f>Loads!$H$237</f>
+        <f>Loads!$H$238</f>
         <v/>
       </c>
       <c r="F103" s="3">
-        <f>Loads!$L$237</f>
+        <f>Loads!$L$238</f>
         <v/>
       </c>
       <c r="G103" s="3">
@@ -39567,27 +39573,27 @@
     </row>
     <row r="104">
       <c r="A104" s="3">
-        <f>Inputs!$A$157</f>
+        <f>Inputs!$A$158</f>
         <v/>
       </c>
       <c r="B104" s="3">
-        <f>Loads!$B$238</f>
+        <f>Loads!$B$239</f>
         <v/>
       </c>
       <c r="C104" s="3">
-        <f>Loads!$D$238</f>
+        <f>Loads!$D$239</f>
         <v/>
       </c>
       <c r="D104" s="3">
-        <f>Loads!$E$238</f>
+        <f>Loads!$E$239</f>
         <v/>
       </c>
       <c r="E104" s="3">
-        <f>Loads!$H$238</f>
+        <f>Loads!$H$239</f>
         <v/>
       </c>
       <c r="F104" s="3">
-        <f>Loads!$L$238</f>
+        <f>Loads!$L$239</f>
         <v/>
       </c>
       <c r="G104" s="3">
@@ -39601,27 +39607,27 @@
     </row>
     <row r="105">
       <c r="A105" s="3">
-        <f>Inputs!$A$158</f>
+        <f>Inputs!$A$159</f>
         <v/>
       </c>
       <c r="B105" s="3">
-        <f>Loads!$B$239</f>
+        <f>Loads!$B$240</f>
         <v/>
       </c>
       <c r="C105" s="3">
-        <f>Loads!$D$239</f>
+        <f>Loads!$D$240</f>
         <v/>
       </c>
       <c r="D105" s="3">
-        <f>Loads!$E$239</f>
+        <f>Loads!$E$240</f>
         <v/>
       </c>
       <c r="E105" s="3">
-        <f>Loads!$H$239</f>
+        <f>Loads!$H$240</f>
         <v/>
       </c>
       <c r="F105" s="3">
-        <f>Loads!$L$239</f>
+        <f>Loads!$L$240</f>
         <v/>
       </c>
       <c r="G105" s="3">
@@ -39635,27 +39641,27 @@
     </row>
     <row r="106">
       <c r="A106" s="3">
-        <f>Inputs!$A$159</f>
+        <f>Inputs!$A$160</f>
         <v/>
       </c>
       <c r="B106" s="3">
-        <f>Loads!$B$240</f>
+        <f>Loads!$B$241</f>
         <v/>
       </c>
       <c r="C106" s="3">
-        <f>Loads!$D$240</f>
+        <f>Loads!$D$241</f>
         <v/>
       </c>
       <c r="D106" s="3">
-        <f>Loads!$E$240</f>
+        <f>Loads!$E$241</f>
         <v/>
       </c>
       <c r="E106" s="3">
-        <f>Loads!$H$240</f>
+        <f>Loads!$H$241</f>
         <v/>
       </c>
       <c r="F106" s="3">
-        <f>Loads!$L$240</f>
+        <f>Loads!$L$241</f>
         <v/>
       </c>
       <c r="G106" s="3">
@@ -39669,27 +39675,27 @@
     </row>
     <row r="107">
       <c r="A107" s="3">
-        <f>Inputs!$A$160</f>
+        <f>Inputs!$A$161</f>
         <v/>
       </c>
       <c r="B107" s="3">
-        <f>Loads!$B$241</f>
+        <f>Loads!$B$242</f>
         <v/>
       </c>
       <c r="C107" s="3">
-        <f>Loads!$D$241</f>
+        <f>Loads!$D$242</f>
         <v/>
       </c>
       <c r="D107" s="3">
-        <f>Loads!$E$241</f>
+        <f>Loads!$E$242</f>
         <v/>
       </c>
       <c r="E107" s="3">
-        <f>Loads!$H$241</f>
+        <f>Loads!$H$242</f>
         <v/>
       </c>
       <c r="F107" s="3">
-        <f>Loads!$L$241</f>
+        <f>Loads!$L$242</f>
         <v/>
       </c>
       <c r="G107" s="3">
@@ -39703,27 +39709,27 @@
     </row>
     <row r="108">
       <c r="A108" s="3">
-        <f>Inputs!$A$161</f>
+        <f>Inputs!$A$162</f>
         <v/>
       </c>
       <c r="B108" s="3">
-        <f>Loads!$B$242</f>
+        <f>Loads!$B$243</f>
         <v/>
       </c>
       <c r="C108" s="3">
-        <f>Loads!$D$242</f>
+        <f>Loads!$D$243</f>
         <v/>
       </c>
       <c r="D108" s="3">
-        <f>Loads!$E$242</f>
+        <f>Loads!$E$243</f>
         <v/>
       </c>
       <c r="E108" s="3">
-        <f>Loads!$H$242</f>
+        <f>Loads!$H$243</f>
         <v/>
       </c>
       <c r="F108" s="3">
-        <f>Loads!$L$242</f>
+        <f>Loads!$L$243</f>
         <v/>
       </c>
       <c r="G108" s="3">
@@ -39737,27 +39743,27 @@
     </row>
     <row r="109">
       <c r="A109" s="3">
-        <f>Inputs!$A$162</f>
+        <f>Inputs!$A$163</f>
         <v/>
       </c>
       <c r="B109" s="3">
-        <f>Loads!$B$243</f>
+        <f>Loads!$B$244</f>
         <v/>
       </c>
       <c r="C109" s="3">
-        <f>Loads!$D$243</f>
+        <f>Loads!$D$244</f>
         <v/>
       </c>
       <c r="D109" s="3">
-        <f>Loads!$E$243</f>
+        <f>Loads!$E$244</f>
         <v/>
       </c>
       <c r="E109" s="3">
-        <f>Loads!$H$243</f>
+        <f>Loads!$H$244</f>
         <v/>
       </c>
       <c r="F109" s="3">
-        <f>Loads!$L$243</f>
+        <f>Loads!$L$244</f>
         <v/>
       </c>
       <c r="G109" s="3">
@@ -39771,27 +39777,27 @@
     </row>
     <row r="110">
       <c r="A110" s="3">
-        <f>Inputs!$A$163</f>
+        <f>Inputs!$A$164</f>
         <v/>
       </c>
       <c r="B110" s="3">
-        <f>Loads!$B$244</f>
+        <f>Loads!$B$245</f>
         <v/>
       </c>
       <c r="C110" s="3">
-        <f>Loads!$D$244</f>
+        <f>Loads!$D$245</f>
         <v/>
       </c>
       <c r="D110" s="3">
-        <f>Loads!$E$244</f>
+        <f>Loads!$E$245</f>
         <v/>
       </c>
       <c r="E110" s="3">
-        <f>Loads!$H$244</f>
+        <f>Loads!$H$245</f>
         <v/>
       </c>
       <c r="F110" s="3">
-        <f>Loads!$L$244</f>
+        <f>Loads!$L$245</f>
         <v/>
       </c>
       <c r="G110" s="3">
@@ -39805,27 +39811,27 @@
     </row>
     <row r="111">
       <c r="A111" s="3">
-        <f>Inputs!$A$164</f>
+        <f>Inputs!$A$165</f>
         <v/>
       </c>
       <c r="B111" s="3">
-        <f>Loads!$B$245</f>
+        <f>Loads!$B$246</f>
         <v/>
       </c>
       <c r="C111" s="3">
-        <f>Loads!$D$245</f>
+        <f>Loads!$D$246</f>
         <v/>
       </c>
       <c r="D111" s="3">
-        <f>Loads!$E$245</f>
+        <f>Loads!$E$246</f>
         <v/>
       </c>
       <c r="E111" s="3">
-        <f>Loads!$H$245</f>
+        <f>Loads!$H$246</f>
         <v/>
       </c>
       <c r="F111" s="3">
-        <f>Loads!$L$245</f>
+        <f>Loads!$L$246</f>
         <v/>
       </c>
       <c r="G111" s="3">
@@ -39839,27 +39845,27 @@
     </row>
     <row r="112">
       <c r="A112" s="3">
-        <f>Inputs!$A$165</f>
+        <f>Inputs!$A$166</f>
         <v/>
       </c>
       <c r="B112" s="3">
-        <f>Loads!$B$246</f>
+        <f>Loads!$B$247</f>
         <v/>
       </c>
       <c r="C112" s="3">
-        <f>Loads!$D$246</f>
+        <f>Loads!$D$247</f>
         <v/>
       </c>
       <c r="D112" s="3">
-        <f>Loads!$E$246</f>
+        <f>Loads!$E$247</f>
         <v/>
       </c>
       <c r="E112" s="3">
-        <f>Loads!$H$246</f>
+        <f>Loads!$H$247</f>
         <v/>
       </c>
       <c r="F112" s="3">
-        <f>Loads!$L$246</f>
+        <f>Loads!$L$247</f>
         <v/>
       </c>
       <c r="G112" s="3">
@@ -39873,27 +39879,27 @@
     </row>
     <row r="113">
       <c r="A113" s="3">
-        <f>Inputs!$A$166</f>
+        <f>Inputs!$A$167</f>
         <v/>
       </c>
       <c r="B113" s="3">
-        <f>Loads!$B$247</f>
+        <f>Loads!$B$248</f>
         <v/>
       </c>
       <c r="C113" s="3">
-        <f>Loads!$D$247</f>
+        <f>Loads!$D$248</f>
         <v/>
       </c>
       <c r="D113" s="3">
-        <f>Loads!$E$247</f>
+        <f>Loads!$E$248</f>
         <v/>
       </c>
       <c r="E113" s="3">
-        <f>Loads!$H$247</f>
+        <f>Loads!$H$248</f>
         <v/>
       </c>
       <c r="F113" s="3">
-        <f>Loads!$L$247</f>
+        <f>Loads!$L$248</f>
         <v/>
       </c>
       <c r="G113" s="3">
@@ -39907,27 +39913,27 @@
     </row>
     <row r="114">
       <c r="A114" s="3">
-        <f>Inputs!$A$167</f>
+        <f>Inputs!$A$168</f>
         <v/>
       </c>
       <c r="B114" s="3">
-        <f>Loads!$B$248</f>
+        <f>Loads!$B$249</f>
         <v/>
       </c>
       <c r="C114" s="3">
-        <f>Loads!$D$248</f>
+        <f>Loads!$D$249</f>
         <v/>
       </c>
       <c r="D114" s="3">
-        <f>Loads!$E$248</f>
+        <f>Loads!$E$249</f>
         <v/>
       </c>
       <c r="E114" s="3">
-        <f>Loads!$H$248</f>
+        <f>Loads!$H$249</f>
         <v/>
       </c>
       <c r="F114" s="3">
-        <f>Loads!$L$248</f>
+        <f>Loads!$L$249</f>
         <v/>
       </c>
       <c r="G114" s="3">
@@ -39941,27 +39947,27 @@
     </row>
     <row r="115">
       <c r="A115" s="3">
-        <f>Inputs!$A$168</f>
+        <f>Inputs!$A$169</f>
         <v/>
       </c>
       <c r="B115" s="3">
-        <f>Loads!$B$249</f>
+        <f>Loads!$B$250</f>
         <v/>
       </c>
       <c r="C115" s="3">
-        <f>Loads!$D$249</f>
+        <f>Loads!$D$250</f>
         <v/>
       </c>
       <c r="D115" s="3">
-        <f>Loads!$E$249</f>
+        <f>Loads!$E$250</f>
         <v/>
       </c>
       <c r="E115" s="3">
-        <f>Loads!$H$249</f>
+        <f>Loads!$H$250</f>
         <v/>
       </c>
       <c r="F115" s="3">
-        <f>Loads!$L$249</f>
+        <f>Loads!$L$250</f>
         <v/>
       </c>
       <c r="G115" s="3">
@@ -39975,27 +39981,27 @@
     </row>
     <row r="116">
       <c r="A116" s="3">
-        <f>Inputs!$A$169</f>
+        <f>Inputs!$A$170</f>
         <v/>
       </c>
       <c r="B116" s="3">
-        <f>Loads!$B$250</f>
+        <f>Loads!$B$251</f>
         <v/>
       </c>
       <c r="C116" s="3">
-        <f>Loads!$D$250</f>
+        <f>Loads!$D$251</f>
         <v/>
       </c>
       <c r="D116" s="3">
-        <f>Loads!$E$250</f>
+        <f>Loads!$E$251</f>
         <v/>
       </c>
       <c r="E116" s="3">
-        <f>Loads!$H$250</f>
+        <f>Loads!$H$251</f>
         <v/>
       </c>
       <c r="F116" s="3">
-        <f>Loads!$L$250</f>
+        <f>Loads!$L$251</f>
         <v/>
       </c>
       <c r="G116" s="3">
@@ -40009,27 +40015,27 @@
     </row>
     <row r="117">
       <c r="A117" s="3">
-        <f>Inputs!$A$170</f>
+        <f>Inputs!$A$171</f>
         <v/>
       </c>
       <c r="B117" s="3">
-        <f>Loads!$B$251</f>
+        <f>Loads!$B$252</f>
         <v/>
       </c>
       <c r="C117" s="3">
-        <f>Loads!$D$251</f>
+        <f>Loads!$D$252</f>
         <v/>
       </c>
       <c r="D117" s="3">
-        <f>Loads!$E$251</f>
+        <f>Loads!$E$252</f>
         <v/>
       </c>
       <c r="E117" s="3">
-        <f>Loads!$H$251</f>
+        <f>Loads!$H$252</f>
         <v/>
       </c>
       <c r="F117" s="3">
-        <f>Loads!$L$251</f>
+        <f>Loads!$L$252</f>
         <v/>
       </c>
       <c r="G117" s="3">
@@ -40043,27 +40049,27 @@
     </row>
     <row r="118">
       <c r="A118" s="3">
-        <f>Inputs!$A$171</f>
+        <f>Inputs!$A$172</f>
         <v/>
       </c>
       <c r="B118" s="3">
-        <f>Loads!$B$252</f>
+        <f>Loads!$B$253</f>
         <v/>
       </c>
       <c r="C118" s="3">
-        <f>Loads!$D$252</f>
+        <f>Loads!$D$253</f>
         <v/>
       </c>
       <c r="D118" s="3">
-        <f>Loads!$E$252</f>
+        <f>Loads!$E$253</f>
         <v/>
       </c>
       <c r="E118" s="3">
-        <f>Loads!$H$252</f>
+        <f>Loads!$H$253</f>
         <v/>
       </c>
       <c r="F118" s="3">
-        <f>Loads!$L$252</f>
+        <f>Loads!$L$253</f>
         <v/>
       </c>
       <c r="G118" s="3">
@@ -40077,27 +40083,27 @@
     </row>
     <row r="119">
       <c r="A119" s="3">
-        <f>Inputs!$A$172</f>
+        <f>Inputs!$A$173</f>
         <v/>
       </c>
       <c r="B119" s="3">
-        <f>Loads!$B$253</f>
+        <f>Loads!$B$254</f>
         <v/>
       </c>
       <c r="C119" s="3">
-        <f>Loads!$D$253</f>
+        <f>Loads!$D$254</f>
         <v/>
       </c>
       <c r="D119" s="3">
-        <f>Loads!$E$253</f>
+        <f>Loads!$E$254</f>
         <v/>
       </c>
       <c r="E119" s="3">
-        <f>Loads!$H$253</f>
+        <f>Loads!$H$254</f>
         <v/>
       </c>
       <c r="F119" s="3">
-        <f>Loads!$L$253</f>
+        <f>Loads!$L$254</f>
         <v/>
       </c>
       <c r="G119" s="3">
@@ -40111,27 +40117,27 @@
     </row>
     <row r="120">
       <c r="A120" s="3">
-        <f>Inputs!$A$173</f>
+        <f>Inputs!$A$174</f>
         <v/>
       </c>
       <c r="B120" s="3">
-        <f>Loads!$B$254</f>
+        <f>Loads!$B$255</f>
         <v/>
       </c>
       <c r="C120" s="3">
-        <f>Loads!$D$254</f>
+        <f>Loads!$D$255</f>
         <v/>
       </c>
       <c r="D120" s="3">
-        <f>Loads!$E$254</f>
+        <f>Loads!$E$255</f>
         <v/>
       </c>
       <c r="E120" s="3">
-        <f>Loads!$H$254</f>
+        <f>Loads!$H$255</f>
         <v/>
       </c>
       <c r="F120" s="3">
-        <f>Loads!$L$254</f>
+        <f>Loads!$L$255</f>
         <v/>
       </c>
       <c r="G120" s="3">
@@ -40145,27 +40151,27 @@
     </row>
     <row r="121">
       <c r="A121" s="3">
-        <f>Inputs!$A$174</f>
+        <f>Inputs!$A$175</f>
         <v/>
       </c>
       <c r="B121" s="3">
-        <f>Loads!$B$255</f>
+        <f>Loads!$B$256</f>
         <v/>
       </c>
       <c r="C121" s="3">
-        <f>Loads!$D$255</f>
+        <f>Loads!$D$256</f>
         <v/>
       </c>
       <c r="D121" s="3">
-        <f>Loads!$E$255</f>
+        <f>Loads!$E$256</f>
         <v/>
       </c>
       <c r="E121" s="3">
-        <f>Loads!$H$255</f>
+        <f>Loads!$H$256</f>
         <v/>
       </c>
       <c r="F121" s="3">
-        <f>Loads!$L$255</f>
+        <f>Loads!$L$256</f>
         <v/>
       </c>
       <c r="G121" s="3">
@@ -40179,27 +40185,27 @@
     </row>
     <row r="122">
       <c r="A122" s="3">
-        <f>Inputs!$A$175</f>
+        <f>Inputs!$A$176</f>
         <v/>
       </c>
       <c r="B122" s="3">
-        <f>Loads!$B$256</f>
+        <f>Loads!$B$257</f>
         <v/>
       </c>
       <c r="C122" s="3">
-        <f>Loads!$D$256</f>
+        <f>Loads!$D$257</f>
         <v/>
       </c>
       <c r="D122" s="3">
-        <f>Loads!$E$256</f>
+        <f>Loads!$E$257</f>
         <v/>
       </c>
       <c r="E122" s="3">
-        <f>Loads!$H$256</f>
+        <f>Loads!$H$257</f>
         <v/>
       </c>
       <c r="F122" s="3">
-        <f>Loads!$L$256</f>
+        <f>Loads!$L$257</f>
         <v/>
       </c>
       <c r="G122" s="3">
@@ -40213,27 +40219,27 @@
     </row>
     <row r="123">
       <c r="A123" s="3">
-        <f>Inputs!$A$176</f>
+        <f>Inputs!$A$177</f>
         <v/>
       </c>
       <c r="B123" s="3">
-        <f>Loads!$B$257</f>
+        <f>Loads!$B$258</f>
         <v/>
       </c>
       <c r="C123" s="3">
-        <f>Loads!$D$257</f>
+        <f>Loads!$D$258</f>
         <v/>
       </c>
       <c r="D123" s="3">
-        <f>Loads!$E$257</f>
+        <f>Loads!$E$258</f>
         <v/>
       </c>
       <c r="E123" s="3">
-        <f>Loads!$H$257</f>
+        <f>Loads!$H$258</f>
         <v/>
       </c>
       <c r="F123" s="3">
-        <f>Loads!$L$257</f>
+        <f>Loads!$L$258</f>
         <v/>
       </c>
       <c r="G123" s="3">
@@ -40247,27 +40253,27 @@
     </row>
     <row r="124">
       <c r="A124" s="3">
-        <f>Inputs!$A$177</f>
+        <f>Inputs!$A$178</f>
         <v/>
       </c>
       <c r="B124" s="3">
-        <f>Loads!$B$258</f>
+        <f>Loads!$B$259</f>
         <v/>
       </c>
       <c r="C124" s="3">
-        <f>Loads!$D$258</f>
+        <f>Loads!$D$259</f>
         <v/>
       </c>
       <c r="D124" s="3">
-        <f>Loads!$E$258</f>
+        <f>Loads!$E$259</f>
         <v/>
       </c>
       <c r="E124" s="3">
-        <f>Loads!$H$258</f>
+        <f>Loads!$H$259</f>
         <v/>
       </c>
       <c r="F124" s="3">
-        <f>Loads!$L$258</f>
+        <f>Loads!$L$259</f>
         <v/>
       </c>
       <c r="G124" s="3">
@@ -40281,27 +40287,27 @@
     </row>
     <row r="125">
       <c r="A125" s="3">
-        <f>Inputs!$A$178</f>
+        <f>Inputs!$A$179</f>
         <v/>
       </c>
       <c r="B125" s="3">
-        <f>Loads!$B$259</f>
+        <f>Loads!$B$260</f>
         <v/>
       </c>
       <c r="C125" s="3">
-        <f>Loads!$D$259</f>
+        <f>Loads!$D$260</f>
         <v/>
       </c>
       <c r="D125" s="3">
-        <f>Loads!$E$259</f>
+        <f>Loads!$E$260</f>
         <v/>
       </c>
       <c r="E125" s="3">
-        <f>Loads!$H$259</f>
+        <f>Loads!$H$260</f>
         <v/>
       </c>
       <c r="F125" s="3">
-        <f>Loads!$L$259</f>
+        <f>Loads!$L$260</f>
         <v/>
       </c>
       <c r="G125" s="3">
@@ -40315,27 +40321,27 @@
     </row>
     <row r="126">
       <c r="A126" s="3">
-        <f>Inputs!$A$179</f>
+        <f>Inputs!$A$180</f>
         <v/>
       </c>
       <c r="B126" s="3">
-        <f>Loads!$B$260</f>
+        <f>Loads!$B$261</f>
         <v/>
       </c>
       <c r="C126" s="3">
-        <f>Loads!$D$260</f>
+        <f>Loads!$D$261</f>
         <v/>
       </c>
       <c r="D126" s="3">
-        <f>Loads!$E$260</f>
+        <f>Loads!$E$261</f>
         <v/>
       </c>
       <c r="E126" s="3">
-        <f>Loads!$H$260</f>
+        <f>Loads!$H$261</f>
         <v/>
       </c>
       <c r="F126" s="3">
-        <f>Loads!$L$260</f>
+        <f>Loads!$L$261</f>
         <v/>
       </c>
       <c r="G126" s="3">
@@ -40349,27 +40355,27 @@
     </row>
     <row r="127">
       <c r="A127" s="3">
-        <f>Inputs!$A$180</f>
+        <f>Inputs!$A$181</f>
         <v/>
       </c>
       <c r="B127" s="3">
-        <f>Loads!$B$261</f>
+        <f>Loads!$B$262</f>
         <v/>
       </c>
       <c r="C127" s="3">
-        <f>Loads!$D$261</f>
+        <f>Loads!$D$262</f>
         <v/>
       </c>
       <c r="D127" s="3">
-        <f>Loads!$E$261</f>
+        <f>Loads!$E$262</f>
         <v/>
       </c>
       <c r="E127" s="3">
-        <f>Loads!$H$261</f>
+        <f>Loads!$H$262</f>
         <v/>
       </c>
       <c r="F127" s="3">
-        <f>Loads!$L$261</f>
+        <f>Loads!$L$262</f>
         <v/>
       </c>
       <c r="G127" s="3">
@@ -40383,27 +40389,27 @@
     </row>
     <row r="128">
       <c r="A128" s="3">
-        <f>Inputs!$A$181</f>
+        <f>Inputs!$A$182</f>
         <v/>
       </c>
       <c r="B128" s="3">
-        <f>Loads!$B$262</f>
+        <f>Loads!$B$263</f>
         <v/>
       </c>
       <c r="C128" s="3">
-        <f>Loads!$D$262</f>
+        <f>Loads!$D$263</f>
         <v/>
       </c>
       <c r="D128" s="3">
-        <f>Loads!$E$262</f>
+        <f>Loads!$E$263</f>
         <v/>
       </c>
       <c r="E128" s="3">
-        <f>Loads!$H$262</f>
+        <f>Loads!$H$263</f>
         <v/>
       </c>
       <c r="F128" s="3">
-        <f>Loads!$L$262</f>
+        <f>Loads!$L$263</f>
         <v/>
       </c>
       <c r="G128" s="3">
@@ -40417,27 +40423,27 @@
     </row>
     <row r="129">
       <c r="A129" s="3">
-        <f>Inputs!$A$182</f>
+        <f>Inputs!$A$183</f>
         <v/>
       </c>
       <c r="B129" s="3">
-        <f>Loads!$B$263</f>
+        <f>Loads!$B$264</f>
         <v/>
       </c>
       <c r="C129" s="3">
-        <f>Loads!$D$263</f>
+        <f>Loads!$D$264</f>
         <v/>
       </c>
       <c r="D129" s="3">
-        <f>Loads!$E$263</f>
+        <f>Loads!$E$264</f>
         <v/>
       </c>
       <c r="E129" s="3">
-        <f>Loads!$H$263</f>
+        <f>Loads!$H$264</f>
         <v/>
       </c>
       <c r="F129" s="3">
-        <f>Loads!$L$263</f>
+        <f>Loads!$L$264</f>
         <v/>
       </c>
       <c r="G129" s="3">
@@ -40451,27 +40457,27 @@
     </row>
     <row r="130">
       <c r="A130" s="3">
-        <f>Inputs!$A$183</f>
+        <f>Inputs!$A$184</f>
         <v/>
       </c>
       <c r="B130" s="3">
-        <f>Loads!$B$264</f>
+        <f>Loads!$B$265</f>
         <v/>
       </c>
       <c r="C130" s="3">
-        <f>Loads!$D$264</f>
+        <f>Loads!$D$265</f>
         <v/>
       </c>
       <c r="D130" s="3">
-        <f>Loads!$E$264</f>
+        <f>Loads!$E$265</f>
         <v/>
       </c>
       <c r="E130" s="3">
-        <f>Loads!$H$264</f>
+        <f>Loads!$H$265</f>
         <v/>
       </c>
       <c r="F130" s="3">
-        <f>Loads!$L$264</f>
+        <f>Loads!$L$265</f>
         <v/>
       </c>
       <c r="G130" s="3">
@@ -40485,27 +40491,27 @@
     </row>
     <row r="131">
       <c r="A131" s="3">
-        <f>Inputs!$A$184</f>
+        <f>Inputs!$A$185</f>
         <v/>
       </c>
       <c r="B131" s="3">
-        <f>Loads!$B$265</f>
+        <f>Loads!$B$266</f>
         <v/>
       </c>
       <c r="C131" s="3">
-        <f>Loads!$D$265</f>
+        <f>Loads!$D$266</f>
         <v/>
       </c>
       <c r="D131" s="3">
-        <f>Loads!$E$265</f>
+        <f>Loads!$E$266</f>
         <v/>
       </c>
       <c r="E131" s="3">
-        <f>Loads!$H$265</f>
+        <f>Loads!$H$266</f>
         <v/>
       </c>
       <c r="F131" s="3">
-        <f>Loads!$L$265</f>
+        <f>Loads!$L$266</f>
         <v/>
       </c>
       <c r="G131" s="3">
@@ -40519,27 +40525,27 @@
     </row>
     <row r="132">
       <c r="A132" s="3">
-        <f>Inputs!$A$185</f>
+        <f>Inputs!$A$186</f>
         <v/>
       </c>
       <c r="B132" s="3">
-        <f>Loads!$B$266</f>
+        <f>Loads!$B$267</f>
         <v/>
       </c>
       <c r="C132" s="3">
-        <f>Loads!$D$266</f>
+        <f>Loads!$D$267</f>
         <v/>
       </c>
       <c r="D132" s="3">
-        <f>Loads!$E$266</f>
+        <f>Loads!$E$267</f>
         <v/>
       </c>
       <c r="E132" s="3">
-        <f>Loads!$H$266</f>
+        <f>Loads!$H$267</f>
         <v/>
       </c>
       <c r="F132" s="3">
-        <f>Loads!$L$266</f>
+        <f>Loads!$L$267</f>
         <v/>
       </c>
       <c r="G132" s="3">
@@ -40553,27 +40559,27 @@
     </row>
     <row r="133">
       <c r="A133" s="3">
-        <f>Inputs!$A$186</f>
+        <f>Inputs!$A$187</f>
         <v/>
       </c>
       <c r="B133" s="3">
-        <f>Loads!$B$267</f>
+        <f>Loads!$B$268</f>
         <v/>
       </c>
       <c r="C133" s="3">
-        <f>Loads!$D$267</f>
+        <f>Loads!$D$268</f>
         <v/>
       </c>
       <c r="D133" s="3">
-        <f>Loads!$E$267</f>
+        <f>Loads!$E$268</f>
         <v/>
       </c>
       <c r="E133" s="3">
-        <f>Loads!$H$267</f>
+        <f>Loads!$H$268</f>
         <v/>
       </c>
       <c r="F133" s="3">
-        <f>Loads!$L$267</f>
+        <f>Loads!$L$268</f>
         <v/>
       </c>
       <c r="G133" s="3">
@@ -40587,27 +40593,27 @@
     </row>
     <row r="134">
       <c r="A134" s="3">
-        <f>Inputs!$A$187</f>
+        <f>Inputs!$A$188</f>
         <v/>
       </c>
       <c r="B134" s="3">
-        <f>Loads!$B$268</f>
+        <f>Loads!$B$269</f>
         <v/>
       </c>
       <c r="C134" s="3">
-        <f>Loads!$D$268</f>
+        <f>Loads!$D$269</f>
         <v/>
       </c>
       <c r="D134" s="3">
-        <f>Loads!$E$268</f>
+        <f>Loads!$E$269</f>
         <v/>
       </c>
       <c r="E134" s="3">
-        <f>Loads!$H$268</f>
+        <f>Loads!$H$269</f>
         <v/>
       </c>
       <c r="F134" s="3">
-        <f>Loads!$L$268</f>
+        <f>Loads!$L$269</f>
         <v/>
       </c>
       <c r="G134" s="3">
@@ -40621,27 +40627,27 @@
     </row>
     <row r="135">
       <c r="A135" s="3">
-        <f>Inputs!$A$188</f>
+        <f>Inputs!$A$189</f>
         <v/>
       </c>
       <c r="B135" s="3">
-        <f>Loads!$B$269</f>
+        <f>Loads!$B$270</f>
         <v/>
       </c>
       <c r="C135" s="3">
-        <f>Loads!$D$269</f>
+        <f>Loads!$D$270</f>
         <v/>
       </c>
       <c r="D135" s="3">
-        <f>Loads!$E$269</f>
+        <f>Loads!$E$270</f>
         <v/>
       </c>
       <c r="E135" s="3">
-        <f>Loads!$H$269</f>
+        <f>Loads!$H$270</f>
         <v/>
       </c>
       <c r="F135" s="3">
-        <f>Loads!$L$269</f>
+        <f>Loads!$L$270</f>
         <v/>
       </c>
       <c r="G135" s="3">
@@ -40655,27 +40661,27 @@
     </row>
     <row r="136">
       <c r="A136" s="3">
-        <f>Inputs!$A$189</f>
+        <f>Inputs!$A$190</f>
         <v/>
       </c>
       <c r="B136" s="3">
-        <f>Loads!$B$270</f>
+        <f>Loads!$B$271</f>
         <v/>
       </c>
       <c r="C136" s="3">
-        <f>Loads!$D$270</f>
+        <f>Loads!$D$271</f>
         <v/>
       </c>
       <c r="D136" s="3">
-        <f>Loads!$E$270</f>
+        <f>Loads!$E$271</f>
         <v/>
       </c>
       <c r="E136" s="3">
-        <f>Loads!$H$270</f>
+        <f>Loads!$H$271</f>
         <v/>
       </c>
       <c r="F136" s="3">
-        <f>Loads!$L$270</f>
+        <f>Loads!$L$271</f>
         <v/>
       </c>
       <c r="G136" s="3">
@@ -40689,27 +40695,27 @@
     </row>
     <row r="137">
       <c r="A137" s="3">
-        <f>Inputs!$A$190</f>
+        <f>Inputs!$A$191</f>
         <v/>
       </c>
       <c r="B137" s="3">
-        <f>Loads!$B$271</f>
+        <f>Loads!$B$272</f>
         <v/>
       </c>
       <c r="C137" s="3">
-        <f>Loads!$D$271</f>
+        <f>Loads!$D$272</f>
         <v/>
       </c>
       <c r="D137" s="3">
-        <f>Loads!$E$271</f>
+        <f>Loads!$E$272</f>
         <v/>
       </c>
       <c r="E137" s="3">
-        <f>Loads!$H$271</f>
+        <f>Loads!$H$272</f>
         <v/>
       </c>
       <c r="F137" s="3">
-        <f>Loads!$L$271</f>
+        <f>Loads!$L$272</f>
         <v/>
       </c>
       <c r="G137" s="3">
@@ -40723,27 +40729,27 @@
     </row>
     <row r="138">
       <c r="A138" s="3">
-        <f>Inputs!$A$191</f>
+        <f>Inputs!$A$192</f>
         <v/>
       </c>
       <c r="B138" s="3">
-        <f>Loads!$B$272</f>
+        <f>Loads!$B$273</f>
         <v/>
       </c>
       <c r="C138" s="3">
-        <f>Loads!$D$272</f>
+        <f>Loads!$D$273</f>
         <v/>
       </c>
       <c r="D138" s="3">
-        <f>Loads!$E$272</f>
+        <f>Loads!$E$273</f>
         <v/>
       </c>
       <c r="E138" s="3">
-        <f>Loads!$H$272</f>
+        <f>Loads!$H$273</f>
         <v/>
       </c>
       <c r="F138" s="3">
-        <f>Loads!$L$272</f>
+        <f>Loads!$L$273</f>
         <v/>
       </c>
       <c r="G138" s="3">
@@ -40757,27 +40763,27 @@
     </row>
     <row r="139">
       <c r="A139" s="3">
-        <f>Inputs!$A$192</f>
+        <f>Inputs!$A$193</f>
         <v/>
       </c>
       <c r="B139" s="3">
-        <f>Loads!$B$273</f>
+        <f>Loads!$B$274</f>
         <v/>
       </c>
       <c r="C139" s="3">
-        <f>Loads!$D$273</f>
+        <f>Loads!$D$274</f>
         <v/>
       </c>
       <c r="D139" s="3">
-        <f>Loads!$E$273</f>
+        <f>Loads!$E$274</f>
         <v/>
       </c>
       <c r="E139" s="3">
-        <f>Loads!$H$273</f>
+        <f>Loads!$H$274</f>
         <v/>
       </c>
       <c r="F139" s="3">
-        <f>Loads!$L$273</f>
+        <f>Loads!$L$274</f>
         <v/>
       </c>
       <c r="G139" s="3">
@@ -40791,27 +40797,27 @@
     </row>
     <row r="140">
       <c r="A140" s="3">
-        <f>Inputs!$A$193</f>
+        <f>Inputs!$A$194</f>
         <v/>
       </c>
       <c r="B140" s="3">
-        <f>Loads!$B$274</f>
+        <f>Loads!$B$275</f>
         <v/>
       </c>
       <c r="C140" s="3">
-        <f>Loads!$D$274</f>
+        <f>Loads!$D$275</f>
         <v/>
       </c>
       <c r="D140" s="3">
-        <f>Loads!$E$274</f>
+        <f>Loads!$E$275</f>
         <v/>
       </c>
       <c r="E140" s="3">
-        <f>Loads!$H$274</f>
+        <f>Loads!$H$275</f>
         <v/>
       </c>
       <c r="F140" s="3">
-        <f>Loads!$L$274</f>
+        <f>Loads!$L$275</f>
         <v/>
       </c>
       <c r="G140" s="3">
@@ -40825,27 +40831,27 @@
     </row>
     <row r="141">
       <c r="A141" s="3">
-        <f>Inputs!$A$194</f>
+        <f>Inputs!$A$195</f>
         <v/>
       </c>
       <c r="B141" s="3">
-        <f>Loads!$B$275</f>
+        <f>Loads!$B$276</f>
         <v/>
       </c>
       <c r="C141" s="3">
-        <f>Loads!$D$275</f>
+        <f>Loads!$D$276</f>
         <v/>
       </c>
       <c r="D141" s="3">
-        <f>Loads!$E$275</f>
+        <f>Loads!$E$276</f>
         <v/>
       </c>
       <c r="E141" s="3">
-        <f>Loads!$H$275</f>
+        <f>Loads!$H$276</f>
         <v/>
       </c>
       <c r="F141" s="3">
-        <f>Loads!$L$275</f>
+        <f>Loads!$L$276</f>
         <v/>
       </c>
       <c r="G141" s="3">
@@ -40859,27 +40865,27 @@
     </row>
     <row r="142">
       <c r="A142" s="3">
-        <f>Inputs!$A$195</f>
+        <f>Inputs!$A$196</f>
         <v/>
       </c>
       <c r="B142" s="3">
-        <f>Loads!$B$276</f>
+        <f>Loads!$B$277</f>
         <v/>
       </c>
       <c r="C142" s="3">
-        <f>Loads!$D$276</f>
+        <f>Loads!$D$277</f>
         <v/>
       </c>
       <c r="D142" s="3">
-        <f>Loads!$E$276</f>
+        <f>Loads!$E$277</f>
         <v/>
       </c>
       <c r="E142" s="3">
-        <f>Loads!$H$276</f>
+        <f>Loads!$H$277</f>
         <v/>
       </c>
       <c r="F142" s="3">
-        <f>Loads!$L$276</f>
+        <f>Loads!$L$277</f>
         <v/>
       </c>
       <c r="G142" s="3">
@@ -40893,27 +40899,27 @@
     </row>
     <row r="143">
       <c r="A143" s="3">
-        <f>Inputs!$A$196</f>
+        <f>Inputs!$A$197</f>
         <v/>
       </c>
       <c r="B143" s="3">
-        <f>Loads!$B$277</f>
+        <f>Loads!$B$278</f>
         <v/>
       </c>
       <c r="C143" s="3">
-        <f>Loads!$D$277</f>
+        <f>Loads!$D$278</f>
         <v/>
       </c>
       <c r="D143" s="3">
-        <f>Loads!$E$277</f>
+        <f>Loads!$E$278</f>
         <v/>
       </c>
       <c r="E143" s="3">
-        <f>Loads!$H$277</f>
+        <f>Loads!$H$278</f>
         <v/>
       </c>
       <c r="F143" s="3">
-        <f>Loads!$L$277</f>
+        <f>Loads!$L$278</f>
         <v/>
       </c>
       <c r="G143" s="3">
@@ -40927,27 +40933,27 @@
     </row>
     <row r="144">
       <c r="A144" s="3">
-        <f>Inputs!$A$197</f>
+        <f>Inputs!$A$198</f>
         <v/>
       </c>
       <c r="B144" s="3">
-        <f>Loads!$B$278</f>
+        <f>Loads!$B$279</f>
         <v/>
       </c>
       <c r="C144" s="3">
-        <f>Loads!$D$278</f>
+        <f>Loads!$D$279</f>
         <v/>
       </c>
       <c r="D144" s="3">
-        <f>Loads!$E$278</f>
+        <f>Loads!$E$279</f>
         <v/>
       </c>
       <c r="E144" s="3">
-        <f>Loads!$H$278</f>
+        <f>Loads!$H$279</f>
         <v/>
       </c>
       <c r="F144" s="3">
-        <f>Loads!$L$278</f>
+        <f>Loads!$L$279</f>
         <v/>
       </c>
       <c r="G144" s="3">
@@ -40961,27 +40967,27 @@
     </row>
     <row r="145">
       <c r="A145" s="3">
-        <f>Inputs!$A$198</f>
+        <f>Inputs!$A$199</f>
         <v/>
       </c>
       <c r="B145" s="3">
-        <f>Loads!$B$279</f>
+        <f>Loads!$B$280</f>
         <v/>
       </c>
       <c r="C145" s="3">
-        <f>Loads!$D$279</f>
+        <f>Loads!$D$280</f>
         <v/>
       </c>
       <c r="D145" s="3">
-        <f>Loads!$E$279</f>
+        <f>Loads!$E$280</f>
         <v/>
       </c>
       <c r="E145" s="3">
-        <f>Loads!$H$279</f>
+        <f>Loads!$H$280</f>
         <v/>
       </c>
       <c r="F145" s="3">
-        <f>Loads!$L$279</f>
+        <f>Loads!$L$280</f>
         <v/>
       </c>
       <c r="G145" s="3">
@@ -40995,27 +41001,27 @@
     </row>
     <row r="146">
       <c r="A146" s="3">
-        <f>Inputs!$A$199</f>
+        <f>Inputs!$A$200</f>
         <v/>
       </c>
       <c r="B146" s="3">
-        <f>Loads!$B$280</f>
+        <f>Loads!$B$281</f>
         <v/>
       </c>
       <c r="C146" s="3">
-        <f>Loads!$D$280</f>
+        <f>Loads!$D$281</f>
         <v/>
       </c>
       <c r="D146" s="3">
-        <f>Loads!$E$280</f>
+        <f>Loads!$E$281</f>
         <v/>
       </c>
       <c r="E146" s="3">
-        <f>Loads!$H$280</f>
+        <f>Loads!$H$281</f>
         <v/>
       </c>
       <c r="F146" s="3">
-        <f>Loads!$L$280</f>
+        <f>Loads!$L$281</f>
         <v/>
       </c>
       <c r="G146" s="3">
@@ -41029,27 +41035,27 @@
     </row>
     <row r="147">
       <c r="A147" s="3">
-        <f>Inputs!$A$200</f>
+        <f>Inputs!$A$201</f>
         <v/>
       </c>
       <c r="B147" s="3">
-        <f>Loads!$B$281</f>
+        <f>Loads!$B$282</f>
         <v/>
       </c>
       <c r="C147" s="3">
-        <f>Loads!$D$281</f>
+        <f>Loads!$D$282</f>
         <v/>
       </c>
       <c r="D147" s="3">
-        <f>Loads!$E$281</f>
+        <f>Loads!$E$282</f>
         <v/>
       </c>
       <c r="E147" s="3">
-        <f>Loads!$H$281</f>
+        <f>Loads!$H$282</f>
         <v/>
       </c>
       <c r="F147" s="3">
-        <f>Loads!$L$281</f>
+        <f>Loads!$L$282</f>
         <v/>
       </c>
       <c r="G147" s="3">
@@ -41063,27 +41069,27 @@
     </row>
     <row r="148">
       <c r="A148" s="3">
-        <f>Inputs!$A$201</f>
+        <f>Inputs!$A$202</f>
         <v/>
       </c>
       <c r="B148" s="3">
-        <f>Loads!$B$282</f>
+        <f>Loads!$B$283</f>
         <v/>
       </c>
       <c r="C148" s="3">
-        <f>Loads!$D$282</f>
+        <f>Loads!$D$283</f>
         <v/>
       </c>
       <c r="D148" s="3">
-        <f>Loads!$E$282</f>
+        <f>Loads!$E$283</f>
         <v/>
       </c>
       <c r="E148" s="3">
-        <f>Loads!$H$282</f>
+        <f>Loads!$H$283</f>
         <v/>
       </c>
       <c r="F148" s="3">
-        <f>Loads!$L$282</f>
+        <f>Loads!$L$283</f>
         <v/>
       </c>
       <c r="G148" s="3">
@@ -41097,27 +41103,27 @@
     </row>
     <row r="149">
       <c r="A149" s="3">
-        <f>Inputs!$A$202</f>
+        <f>Inputs!$A$203</f>
         <v/>
       </c>
       <c r="B149" s="3">
-        <f>Loads!$B$283</f>
+        <f>Loads!$B$284</f>
         <v/>
       </c>
       <c r="C149" s="3">
-        <f>Loads!$D$283</f>
+        <f>Loads!$D$284</f>
         <v/>
       </c>
       <c r="D149" s="3">
-        <f>Loads!$E$283</f>
+        <f>Loads!$E$284</f>
         <v/>
       </c>
       <c r="E149" s="3">
-        <f>Loads!$H$283</f>
+        <f>Loads!$H$284</f>
         <v/>
       </c>
       <c r="F149" s="3">
-        <f>Loads!$L$283</f>
+        <f>Loads!$L$284</f>
         <v/>
       </c>
       <c r="G149" s="3">
@@ -41131,27 +41137,27 @@
     </row>
     <row r="150">
       <c r="A150" s="3">
-        <f>Inputs!$A$203</f>
+        <f>Inputs!$A$204</f>
         <v/>
       </c>
       <c r="B150" s="3">
-        <f>Loads!$B$284</f>
+        <f>Loads!$B$285</f>
         <v/>
       </c>
       <c r="C150" s="3">
-        <f>Loads!$D$284</f>
+        <f>Loads!$D$285</f>
         <v/>
       </c>
       <c r="D150" s="3">
-        <f>Loads!$E$284</f>
+        <f>Loads!$E$285</f>
         <v/>
       </c>
       <c r="E150" s="3">
-        <f>Loads!$H$284</f>
+        <f>Loads!$H$285</f>
         <v/>
       </c>
       <c r="F150" s="3">
-        <f>Loads!$L$284</f>
+        <f>Loads!$L$285</f>
         <v/>
       </c>
       <c r="G150" s="3">
@@ -41165,27 +41171,27 @@
     </row>
     <row r="151">
       <c r="A151" s="3">
-        <f>Inputs!$A$204</f>
+        <f>Inputs!$A$205</f>
         <v/>
       </c>
       <c r="B151" s="3">
-        <f>Loads!$B$285</f>
+        <f>Loads!$B$286</f>
         <v/>
       </c>
       <c r="C151" s="3">
-        <f>Loads!$D$285</f>
+        <f>Loads!$D$286</f>
         <v/>
       </c>
       <c r="D151" s="3">
-        <f>Loads!$E$285</f>
+        <f>Loads!$E$286</f>
         <v/>
       </c>
       <c r="E151" s="3">
-        <f>Loads!$H$285</f>
+        <f>Loads!$H$286</f>
         <v/>
       </c>
       <c r="F151" s="3">
-        <f>Loads!$L$285</f>
+        <f>Loads!$L$286</f>
         <v/>
       </c>
       <c r="G151" s="3">
@@ -41199,27 +41205,27 @@
     </row>
     <row r="152">
       <c r="A152" s="3">
-        <f>Inputs!$A$205</f>
+        <f>Inputs!$A$206</f>
         <v/>
       </c>
       <c r="B152" s="3">
-        <f>Loads!$B$286</f>
+        <f>Loads!$B$287</f>
         <v/>
       </c>
       <c r="C152" s="3">
-        <f>Loads!$D$286</f>
+        <f>Loads!$D$287</f>
         <v/>
       </c>
       <c r="D152" s="3">
-        <f>Loads!$E$286</f>
+        <f>Loads!$E$287</f>
         <v/>
       </c>
       <c r="E152" s="3">
-        <f>Loads!$H$286</f>
+        <f>Loads!$H$287</f>
         <v/>
       </c>
       <c r="F152" s="3">
-        <f>Loads!$L$286</f>
+        <f>Loads!$L$287</f>
         <v/>
       </c>
       <c r="G152" s="3">
@@ -41233,27 +41239,27 @@
     </row>
     <row r="153">
       <c r="A153" s="3">
-        <f>Inputs!$A$206</f>
+        <f>Inputs!$A$207</f>
         <v/>
       </c>
       <c r="B153" s="3">
-        <f>Loads!$B$287</f>
+        <f>Loads!$B$288</f>
         <v/>
       </c>
       <c r="C153" s="3">
-        <f>Loads!$D$287</f>
+        <f>Loads!$D$288</f>
         <v/>
       </c>
       <c r="D153" s="3">
-        <f>Loads!$E$287</f>
+        <f>Loads!$E$288</f>
         <v/>
       </c>
       <c r="E153" s="3">
-        <f>Loads!$H$287</f>
+        <f>Loads!$H$288</f>
         <v/>
       </c>
       <c r="F153" s="3">
-        <f>Loads!$L$287</f>
+        <f>Loads!$L$288</f>
         <v/>
       </c>
       <c r="G153" s="3">
@@ -41267,27 +41273,27 @@
     </row>
     <row r="154">
       <c r="A154" s="3">
-        <f>Inputs!$A$207</f>
+        <f>Inputs!$A$208</f>
         <v/>
       </c>
       <c r="B154" s="3">
-        <f>Loads!$B$288</f>
+        <f>Loads!$B$289</f>
         <v/>
       </c>
       <c r="C154" s="3">
-        <f>Loads!$D$288</f>
+        <f>Loads!$D$289</f>
         <v/>
       </c>
       <c r="D154" s="3">
-        <f>Loads!$E$288</f>
+        <f>Loads!$E$289</f>
         <v/>
       </c>
       <c r="E154" s="3">
-        <f>Loads!$H$288</f>
+        <f>Loads!$H$289</f>
         <v/>
       </c>
       <c r="F154" s="3">
-        <f>Loads!$L$288</f>
+        <f>Loads!$L$289</f>
         <v/>
       </c>
       <c r="G154" s="3">
@@ -41301,27 +41307,27 @@
     </row>
     <row r="155">
       <c r="A155" s="3">
-        <f>Inputs!$A$208</f>
+        <f>Inputs!$A$209</f>
         <v/>
       </c>
       <c r="B155" s="3">
-        <f>Loads!$B$289</f>
+        <f>Loads!$B$290</f>
         <v/>
       </c>
       <c r="C155" s="3">
-        <f>Loads!$D$289</f>
+        <f>Loads!$D$290</f>
         <v/>
       </c>
       <c r="D155" s="3">
-        <f>Loads!$E$289</f>
+        <f>Loads!$E$290</f>
         <v/>
       </c>
       <c r="E155" s="3">
-        <f>Loads!$H$289</f>
+        <f>Loads!$H$290</f>
         <v/>
       </c>
       <c r="F155" s="3">
-        <f>Loads!$L$289</f>
+        <f>Loads!$L$290</f>
         <v/>
       </c>
       <c r="G155" s="3">
@@ -41335,27 +41341,27 @@
     </row>
     <row r="156">
       <c r="A156" s="3">
-        <f>Inputs!$A$209</f>
+        <f>Inputs!$A$210</f>
         <v/>
       </c>
       <c r="B156" s="3">
-        <f>Loads!$B$290</f>
+        <f>Loads!$B$291</f>
         <v/>
       </c>
       <c r="C156" s="3">
-        <f>Loads!$D$290</f>
+        <f>Loads!$D$291</f>
         <v/>
       </c>
       <c r="D156" s="3">
-        <f>Loads!$E$290</f>
+        <f>Loads!$E$291</f>
         <v/>
       </c>
       <c r="E156" s="3">
-        <f>Loads!$H$290</f>
+        <f>Loads!$H$291</f>
         <v/>
       </c>
       <c r="F156" s="3">
-        <f>Loads!$L$290</f>
+        <f>Loads!$L$291</f>
         <v/>
       </c>
       <c r="G156" s="3">
@@ -41369,27 +41375,27 @@
     </row>
     <row r="157">
       <c r="A157" s="3">
-        <f>Inputs!$A$210</f>
+        <f>Inputs!$A$211</f>
         <v/>
       </c>
       <c r="B157" s="3">
-        <f>Loads!$B$291</f>
+        <f>Loads!$B$292</f>
         <v/>
       </c>
       <c r="C157" s="3">
-        <f>Loads!$D$291</f>
+        <f>Loads!$D$292</f>
         <v/>
       </c>
       <c r="D157" s="3">
-        <f>Loads!$E$291</f>
+        <f>Loads!$E$292</f>
         <v/>
       </c>
       <c r="E157" s="3">
-        <f>Loads!$H$291</f>
+        <f>Loads!$H$292</f>
         <v/>
       </c>
       <c r="F157" s="3">
-        <f>Loads!$L$291</f>
+        <f>Loads!$L$292</f>
         <v/>
       </c>
       <c r="G157" s="3">
@@ -41403,27 +41409,27 @@
     </row>
     <row r="158">
       <c r="A158" s="3">
-        <f>Inputs!$A$211</f>
+        <f>Inputs!$A$212</f>
         <v/>
       </c>
       <c r="B158" s="3">
-        <f>Loads!$B$292</f>
+        <f>Loads!$B$293</f>
         <v/>
       </c>
       <c r="C158" s="3">
-        <f>Loads!$D$292</f>
+        <f>Loads!$D$293</f>
         <v/>
       </c>
       <c r="D158" s="3">
-        <f>Loads!$E$292</f>
+        <f>Loads!$E$293</f>
         <v/>
       </c>
       <c r="E158" s="3">
-        <f>Loads!$H$292</f>
+        <f>Loads!$H$293</f>
         <v/>
       </c>
       <c r="F158" s="3">
-        <f>Loads!$L$292</f>
+        <f>Loads!$L$293</f>
         <v/>
       </c>
       <c r="G158" s="3">
@@ -41437,27 +41443,27 @@
     </row>
     <row r="159">
       <c r="A159" s="3">
-        <f>Inputs!$A$212</f>
+        <f>Inputs!$A$213</f>
         <v/>
       </c>
       <c r="B159" s="3">
-        <f>Loads!$B$293</f>
+        <f>Loads!$B$294</f>
         <v/>
       </c>
       <c r="C159" s="3">
-        <f>Loads!$D$293</f>
+        <f>Loads!$D$294</f>
         <v/>
       </c>
       <c r="D159" s="3">
-        <f>Loads!$E$293</f>
+        <f>Loads!$E$294</f>
         <v/>
       </c>
       <c r="E159" s="3">
-        <f>Loads!$H$293</f>
+        <f>Loads!$H$294</f>
         <v/>
       </c>
       <c r="F159" s="3">
-        <f>Loads!$L$293</f>
+        <f>Loads!$L$294</f>
         <v/>
       </c>
       <c r="G159" s="3">
@@ -41471,27 +41477,27 @@
     </row>
     <row r="160">
       <c r="A160" s="3">
-        <f>Inputs!$A$213</f>
+        <f>Inputs!$A$214</f>
         <v/>
       </c>
       <c r="B160" s="3">
-        <f>Loads!$B$294</f>
+        <f>Loads!$B$295</f>
         <v/>
       </c>
       <c r="C160" s="3">
-        <f>Loads!$D$294</f>
+        <f>Loads!$D$295</f>
         <v/>
       </c>
       <c r="D160" s="3">
-        <f>Loads!$E$294</f>
+        <f>Loads!$E$295</f>
         <v/>
       </c>
       <c r="E160" s="3">
-        <f>Loads!$H$294</f>
+        <f>Loads!$H$295</f>
         <v/>
       </c>
       <c r="F160" s="3">
-        <f>Loads!$L$294</f>
+        <f>Loads!$L$295</f>
         <v/>
       </c>
       <c r="G160" s="3">
@@ -41505,27 +41511,27 @@
     </row>
     <row r="161">
       <c r="A161" s="3">
-        <f>Inputs!$A$214</f>
+        <f>Inputs!$A$215</f>
         <v/>
       </c>
       <c r="B161" s="3">
-        <f>Loads!$B$295</f>
+        <f>Loads!$B$296</f>
         <v/>
       </c>
       <c r="C161" s="3">
-        <f>Loads!$D$295</f>
+        <f>Loads!$D$296</f>
         <v/>
       </c>
       <c r="D161" s="3">
-        <f>Loads!$E$295</f>
+        <f>Loads!$E$296</f>
         <v/>
       </c>
       <c r="E161" s="3">
-        <f>Loads!$H$295</f>
+        <f>Loads!$H$296</f>
         <v/>
       </c>
       <c r="F161" s="3">
-        <f>Loads!$L$295</f>
+        <f>Loads!$L$296</f>
         <v/>
       </c>
       <c r="G161" s="3">
@@ -41539,27 +41545,27 @@
     </row>
     <row r="162">
       <c r="A162" s="3">
-        <f>Inputs!$A$215</f>
+        <f>Inputs!$A$216</f>
         <v/>
       </c>
       <c r="B162" s="3">
-        <f>Loads!$B$296</f>
+        <f>Loads!$B$297</f>
         <v/>
       </c>
       <c r="C162" s="3">
-        <f>Loads!$D$296</f>
+        <f>Loads!$D$297</f>
         <v/>
       </c>
       <c r="D162" s="3">
-        <f>Loads!$E$296</f>
+        <f>Loads!$E$297</f>
         <v/>
       </c>
       <c r="E162" s="3">
-        <f>Loads!$H$296</f>
+        <f>Loads!$H$297</f>
         <v/>
       </c>
       <c r="F162" s="3">
-        <f>Loads!$L$296</f>
+        <f>Loads!$L$297</f>
         <v/>
       </c>
       <c r="G162" s="3">
@@ -41573,27 +41579,27 @@
     </row>
     <row r="163">
       <c r="A163" s="3">
-        <f>Inputs!$A$216</f>
+        <f>Inputs!$A$217</f>
         <v/>
       </c>
       <c r="B163" s="3">
-        <f>Loads!$B$297</f>
+        <f>Loads!$B$298</f>
         <v/>
       </c>
       <c r="C163" s="3">
-        <f>Loads!$D$297</f>
+        <f>Loads!$D$298</f>
         <v/>
       </c>
       <c r="D163" s="3">
-        <f>Loads!$E$297</f>
+        <f>Loads!$E$298</f>
         <v/>
       </c>
       <c r="E163" s="3">
-        <f>Loads!$H$297</f>
+        <f>Loads!$H$298</f>
         <v/>
       </c>
       <c r="F163" s="3">
-        <f>Loads!$L$297</f>
+        <f>Loads!$L$298</f>
         <v/>
       </c>
       <c r="G163" s="3">
@@ -41605,1845 +41611,1701 @@
         <v/>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="3">
-        <f>Inputs!$A$217</f>
-        <v/>
-      </c>
-      <c r="B164" s="3">
-        <f>Loads!$B$298</f>
-        <v/>
-      </c>
-      <c r="C164" s="3">
-        <f>Loads!$D$298</f>
-        <v/>
-      </c>
-      <c r="D164" s="3">
-        <f>Loads!$E$298</f>
-        <v/>
-      </c>
-      <c r="E164" s="3">
-        <f>Loads!$H$298</f>
-        <v/>
-      </c>
-      <c r="F164" s="3">
-        <f>Loads!$L$298</f>
-        <v/>
-      </c>
-      <c r="G164" s="3">
-        <f>OutOfPlane!$E$164+OutOfPlane!$F$164</f>
-        <v/>
-      </c>
-      <c r="H164" s="3">
-        <f>-OutOfPlane!$G$164*(OutOfPlane!$B$13-OutOfPlane!$B$14*(OutOfPlane!$D$164-OutOfPlane!$B$12))</f>
-        <v/>
+    <row r="167">
+      <c r="A167" s="6" t="inlineStr">
+        <is>
+          <t>Wind areas, Y wind (row i = Inputs wind areas row i)</t>
+        </is>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="6" t="inlineStr">
-        <is>
-          <t>Wind areas, Y wind (row i = Inputs wind areas row i)</t>
+      <c r="A168" s="8" t="inlineStr">
+        <is>
+          <t>Active [1/0]</t>
+        </is>
+      </c>
+      <c r="B168" s="8" t="inlineStr">
+        <is>
+          <t>Body</t>
+        </is>
+      </c>
+      <c r="C168" s="8" t="inlineStr">
+        <is>
+          <t>Frame</t>
+        </is>
+      </c>
+      <c r="D168" s="8" t="inlineStr">
+        <is>
+          <t>x global [m]</t>
+        </is>
+      </c>
+      <c r="E168" s="8" t="inlineStr">
+        <is>
+          <t>z global [m]</t>
+        </is>
+      </c>
+      <c r="F168" s="8" t="inlineStr">
+        <is>
+          <t>Cd</t>
+        </is>
+      </c>
+      <c r="G168" s="8" t="inlineStr">
+        <is>
+          <t>Area for Y wind [m^2]</t>
+        </is>
+      </c>
+      <c r="H168" s="8" t="inlineStr">
+        <is>
+          <t>Wind Fy = sign q Cd A_y [kN]</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="8" t="inlineStr">
-        <is>
-          <t>Active [1/0]</t>
-        </is>
-      </c>
-      <c r="B169" s="8" t="inlineStr">
-        <is>
-          <t>Body</t>
-        </is>
-      </c>
-      <c r="C169" s="8" t="inlineStr">
-        <is>
-          <t>Frame</t>
-        </is>
-      </c>
-      <c r="D169" s="8" t="inlineStr">
-        <is>
-          <t>x global [m]</t>
-        </is>
-      </c>
-      <c r="E169" s="8" t="inlineStr">
-        <is>
-          <t>z global [m]</t>
-        </is>
-      </c>
-      <c r="F169" s="8" t="inlineStr">
-        <is>
-          <t>Cd</t>
-        </is>
-      </c>
-      <c r="G169" s="8" t="inlineStr">
-        <is>
-          <t>Area for Y wind [m^2]</t>
-        </is>
-      </c>
-      <c r="H169" s="8" t="inlineStr">
-        <is>
-          <t>Area scale</t>
-        </is>
-      </c>
-      <c r="I169" s="8" t="inlineStr">
-        <is>
-          <t>Wind Fy = sign q Cd A_y scale [kN]</t>
+      <c r="A169" s="7" t="inlineStr">
+        <is>
+          <t>active (from Inputs)</t>
+        </is>
+      </c>
+      <c r="B169" s="7" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="C169" s="7" t="inlineStr">
+        <is>
+          <t>frame</t>
+        </is>
+      </c>
+      <c r="D169" s="7" t="inlineStr">
+        <is>
+          <t>x_m (Loads)</t>
+        </is>
+      </c>
+      <c r="E169" s="7" t="inlineStr">
+        <is>
+          <t>z_m (Loads)</t>
+        </is>
+      </c>
+      <c r="F169" s="7" t="inlineStr">
+        <is>
+          <t>cd</t>
+        </is>
+      </c>
+      <c r="G169" s="7" t="inlineStr">
+        <is>
+          <t>area_y_m2 (not scaled by the boom angle)</t>
+        </is>
+      </c>
+      <c r="H169" s="7" t="inlineStr">
+        <is>
+          <t>fy_kN</t>
         </is>
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="7" t="inlineStr">
-        <is>
-          <t>active (from Inputs)</t>
-        </is>
-      </c>
-      <c r="B170" s="7" t="inlineStr">
-        <is>
-          <t>body</t>
-        </is>
-      </c>
-      <c r="C170" s="7" t="inlineStr">
-        <is>
-          <t>frame</t>
-        </is>
-      </c>
-      <c r="D170" s="7" t="inlineStr">
-        <is>
-          <t>x_m (Loads)</t>
-        </is>
-      </c>
-      <c r="E170" s="7" t="inlineStr">
-        <is>
-          <t>z_m (Loads)</t>
-        </is>
-      </c>
-      <c r="F170" s="7" t="inlineStr">
-        <is>
-          <t>cd</t>
-        </is>
-      </c>
-      <c r="G170" s="7" t="inlineStr">
-        <is>
-          <t>area_y_m2</t>
-        </is>
-      </c>
-      <c r="H170" s="7" t="inlineStr">
-        <is>
-          <t>scale (|sin(boom angle)| if boom-local, else 1)</t>
-        </is>
-      </c>
-      <c r="I170" s="7" t="inlineStr">
-        <is>
-          <t>fy_kN</t>
-        </is>
+      <c r="A170" s="3">
+        <f>Inputs!$A$92</f>
+        <v/>
+      </c>
+      <c r="B170" s="3">
+        <f>Loads!$B$79</f>
+        <v/>
+      </c>
+      <c r="C170" s="3">
+        <f>IF(OutOfPlane!$A$170=1,Inputs!$D$92&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="D170" s="3">
+        <f>Loads!$C$79</f>
+        <v/>
+      </c>
+      <c r="E170" s="3">
+        <f>Loads!$D$79</f>
+        <v/>
+      </c>
+      <c r="F170" s="3">
+        <f>IF(OutOfPlane!$A$170=1,Inputs!$E$92+0,0)</f>
+        <v/>
+      </c>
+      <c r="G170" s="3">
+        <f>IF(OutOfPlane!$A$170=1,Inputs!$G$92+0,0)</f>
+        <v/>
+      </c>
+      <c r="H170" s="3">
+        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$170*OutOfPlane!$G$170</f>
+        <v/>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="3">
-        <f>Inputs!$A$92</f>
+        <f>Inputs!$A$93</f>
         <v/>
       </c>
       <c r="B171" s="3">
-        <f>Loads!$B$79</f>
+        <f>Loads!$B$80</f>
         <v/>
       </c>
       <c r="C171" s="3">
-        <f>IF(OutOfPlane!$A$171=1,Inputs!$D$92&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$171=1,Inputs!$D$93&amp;"","")</f>
         <v/>
       </c>
       <c r="D171" s="3">
-        <f>Loads!$C$79</f>
+        <f>Loads!$C$80</f>
         <v/>
       </c>
       <c r="E171" s="3">
-        <f>Loads!$D$79</f>
+        <f>Loads!$D$80</f>
         <v/>
       </c>
       <c r="F171" s="3">
-        <f>IF(OutOfPlane!$A$171=1,Inputs!$E$92+0,0)</f>
+        <f>IF(OutOfPlane!$A$171=1,Inputs!$E$93+0,0)</f>
         <v/>
       </c>
       <c r="G171" s="3">
-        <f>IF(OutOfPlane!$A$171=1,Inputs!$G$92+0,0)</f>
+        <f>IF(OutOfPlane!$A$171=1,Inputs!$G$93+0,0)</f>
         <v/>
       </c>
       <c r="H171" s="3">
-        <f>IF(OutOfPlane!$A$171=1,IF(OutOfPlane!$C$171="boom_local",OutOfPlane!$B$17,1),0)</f>
-        <v/>
-      </c>
-      <c r="I171" s="3">
-        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$171*OutOfPlane!$G$171*OutOfPlane!$H$171</f>
+        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$171*OutOfPlane!$G$171</f>
         <v/>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="3">
-        <f>Inputs!$A$93</f>
+        <f>Inputs!$A$94</f>
         <v/>
       </c>
       <c r="B172" s="3">
-        <f>Loads!$B$80</f>
+        <f>Loads!$B$81</f>
         <v/>
       </c>
       <c r="C172" s="3">
-        <f>IF(OutOfPlane!$A$172=1,Inputs!$D$93&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$172=1,Inputs!$D$94&amp;"","")</f>
         <v/>
       </c>
       <c r="D172" s="3">
-        <f>Loads!$C$80</f>
+        <f>Loads!$C$81</f>
         <v/>
       </c>
       <c r="E172" s="3">
-        <f>Loads!$D$80</f>
+        <f>Loads!$D$81</f>
         <v/>
       </c>
       <c r="F172" s="3">
-        <f>IF(OutOfPlane!$A$172=1,Inputs!$E$93+0,0)</f>
+        <f>IF(OutOfPlane!$A$172=1,Inputs!$E$94+0,0)</f>
         <v/>
       </c>
       <c r="G172" s="3">
-        <f>IF(OutOfPlane!$A$172=1,Inputs!$G$93+0,0)</f>
+        <f>IF(OutOfPlane!$A$172=1,Inputs!$G$94+0,0)</f>
         <v/>
       </c>
       <c r="H172" s="3">
-        <f>IF(OutOfPlane!$A$172=1,IF(OutOfPlane!$C$172="boom_local",OutOfPlane!$B$17,1),0)</f>
-        <v/>
-      </c>
-      <c r="I172" s="3">
-        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$172*OutOfPlane!$G$172*OutOfPlane!$H$172</f>
+        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$172*OutOfPlane!$G$172</f>
         <v/>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="3">
-        <f>Inputs!$A$94</f>
+        <f>Inputs!$A$95</f>
         <v/>
       </c>
       <c r="B173" s="3">
-        <f>Loads!$B$81</f>
+        <f>Loads!$B$82</f>
         <v/>
       </c>
       <c r="C173" s="3">
-        <f>IF(OutOfPlane!$A$173=1,Inputs!$D$94&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$173=1,Inputs!$D$95&amp;"","")</f>
         <v/>
       </c>
       <c r="D173" s="3">
-        <f>Loads!$C$81</f>
+        <f>Loads!$C$82</f>
         <v/>
       </c>
       <c r="E173" s="3">
-        <f>Loads!$D$81</f>
+        <f>Loads!$D$82</f>
         <v/>
       </c>
       <c r="F173" s="3">
-        <f>IF(OutOfPlane!$A$173=1,Inputs!$E$94+0,0)</f>
+        <f>IF(OutOfPlane!$A$173=1,Inputs!$E$95+0,0)</f>
         <v/>
       </c>
       <c r="G173" s="3">
-        <f>IF(OutOfPlane!$A$173=1,Inputs!$G$94+0,0)</f>
+        <f>IF(OutOfPlane!$A$173=1,Inputs!$G$95+0,0)</f>
         <v/>
       </c>
       <c r="H173" s="3">
-        <f>IF(OutOfPlane!$A$173=1,IF(OutOfPlane!$C$173="boom_local",OutOfPlane!$B$17,1),0)</f>
-        <v/>
-      </c>
-      <c r="I173" s="3">
-        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$173*OutOfPlane!$G$173*OutOfPlane!$H$173</f>
+        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$173*OutOfPlane!$G$173</f>
         <v/>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="3">
-        <f>Inputs!$A$95</f>
+        <f>Inputs!$A$96</f>
         <v/>
       </c>
       <c r="B174" s="3">
-        <f>Loads!$B$82</f>
+        <f>Loads!$B$83</f>
         <v/>
       </c>
       <c r="C174" s="3">
-        <f>IF(OutOfPlane!$A$174=1,Inputs!$D$95&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$174=1,Inputs!$D$96&amp;"","")</f>
         <v/>
       </c>
       <c r="D174" s="3">
-        <f>Loads!$C$82</f>
+        <f>Loads!$C$83</f>
         <v/>
       </c>
       <c r="E174" s="3">
-        <f>Loads!$D$82</f>
+        <f>Loads!$D$83</f>
         <v/>
       </c>
       <c r="F174" s="3">
-        <f>IF(OutOfPlane!$A$174=1,Inputs!$E$95+0,0)</f>
+        <f>IF(OutOfPlane!$A$174=1,Inputs!$E$96+0,0)</f>
         <v/>
       </c>
       <c r="G174" s="3">
-        <f>IF(OutOfPlane!$A$174=1,Inputs!$G$95+0,0)</f>
+        <f>IF(OutOfPlane!$A$174=1,Inputs!$G$96+0,0)</f>
         <v/>
       </c>
       <c r="H174" s="3">
-        <f>IF(OutOfPlane!$A$174=1,IF(OutOfPlane!$C$174="boom_local",OutOfPlane!$B$17,1),0)</f>
-        <v/>
-      </c>
-      <c r="I174" s="3">
-        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$174*OutOfPlane!$G$174*OutOfPlane!$H$174</f>
+        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$174*OutOfPlane!$G$174</f>
         <v/>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="3">
-        <f>Inputs!$A$96</f>
+        <f>Inputs!$A$97</f>
         <v/>
       </c>
       <c r="B175" s="3">
-        <f>Loads!$B$83</f>
+        <f>Loads!$B$84</f>
         <v/>
       </c>
       <c r="C175" s="3">
-        <f>IF(OutOfPlane!$A$175=1,Inputs!$D$96&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$175=1,Inputs!$D$97&amp;"","")</f>
         <v/>
       </c>
       <c r="D175" s="3">
-        <f>Loads!$C$83</f>
+        <f>Loads!$C$84</f>
         <v/>
       </c>
       <c r="E175" s="3">
-        <f>Loads!$D$83</f>
+        <f>Loads!$D$84</f>
         <v/>
       </c>
       <c r="F175" s="3">
-        <f>IF(OutOfPlane!$A$175=1,Inputs!$E$96+0,0)</f>
+        <f>IF(OutOfPlane!$A$175=1,Inputs!$E$97+0,0)</f>
         <v/>
       </c>
       <c r="G175" s="3">
-        <f>IF(OutOfPlane!$A$175=1,Inputs!$G$96+0,0)</f>
+        <f>IF(OutOfPlane!$A$175=1,Inputs!$G$97+0,0)</f>
         <v/>
       </c>
       <c r="H175" s="3">
-        <f>IF(OutOfPlane!$A$175=1,IF(OutOfPlane!$C$175="boom_local",OutOfPlane!$B$17,1),0)</f>
-        <v/>
-      </c>
-      <c r="I175" s="3">
-        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$175*OutOfPlane!$G$175*OutOfPlane!$H$175</f>
+        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$175*OutOfPlane!$G$175</f>
         <v/>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="3">
-        <f>Inputs!$A$97</f>
+        <f>Inputs!$A$98</f>
         <v/>
       </c>
       <c r="B176" s="3">
-        <f>Loads!$B$84</f>
+        <f>Loads!$B$85</f>
         <v/>
       </c>
       <c r="C176" s="3">
-        <f>IF(OutOfPlane!$A$176=1,Inputs!$D$97&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$176=1,Inputs!$D$98&amp;"","")</f>
         <v/>
       </c>
       <c r="D176" s="3">
-        <f>Loads!$C$84</f>
+        <f>Loads!$C$85</f>
         <v/>
       </c>
       <c r="E176" s="3">
-        <f>Loads!$D$84</f>
+        <f>Loads!$D$85</f>
         <v/>
       </c>
       <c r="F176" s="3">
-        <f>IF(OutOfPlane!$A$176=1,Inputs!$E$97+0,0)</f>
+        <f>IF(OutOfPlane!$A$176=1,Inputs!$E$98+0,0)</f>
         <v/>
       </c>
       <c r="G176" s="3">
-        <f>IF(OutOfPlane!$A$176=1,Inputs!$G$97+0,0)</f>
+        <f>IF(OutOfPlane!$A$176=1,Inputs!$G$98+0,0)</f>
         <v/>
       </c>
       <c r="H176" s="3">
-        <f>IF(OutOfPlane!$A$176=1,IF(OutOfPlane!$C$176="boom_local",OutOfPlane!$B$17,1),0)</f>
-        <v/>
-      </c>
-      <c r="I176" s="3">
-        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$176*OutOfPlane!$G$176*OutOfPlane!$H$176</f>
+        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$176*OutOfPlane!$G$176</f>
         <v/>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="3">
-        <f>Inputs!$A$98</f>
+        <f>Inputs!$A$99</f>
         <v/>
       </c>
       <c r="B177" s="3">
-        <f>Loads!$B$85</f>
+        <f>Loads!$B$86</f>
         <v/>
       </c>
       <c r="C177" s="3">
-        <f>IF(OutOfPlane!$A$177=1,Inputs!$D$98&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$177=1,Inputs!$D$99&amp;"","")</f>
         <v/>
       </c>
       <c r="D177" s="3">
-        <f>Loads!$C$85</f>
+        <f>Loads!$C$86</f>
         <v/>
       </c>
       <c r="E177" s="3">
-        <f>Loads!$D$85</f>
+        <f>Loads!$D$86</f>
         <v/>
       </c>
       <c r="F177" s="3">
-        <f>IF(OutOfPlane!$A$177=1,Inputs!$E$98+0,0)</f>
+        <f>IF(OutOfPlane!$A$177=1,Inputs!$E$99+0,0)</f>
         <v/>
       </c>
       <c r="G177" s="3">
-        <f>IF(OutOfPlane!$A$177=1,Inputs!$G$98+0,0)</f>
+        <f>IF(OutOfPlane!$A$177=1,Inputs!$G$99+0,0)</f>
         <v/>
       </c>
       <c r="H177" s="3">
-        <f>IF(OutOfPlane!$A$177=1,IF(OutOfPlane!$C$177="boom_local",OutOfPlane!$B$17,1),0)</f>
-        <v/>
-      </c>
-      <c r="I177" s="3">
-        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$177*OutOfPlane!$G$177*OutOfPlane!$H$177</f>
+        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$177*OutOfPlane!$G$177</f>
         <v/>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="3">
-        <f>Inputs!$A$99</f>
+        <f>Inputs!$A$100</f>
         <v/>
       </c>
       <c r="B178" s="3">
-        <f>Loads!$B$86</f>
+        <f>Loads!$B$87</f>
         <v/>
       </c>
       <c r="C178" s="3">
-        <f>IF(OutOfPlane!$A$178=1,Inputs!$D$99&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$178=1,Inputs!$D$100&amp;"","")</f>
         <v/>
       </c>
       <c r="D178" s="3">
-        <f>Loads!$C$86</f>
+        <f>Loads!$C$87</f>
         <v/>
       </c>
       <c r="E178" s="3">
-        <f>Loads!$D$86</f>
+        <f>Loads!$D$87</f>
         <v/>
       </c>
       <c r="F178" s="3">
-        <f>IF(OutOfPlane!$A$178=1,Inputs!$E$99+0,0)</f>
+        <f>IF(OutOfPlane!$A$178=1,Inputs!$E$100+0,0)</f>
         <v/>
       </c>
       <c r="G178" s="3">
-        <f>IF(OutOfPlane!$A$178=1,Inputs!$G$99+0,0)</f>
+        <f>IF(OutOfPlane!$A$178=1,Inputs!$G$100+0,0)</f>
         <v/>
       </c>
       <c r="H178" s="3">
-        <f>IF(OutOfPlane!$A$178=1,IF(OutOfPlane!$C$178="boom_local",OutOfPlane!$B$17,1),0)</f>
-        <v/>
-      </c>
-      <c r="I178" s="3">
-        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$178*OutOfPlane!$G$178*OutOfPlane!$H$178</f>
+        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$178*OutOfPlane!$G$178</f>
         <v/>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="3">
-        <f>Inputs!$A$100</f>
+        <f>Inputs!$A$101</f>
         <v/>
       </c>
       <c r="B179" s="3">
-        <f>Loads!$B$87</f>
+        <f>Loads!$B$88</f>
         <v/>
       </c>
       <c r="C179" s="3">
-        <f>IF(OutOfPlane!$A$179=1,Inputs!$D$100&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$179=1,Inputs!$D$101&amp;"","")</f>
         <v/>
       </c>
       <c r="D179" s="3">
-        <f>Loads!$C$87</f>
+        <f>Loads!$C$88</f>
         <v/>
       </c>
       <c r="E179" s="3">
-        <f>Loads!$D$87</f>
+        <f>Loads!$D$88</f>
         <v/>
       </c>
       <c r="F179" s="3">
-        <f>IF(OutOfPlane!$A$179=1,Inputs!$E$100+0,0)</f>
+        <f>IF(OutOfPlane!$A$179=1,Inputs!$E$101+0,0)</f>
         <v/>
       </c>
       <c r="G179" s="3">
-        <f>IF(OutOfPlane!$A$179=1,Inputs!$G$100+0,0)</f>
+        <f>IF(OutOfPlane!$A$179=1,Inputs!$G$101+0,0)</f>
         <v/>
       </c>
       <c r="H179" s="3">
-        <f>IF(OutOfPlane!$A$179=1,IF(OutOfPlane!$C$179="boom_local",OutOfPlane!$B$17,1),0)</f>
-        <v/>
-      </c>
-      <c r="I179" s="3">
-        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$179*OutOfPlane!$G$179*OutOfPlane!$H$179</f>
+        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$179*OutOfPlane!$G$179</f>
         <v/>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="3">
-        <f>Inputs!$A$101</f>
+        <f>Inputs!$A$102</f>
         <v/>
       </c>
       <c r="B180" s="3">
-        <f>Loads!$B$88</f>
+        <f>Loads!$B$89</f>
         <v/>
       </c>
       <c r="C180" s="3">
-        <f>IF(OutOfPlane!$A$180=1,Inputs!$D$101&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$180=1,Inputs!$D$102&amp;"","")</f>
         <v/>
       </c>
       <c r="D180" s="3">
-        <f>Loads!$C$88</f>
+        <f>Loads!$C$89</f>
         <v/>
       </c>
       <c r="E180" s="3">
-        <f>Loads!$D$88</f>
+        <f>Loads!$D$89</f>
         <v/>
       </c>
       <c r="F180" s="3">
-        <f>IF(OutOfPlane!$A$180=1,Inputs!$E$101+0,0)</f>
+        <f>IF(OutOfPlane!$A$180=1,Inputs!$E$102+0,0)</f>
         <v/>
       </c>
       <c r="G180" s="3">
-        <f>IF(OutOfPlane!$A$180=1,Inputs!$G$101+0,0)</f>
+        <f>IF(OutOfPlane!$A$180=1,Inputs!$G$102+0,0)</f>
         <v/>
       </c>
       <c r="H180" s="3">
-        <f>IF(OutOfPlane!$A$180=1,IF(OutOfPlane!$C$180="boom_local",OutOfPlane!$B$17,1),0)</f>
-        <v/>
-      </c>
-      <c r="I180" s="3">
-        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$180*OutOfPlane!$G$180*OutOfPlane!$H$180</f>
+        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$180*OutOfPlane!$G$180</f>
         <v/>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="3">
-        <f>Inputs!$A$102</f>
+        <f>Inputs!$A$103</f>
         <v/>
       </c>
       <c r="B181" s="3">
-        <f>Loads!$B$89</f>
+        <f>Loads!$B$90</f>
         <v/>
       </c>
       <c r="C181" s="3">
-        <f>IF(OutOfPlane!$A$181=1,Inputs!$D$102&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$181=1,Inputs!$D$103&amp;"","")</f>
         <v/>
       </c>
       <c r="D181" s="3">
-        <f>Loads!$C$89</f>
+        <f>Loads!$C$90</f>
         <v/>
       </c>
       <c r="E181" s="3">
-        <f>Loads!$D$89</f>
+        <f>Loads!$D$90</f>
         <v/>
       </c>
       <c r="F181" s="3">
-        <f>IF(OutOfPlane!$A$181=1,Inputs!$E$102+0,0)</f>
+        <f>IF(OutOfPlane!$A$181=1,Inputs!$E$103+0,0)</f>
         <v/>
       </c>
       <c r="G181" s="3">
-        <f>IF(OutOfPlane!$A$181=1,Inputs!$G$102+0,0)</f>
+        <f>IF(OutOfPlane!$A$181=1,Inputs!$G$103+0,0)</f>
         <v/>
       </c>
       <c r="H181" s="3">
-        <f>IF(OutOfPlane!$A$181=1,IF(OutOfPlane!$C$181="boom_local",OutOfPlane!$B$17,1),0)</f>
-        <v/>
-      </c>
-      <c r="I181" s="3">
-        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$181*OutOfPlane!$G$181*OutOfPlane!$H$181</f>
+        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$181*OutOfPlane!$G$181</f>
         <v/>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="3">
-        <f>Inputs!$A$103</f>
+        <f>Inputs!$A$104</f>
         <v/>
       </c>
       <c r="B182" s="3">
-        <f>Loads!$B$90</f>
+        <f>Loads!$B$91</f>
         <v/>
       </c>
       <c r="C182" s="3">
-        <f>IF(OutOfPlane!$A$182=1,Inputs!$D$103&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$182=1,Inputs!$D$104&amp;"","")</f>
         <v/>
       </c>
       <c r="D182" s="3">
-        <f>Loads!$C$90</f>
+        <f>Loads!$C$91</f>
         <v/>
       </c>
       <c r="E182" s="3">
-        <f>Loads!$D$90</f>
+        <f>Loads!$D$91</f>
         <v/>
       </c>
       <c r="F182" s="3">
-        <f>IF(OutOfPlane!$A$182=1,Inputs!$E$103+0,0)</f>
+        <f>IF(OutOfPlane!$A$182=1,Inputs!$E$104+0,0)</f>
         <v/>
       </c>
       <c r="G182" s="3">
-        <f>IF(OutOfPlane!$A$182=1,Inputs!$G$103+0,0)</f>
+        <f>IF(OutOfPlane!$A$182=1,Inputs!$G$104+0,0)</f>
         <v/>
       </c>
       <c r="H182" s="3">
-        <f>IF(OutOfPlane!$A$182=1,IF(OutOfPlane!$C$182="boom_local",OutOfPlane!$B$17,1),0)</f>
-        <v/>
-      </c>
-      <c r="I182" s="3">
-        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$182*OutOfPlane!$G$182*OutOfPlane!$H$182</f>
+        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$182*OutOfPlane!$G$182</f>
         <v/>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="3">
-        <f>Inputs!$A$104</f>
+        <f>Inputs!$A$105</f>
         <v/>
       </c>
       <c r="B183" s="3">
-        <f>Loads!$B$91</f>
+        <f>Loads!$B$92</f>
         <v/>
       </c>
       <c r="C183" s="3">
-        <f>IF(OutOfPlane!$A$183=1,Inputs!$D$104&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$183=1,Inputs!$D$105&amp;"","")</f>
         <v/>
       </c>
       <c r="D183" s="3">
-        <f>Loads!$C$91</f>
+        <f>Loads!$C$92</f>
         <v/>
       </c>
       <c r="E183" s="3">
-        <f>Loads!$D$91</f>
+        <f>Loads!$D$92</f>
         <v/>
       </c>
       <c r="F183" s="3">
-        <f>IF(OutOfPlane!$A$183=1,Inputs!$E$104+0,0)</f>
+        <f>IF(OutOfPlane!$A$183=1,Inputs!$E$105+0,0)</f>
         <v/>
       </c>
       <c r="G183" s="3">
-        <f>IF(OutOfPlane!$A$183=1,Inputs!$G$104+0,0)</f>
+        <f>IF(OutOfPlane!$A$183=1,Inputs!$G$105+0,0)</f>
         <v/>
       </c>
       <c r="H183" s="3">
-        <f>IF(OutOfPlane!$A$183=1,IF(OutOfPlane!$C$183="boom_local",OutOfPlane!$B$17,1),0)</f>
-        <v/>
-      </c>
-      <c r="I183" s="3">
-        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$183*OutOfPlane!$G$183*OutOfPlane!$H$183</f>
+        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$183*OutOfPlane!$G$183</f>
         <v/>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="3">
-        <f>Inputs!$A$105</f>
+        <f>Inputs!$A$106</f>
         <v/>
       </c>
       <c r="B184" s="3">
-        <f>Loads!$B$92</f>
+        <f>Loads!$B$93</f>
         <v/>
       </c>
       <c r="C184" s="3">
-        <f>IF(OutOfPlane!$A$184=1,Inputs!$D$105&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$184=1,Inputs!$D$106&amp;"","")</f>
         <v/>
       </c>
       <c r="D184" s="3">
-        <f>Loads!$C$92</f>
+        <f>Loads!$C$93</f>
         <v/>
       </c>
       <c r="E184" s="3">
-        <f>Loads!$D$92</f>
+        <f>Loads!$D$93</f>
         <v/>
       </c>
       <c r="F184" s="3">
-        <f>IF(OutOfPlane!$A$184=1,Inputs!$E$105+0,0)</f>
+        <f>IF(OutOfPlane!$A$184=1,Inputs!$E$106+0,0)</f>
         <v/>
       </c>
       <c r="G184" s="3">
-        <f>IF(OutOfPlane!$A$184=1,Inputs!$G$105+0,0)</f>
+        <f>IF(OutOfPlane!$A$184=1,Inputs!$G$106+0,0)</f>
         <v/>
       </c>
       <c r="H184" s="3">
-        <f>IF(OutOfPlane!$A$184=1,IF(OutOfPlane!$C$184="boom_local",OutOfPlane!$B$17,1),0)</f>
-        <v/>
-      </c>
-      <c r="I184" s="3">
-        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$184*OutOfPlane!$G$184*OutOfPlane!$H$184</f>
+        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$184*OutOfPlane!$G$184</f>
         <v/>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="3">
-        <f>Inputs!$A$106</f>
+        <f>Inputs!$A$107</f>
         <v/>
       </c>
       <c r="B185" s="3">
-        <f>Loads!$B$93</f>
+        <f>Loads!$B$94</f>
         <v/>
       </c>
       <c r="C185" s="3">
-        <f>IF(OutOfPlane!$A$185=1,Inputs!$D$106&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$185=1,Inputs!$D$107&amp;"","")</f>
         <v/>
       </c>
       <c r="D185" s="3">
-        <f>Loads!$C$93</f>
+        <f>Loads!$C$94</f>
         <v/>
       </c>
       <c r="E185" s="3">
-        <f>Loads!$D$93</f>
+        <f>Loads!$D$94</f>
         <v/>
       </c>
       <c r="F185" s="3">
-        <f>IF(OutOfPlane!$A$185=1,Inputs!$E$106+0,0)</f>
+        <f>IF(OutOfPlane!$A$185=1,Inputs!$E$107+0,0)</f>
         <v/>
       </c>
       <c r="G185" s="3">
-        <f>IF(OutOfPlane!$A$185=1,Inputs!$G$106+0,0)</f>
+        <f>IF(OutOfPlane!$A$185=1,Inputs!$G$107+0,0)</f>
         <v/>
       </c>
       <c r="H185" s="3">
-        <f>IF(OutOfPlane!$A$185=1,IF(OutOfPlane!$C$185="boom_local",OutOfPlane!$B$17,1),0)</f>
-        <v/>
-      </c>
-      <c r="I185" s="3">
-        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$185*OutOfPlane!$G$185*OutOfPlane!$H$185</f>
+        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$185*OutOfPlane!$G$185</f>
         <v/>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="3">
-        <f>Inputs!$A$107</f>
+        <f>Inputs!$A$108</f>
         <v/>
       </c>
       <c r="B186" s="3">
-        <f>Loads!$B$94</f>
+        <f>Loads!$B$95</f>
         <v/>
       </c>
       <c r="C186" s="3">
-        <f>IF(OutOfPlane!$A$186=1,Inputs!$D$107&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$186=1,Inputs!$D$108&amp;"","")</f>
         <v/>
       </c>
       <c r="D186" s="3">
-        <f>Loads!$C$94</f>
+        <f>Loads!$C$95</f>
         <v/>
       </c>
       <c r="E186" s="3">
-        <f>Loads!$D$94</f>
+        <f>Loads!$D$95</f>
         <v/>
       </c>
       <c r="F186" s="3">
-        <f>IF(OutOfPlane!$A$186=1,Inputs!$E$107+0,0)</f>
+        <f>IF(OutOfPlane!$A$186=1,Inputs!$E$108+0,0)</f>
         <v/>
       </c>
       <c r="G186" s="3">
-        <f>IF(OutOfPlane!$A$186=1,Inputs!$G$107+0,0)</f>
+        <f>IF(OutOfPlane!$A$186=1,Inputs!$G$108+0,0)</f>
         <v/>
       </c>
       <c r="H186" s="3">
-        <f>IF(OutOfPlane!$A$186=1,IF(OutOfPlane!$C$186="boom_local",OutOfPlane!$B$17,1),0)</f>
-        <v/>
-      </c>
-      <c r="I186" s="3">
-        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$186*OutOfPlane!$G$186*OutOfPlane!$H$186</f>
+        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$186*OutOfPlane!$G$186</f>
         <v/>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="3">
-        <f>Inputs!$A$108</f>
+        <f>Inputs!$A$109</f>
         <v/>
       </c>
       <c r="B187" s="3">
-        <f>Loads!$B$95</f>
+        <f>Loads!$B$96</f>
         <v/>
       </c>
       <c r="C187" s="3">
-        <f>IF(OutOfPlane!$A$187=1,Inputs!$D$108&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$187=1,Inputs!$D$109&amp;"","")</f>
         <v/>
       </c>
       <c r="D187" s="3">
-        <f>Loads!$C$95</f>
+        <f>Loads!$C$96</f>
         <v/>
       </c>
       <c r="E187" s="3">
-        <f>Loads!$D$95</f>
+        <f>Loads!$D$96</f>
         <v/>
       </c>
       <c r="F187" s="3">
-        <f>IF(OutOfPlane!$A$187=1,Inputs!$E$108+0,0)</f>
+        <f>IF(OutOfPlane!$A$187=1,Inputs!$E$109+0,0)</f>
         <v/>
       </c>
       <c r="G187" s="3">
-        <f>IF(OutOfPlane!$A$187=1,Inputs!$G$108+0,0)</f>
+        <f>IF(OutOfPlane!$A$187=1,Inputs!$G$109+0,0)</f>
         <v/>
       </c>
       <c r="H187" s="3">
-        <f>IF(OutOfPlane!$A$187=1,IF(OutOfPlane!$C$187="boom_local",OutOfPlane!$B$17,1),0)</f>
-        <v/>
-      </c>
-      <c r="I187" s="3">
-        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$187*OutOfPlane!$G$187*OutOfPlane!$H$187</f>
+        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$187*OutOfPlane!$G$187</f>
         <v/>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="3">
-        <f>Inputs!$A$109</f>
+        <f>Inputs!$A$110</f>
         <v/>
       </c>
       <c r="B188" s="3">
-        <f>Loads!$B$96</f>
+        <f>Loads!$B$97</f>
         <v/>
       </c>
       <c r="C188" s="3">
-        <f>IF(OutOfPlane!$A$188=1,Inputs!$D$109&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$188=1,Inputs!$D$110&amp;"","")</f>
         <v/>
       </c>
       <c r="D188" s="3">
-        <f>Loads!$C$96</f>
+        <f>Loads!$C$97</f>
         <v/>
       </c>
       <c r="E188" s="3">
-        <f>Loads!$D$96</f>
+        <f>Loads!$D$97</f>
         <v/>
       </c>
       <c r="F188" s="3">
-        <f>IF(OutOfPlane!$A$188=1,Inputs!$E$109+0,0)</f>
+        <f>IF(OutOfPlane!$A$188=1,Inputs!$E$110+0,0)</f>
         <v/>
       </c>
       <c r="G188" s="3">
-        <f>IF(OutOfPlane!$A$188=1,Inputs!$G$109+0,0)</f>
+        <f>IF(OutOfPlane!$A$188=1,Inputs!$G$110+0,0)</f>
         <v/>
       </c>
       <c r="H188" s="3">
-        <f>IF(OutOfPlane!$A$188=1,IF(OutOfPlane!$C$188="boom_local",OutOfPlane!$B$17,1),0)</f>
-        <v/>
-      </c>
-      <c r="I188" s="3">
-        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$188*OutOfPlane!$G$188*OutOfPlane!$H$188</f>
+        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$188*OutOfPlane!$G$188</f>
         <v/>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="3">
-        <f>Inputs!$A$110</f>
+        <f>Inputs!$A$111</f>
         <v/>
       </c>
       <c r="B189" s="3">
-        <f>Loads!$B$97</f>
+        <f>Loads!$B$98</f>
         <v/>
       </c>
       <c r="C189" s="3">
-        <f>IF(OutOfPlane!$A$189=1,Inputs!$D$110&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$189=1,Inputs!$D$111&amp;"","")</f>
         <v/>
       </c>
       <c r="D189" s="3">
-        <f>Loads!$C$97</f>
+        <f>Loads!$C$98</f>
         <v/>
       </c>
       <c r="E189" s="3">
-        <f>Loads!$D$97</f>
+        <f>Loads!$D$98</f>
         <v/>
       </c>
       <c r="F189" s="3">
-        <f>IF(OutOfPlane!$A$189=1,Inputs!$E$110+0,0)</f>
+        <f>IF(OutOfPlane!$A$189=1,Inputs!$E$111+0,0)</f>
         <v/>
       </c>
       <c r="G189" s="3">
-        <f>IF(OutOfPlane!$A$189=1,Inputs!$G$110+0,0)</f>
+        <f>IF(OutOfPlane!$A$189=1,Inputs!$G$111+0,0)</f>
         <v/>
       </c>
       <c r="H189" s="3">
-        <f>IF(OutOfPlane!$A$189=1,IF(OutOfPlane!$C$189="boom_local",OutOfPlane!$B$17,1),0)</f>
-        <v/>
-      </c>
-      <c r="I189" s="3">
-        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$189*OutOfPlane!$G$189*OutOfPlane!$H$189</f>
+        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$189*OutOfPlane!$G$189</f>
         <v/>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="3">
-        <f>Inputs!$A$111</f>
+        <f>Inputs!$A$112</f>
         <v/>
       </c>
       <c r="B190" s="3">
-        <f>Loads!$B$98</f>
+        <f>Loads!$B$99</f>
         <v/>
       </c>
       <c r="C190" s="3">
-        <f>IF(OutOfPlane!$A$190=1,Inputs!$D$111&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$190=1,Inputs!$D$112&amp;"","")</f>
         <v/>
       </c>
       <c r="D190" s="3">
-        <f>Loads!$C$98</f>
+        <f>Loads!$C$99</f>
         <v/>
       </c>
       <c r="E190" s="3">
-        <f>Loads!$D$98</f>
+        <f>Loads!$D$99</f>
         <v/>
       </c>
       <c r="F190" s="3">
-        <f>IF(OutOfPlane!$A$190=1,Inputs!$E$111+0,0)</f>
+        <f>IF(OutOfPlane!$A$190=1,Inputs!$E$112+0,0)</f>
         <v/>
       </c>
       <c r="G190" s="3">
-        <f>IF(OutOfPlane!$A$190=1,Inputs!$G$111+0,0)</f>
+        <f>IF(OutOfPlane!$A$190=1,Inputs!$G$112+0,0)</f>
         <v/>
       </c>
       <c r="H190" s="3">
-        <f>IF(OutOfPlane!$A$190=1,IF(OutOfPlane!$C$190="boom_local",OutOfPlane!$B$17,1),0)</f>
-        <v/>
-      </c>
-      <c r="I190" s="3">
-        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$190*OutOfPlane!$G$190*OutOfPlane!$H$190</f>
+        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$190*OutOfPlane!$G$190</f>
         <v/>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="3">
-        <f>Inputs!$A$112</f>
+        <f>Inputs!$A$113</f>
         <v/>
       </c>
       <c r="B191" s="3">
-        <f>Loads!$B$99</f>
+        <f>Loads!$B$100</f>
         <v/>
       </c>
       <c r="C191" s="3">
-        <f>IF(OutOfPlane!$A$191=1,Inputs!$D$112&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$191=1,Inputs!$D$113&amp;"","")</f>
         <v/>
       </c>
       <c r="D191" s="3">
-        <f>Loads!$C$99</f>
+        <f>Loads!$C$100</f>
         <v/>
       </c>
       <c r="E191" s="3">
-        <f>Loads!$D$99</f>
+        <f>Loads!$D$100</f>
         <v/>
       </c>
       <c r="F191" s="3">
-        <f>IF(OutOfPlane!$A$191=1,Inputs!$E$112+0,0)</f>
+        <f>IF(OutOfPlane!$A$191=1,Inputs!$E$113+0,0)</f>
         <v/>
       </c>
       <c r="G191" s="3">
-        <f>IF(OutOfPlane!$A$191=1,Inputs!$G$112+0,0)</f>
+        <f>IF(OutOfPlane!$A$191=1,Inputs!$G$113+0,0)</f>
         <v/>
       </c>
       <c r="H191" s="3">
-        <f>IF(OutOfPlane!$A$191=1,IF(OutOfPlane!$C$191="boom_local",OutOfPlane!$B$17,1),0)</f>
-        <v/>
-      </c>
-      <c r="I191" s="3">
-        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$191*OutOfPlane!$G$191*OutOfPlane!$H$191</f>
+        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$191*OutOfPlane!$G$191</f>
         <v/>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="3">
-        <f>Inputs!$A$113</f>
+        <f>Inputs!$A$114</f>
         <v/>
       </c>
       <c r="B192" s="3">
-        <f>Loads!$B$100</f>
+        <f>Loads!$B$101</f>
         <v/>
       </c>
       <c r="C192" s="3">
-        <f>IF(OutOfPlane!$A$192=1,Inputs!$D$113&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$192=1,Inputs!$D$114&amp;"","")</f>
         <v/>
       </c>
       <c r="D192" s="3">
-        <f>Loads!$C$100</f>
+        <f>Loads!$C$101</f>
         <v/>
       </c>
       <c r="E192" s="3">
-        <f>Loads!$D$100</f>
+        <f>Loads!$D$101</f>
         <v/>
       </c>
       <c r="F192" s="3">
-        <f>IF(OutOfPlane!$A$192=1,Inputs!$E$113+0,0)</f>
+        <f>IF(OutOfPlane!$A$192=1,Inputs!$E$114+0,0)</f>
         <v/>
       </c>
       <c r="G192" s="3">
-        <f>IF(OutOfPlane!$A$192=1,Inputs!$G$113+0,0)</f>
+        <f>IF(OutOfPlane!$A$192=1,Inputs!$G$114+0,0)</f>
         <v/>
       </c>
       <c r="H192" s="3">
-        <f>IF(OutOfPlane!$A$192=1,IF(OutOfPlane!$C$192="boom_local",OutOfPlane!$B$17,1),0)</f>
-        <v/>
-      </c>
-      <c r="I192" s="3">
-        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$192*OutOfPlane!$G$192*OutOfPlane!$H$192</f>
+        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$192*OutOfPlane!$G$192</f>
         <v/>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="3">
-        <f>Inputs!$A$114</f>
+        <f>Inputs!$A$115</f>
         <v/>
       </c>
       <c r="B193" s="3">
-        <f>Loads!$B$101</f>
+        <f>Loads!$B$102</f>
         <v/>
       </c>
       <c r="C193" s="3">
-        <f>IF(OutOfPlane!$A$193=1,Inputs!$D$114&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$193=1,Inputs!$D$115&amp;"","")</f>
         <v/>
       </c>
       <c r="D193" s="3">
-        <f>Loads!$C$101</f>
+        <f>Loads!$C$102</f>
         <v/>
       </c>
       <c r="E193" s="3">
-        <f>Loads!$D$101</f>
+        <f>Loads!$D$102</f>
         <v/>
       </c>
       <c r="F193" s="3">
-        <f>IF(OutOfPlane!$A$193=1,Inputs!$E$114+0,0)</f>
+        <f>IF(OutOfPlane!$A$193=1,Inputs!$E$115+0,0)</f>
         <v/>
       </c>
       <c r="G193" s="3">
-        <f>IF(OutOfPlane!$A$193=1,Inputs!$G$114+0,0)</f>
+        <f>IF(OutOfPlane!$A$193=1,Inputs!$G$115+0,0)</f>
         <v/>
       </c>
       <c r="H193" s="3">
-        <f>IF(OutOfPlane!$A$193=1,IF(OutOfPlane!$C$193="boom_local",OutOfPlane!$B$17,1),0)</f>
-        <v/>
-      </c>
-      <c r="I193" s="3">
-        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$193*OutOfPlane!$G$193*OutOfPlane!$H$193</f>
+        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$193*OutOfPlane!$G$193</f>
         <v/>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="3">
-        <f>Inputs!$A$115</f>
+        <f>Inputs!$A$116</f>
         <v/>
       </c>
       <c r="B194" s="3">
-        <f>Loads!$B$102</f>
+        <f>Loads!$B$103</f>
         <v/>
       </c>
       <c r="C194" s="3">
-        <f>IF(OutOfPlane!$A$194=1,Inputs!$D$115&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$194=1,Inputs!$D$116&amp;"","")</f>
         <v/>
       </c>
       <c r="D194" s="3">
-        <f>Loads!$C$102</f>
+        <f>Loads!$C$103</f>
         <v/>
       </c>
       <c r="E194" s="3">
-        <f>Loads!$D$102</f>
+        <f>Loads!$D$103</f>
         <v/>
       </c>
       <c r="F194" s="3">
-        <f>IF(OutOfPlane!$A$194=1,Inputs!$E$115+0,0)</f>
+        <f>IF(OutOfPlane!$A$194=1,Inputs!$E$116+0,0)</f>
         <v/>
       </c>
       <c r="G194" s="3">
-        <f>IF(OutOfPlane!$A$194=1,Inputs!$G$115+0,0)</f>
+        <f>IF(OutOfPlane!$A$194=1,Inputs!$G$116+0,0)</f>
         <v/>
       </c>
       <c r="H194" s="3">
-        <f>IF(OutOfPlane!$A$194=1,IF(OutOfPlane!$C$194="boom_local",OutOfPlane!$B$17,1),0)</f>
-        <v/>
-      </c>
-      <c r="I194" s="3">
-        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$194*OutOfPlane!$G$194*OutOfPlane!$H$194</f>
+        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$194*OutOfPlane!$G$194</f>
         <v/>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="3">
-        <f>Inputs!$A$116</f>
+        <f>Inputs!$A$117</f>
         <v/>
       </c>
       <c r="B195" s="3">
-        <f>Loads!$B$103</f>
+        <f>Loads!$B$104</f>
         <v/>
       </c>
       <c r="C195" s="3">
-        <f>IF(OutOfPlane!$A$195=1,Inputs!$D$116&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$195=1,Inputs!$D$117&amp;"","")</f>
         <v/>
       </c>
       <c r="D195" s="3">
-        <f>Loads!$C$103</f>
+        <f>Loads!$C$104</f>
         <v/>
       </c>
       <c r="E195" s="3">
-        <f>Loads!$D$103</f>
+        <f>Loads!$D$104</f>
         <v/>
       </c>
       <c r="F195" s="3">
-        <f>IF(OutOfPlane!$A$195=1,Inputs!$E$116+0,0)</f>
+        <f>IF(OutOfPlane!$A$195=1,Inputs!$E$117+0,0)</f>
         <v/>
       </c>
       <c r="G195" s="3">
-        <f>IF(OutOfPlane!$A$195=1,Inputs!$G$116+0,0)</f>
+        <f>IF(OutOfPlane!$A$195=1,Inputs!$G$117+0,0)</f>
         <v/>
       </c>
       <c r="H195" s="3">
-        <f>IF(OutOfPlane!$A$195=1,IF(OutOfPlane!$C$195="boom_local",OutOfPlane!$B$17,1),0)</f>
-        <v/>
-      </c>
-      <c r="I195" s="3">
-        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$195*OutOfPlane!$G$195*OutOfPlane!$H$195</f>
+        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$195*OutOfPlane!$G$195</f>
         <v/>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="3">
-        <f>Inputs!$A$117</f>
+        <f>Inputs!$A$118</f>
         <v/>
       </c>
       <c r="B196" s="3">
-        <f>Loads!$B$104</f>
+        <f>Loads!$B$105</f>
         <v/>
       </c>
       <c r="C196" s="3">
-        <f>IF(OutOfPlane!$A$196=1,Inputs!$D$117&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$196=1,Inputs!$D$118&amp;"","")</f>
         <v/>
       </c>
       <c r="D196" s="3">
-        <f>Loads!$C$104</f>
+        <f>Loads!$C$105</f>
         <v/>
       </c>
       <c r="E196" s="3">
-        <f>Loads!$D$104</f>
+        <f>Loads!$D$105</f>
         <v/>
       </c>
       <c r="F196" s="3">
-        <f>IF(OutOfPlane!$A$196=1,Inputs!$E$117+0,0)</f>
+        <f>IF(OutOfPlane!$A$196=1,Inputs!$E$118+0,0)</f>
         <v/>
       </c>
       <c r="G196" s="3">
-        <f>IF(OutOfPlane!$A$196=1,Inputs!$G$117+0,0)</f>
+        <f>IF(OutOfPlane!$A$196=1,Inputs!$G$118+0,0)</f>
         <v/>
       </c>
       <c r="H196" s="3">
-        <f>IF(OutOfPlane!$A$196=1,IF(OutOfPlane!$C$196="boom_local",OutOfPlane!$B$17,1),0)</f>
-        <v/>
-      </c>
-      <c r="I196" s="3">
-        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$196*OutOfPlane!$G$196*OutOfPlane!$H$196</f>
+        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$196*OutOfPlane!$G$196</f>
         <v/>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="3">
-        <f>Inputs!$A$118</f>
+        <f>Inputs!$A$119</f>
         <v/>
       </c>
       <c r="B197" s="3">
-        <f>Loads!$B$105</f>
+        <f>Loads!$B$106</f>
         <v/>
       </c>
       <c r="C197" s="3">
-        <f>IF(OutOfPlane!$A$197=1,Inputs!$D$118&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$197=1,Inputs!$D$119&amp;"","")</f>
         <v/>
       </c>
       <c r="D197" s="3">
-        <f>Loads!$C$105</f>
+        <f>Loads!$C$106</f>
         <v/>
       </c>
       <c r="E197" s="3">
-        <f>Loads!$D$105</f>
+        <f>Loads!$D$106</f>
         <v/>
       </c>
       <c r="F197" s="3">
-        <f>IF(OutOfPlane!$A$197=1,Inputs!$E$118+0,0)</f>
+        <f>IF(OutOfPlane!$A$197=1,Inputs!$E$119+0,0)</f>
         <v/>
       </c>
       <c r="G197" s="3">
-        <f>IF(OutOfPlane!$A$197=1,Inputs!$G$118+0,0)</f>
+        <f>IF(OutOfPlane!$A$197=1,Inputs!$G$119+0,0)</f>
         <v/>
       </c>
       <c r="H197" s="3">
-        <f>IF(OutOfPlane!$A$197=1,IF(OutOfPlane!$C$197="boom_local",OutOfPlane!$B$17,1),0)</f>
-        <v/>
-      </c>
-      <c r="I197" s="3">
-        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$197*OutOfPlane!$G$197*OutOfPlane!$H$197</f>
+        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$197*OutOfPlane!$G$197</f>
         <v/>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="3">
-        <f>Inputs!$A$119</f>
+        <f>Inputs!$A$120</f>
         <v/>
       </c>
       <c r="B198" s="3">
-        <f>Loads!$B$106</f>
+        <f>Loads!$B$107</f>
         <v/>
       </c>
       <c r="C198" s="3">
-        <f>IF(OutOfPlane!$A$198=1,Inputs!$D$119&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$198=1,Inputs!$D$120&amp;"","")</f>
         <v/>
       </c>
       <c r="D198" s="3">
-        <f>Loads!$C$106</f>
+        <f>Loads!$C$107</f>
         <v/>
       </c>
       <c r="E198" s="3">
-        <f>Loads!$D$106</f>
+        <f>Loads!$D$107</f>
         <v/>
       </c>
       <c r="F198" s="3">
-        <f>IF(OutOfPlane!$A$198=1,Inputs!$E$119+0,0)</f>
+        <f>IF(OutOfPlane!$A$198=1,Inputs!$E$120+0,0)</f>
         <v/>
       </c>
       <c r="G198" s="3">
-        <f>IF(OutOfPlane!$A$198=1,Inputs!$G$119+0,0)</f>
+        <f>IF(OutOfPlane!$A$198=1,Inputs!$G$120+0,0)</f>
         <v/>
       </c>
       <c r="H198" s="3">
-        <f>IF(OutOfPlane!$A$198=1,IF(OutOfPlane!$C$198="boom_local",OutOfPlane!$B$17,1),0)</f>
-        <v/>
-      </c>
-      <c r="I198" s="3">
-        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$198*OutOfPlane!$G$198*OutOfPlane!$H$198</f>
+        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$198*OutOfPlane!$G$198</f>
         <v/>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="3">
-        <f>Inputs!$A$120</f>
+        <f>Inputs!$A$121</f>
         <v/>
       </c>
       <c r="B199" s="3">
-        <f>Loads!$B$107</f>
+        <f>Loads!$B$108</f>
         <v/>
       </c>
       <c r="C199" s="3">
-        <f>IF(OutOfPlane!$A$199=1,Inputs!$D$120&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$199=1,Inputs!$D$121&amp;"","")</f>
         <v/>
       </c>
       <c r="D199" s="3">
-        <f>Loads!$C$107</f>
+        <f>Loads!$C$108</f>
         <v/>
       </c>
       <c r="E199" s="3">
-        <f>Loads!$D$107</f>
+        <f>Loads!$D$108</f>
         <v/>
       </c>
       <c r="F199" s="3">
-        <f>IF(OutOfPlane!$A$199=1,Inputs!$E$120+0,0)</f>
+        <f>IF(OutOfPlane!$A$199=1,Inputs!$E$121+0,0)</f>
         <v/>
       </c>
       <c r="G199" s="3">
-        <f>IF(OutOfPlane!$A$199=1,Inputs!$G$120+0,0)</f>
+        <f>IF(OutOfPlane!$A$199=1,Inputs!$G$121+0,0)</f>
         <v/>
       </c>
       <c r="H199" s="3">
-        <f>IF(OutOfPlane!$A$199=1,IF(OutOfPlane!$C$199="boom_local",OutOfPlane!$B$17,1),0)</f>
-        <v/>
-      </c>
-      <c r="I199" s="3">
-        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$199*OutOfPlane!$G$199*OutOfPlane!$H$199</f>
+        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$199*OutOfPlane!$G$199</f>
         <v/>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="3">
-        <f>Inputs!$A$121</f>
+        <f>Inputs!$A$122</f>
         <v/>
       </c>
       <c r="B200" s="3">
-        <f>Loads!$B$108</f>
+        <f>Loads!$B$109</f>
         <v/>
       </c>
       <c r="C200" s="3">
-        <f>IF(OutOfPlane!$A$200=1,Inputs!$D$121&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$200=1,Inputs!$D$122&amp;"","")</f>
         <v/>
       </c>
       <c r="D200" s="3">
-        <f>Loads!$C$108</f>
+        <f>Loads!$C$109</f>
         <v/>
       </c>
       <c r="E200" s="3">
-        <f>Loads!$D$108</f>
+        <f>Loads!$D$109</f>
         <v/>
       </c>
       <c r="F200" s="3">
-        <f>IF(OutOfPlane!$A$200=1,Inputs!$E$121+0,0)</f>
+        <f>IF(OutOfPlane!$A$200=1,Inputs!$E$122+0,0)</f>
         <v/>
       </c>
       <c r="G200" s="3">
-        <f>IF(OutOfPlane!$A$200=1,Inputs!$G$121+0,0)</f>
+        <f>IF(OutOfPlane!$A$200=1,Inputs!$G$122+0,0)</f>
         <v/>
       </c>
       <c r="H200" s="3">
-        <f>IF(OutOfPlane!$A$200=1,IF(OutOfPlane!$C$200="boom_local",OutOfPlane!$B$17,1),0)</f>
-        <v/>
-      </c>
-      <c r="I200" s="3">
-        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$200*OutOfPlane!$G$200*OutOfPlane!$H$200</f>
+        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$200*OutOfPlane!$G$200</f>
         <v/>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="3">
-        <f>Inputs!$A$122</f>
+        <f>Inputs!$A$123</f>
         <v/>
       </c>
       <c r="B201" s="3">
-        <f>Loads!$B$109</f>
+        <f>Loads!$B$110</f>
         <v/>
       </c>
       <c r="C201" s="3">
-        <f>IF(OutOfPlane!$A$201=1,Inputs!$D$122&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$201=1,Inputs!$D$123&amp;"","")</f>
         <v/>
       </c>
       <c r="D201" s="3">
-        <f>Loads!$C$109</f>
+        <f>Loads!$C$110</f>
         <v/>
       </c>
       <c r="E201" s="3">
-        <f>Loads!$D$109</f>
+        <f>Loads!$D$110</f>
         <v/>
       </c>
       <c r="F201" s="3">
-        <f>IF(OutOfPlane!$A$201=1,Inputs!$E$122+0,0)</f>
+        <f>IF(OutOfPlane!$A$201=1,Inputs!$E$123+0,0)</f>
         <v/>
       </c>
       <c r="G201" s="3">
-        <f>IF(OutOfPlane!$A$201=1,Inputs!$G$122+0,0)</f>
+        <f>IF(OutOfPlane!$A$201=1,Inputs!$G$123+0,0)</f>
         <v/>
       </c>
       <c r="H201" s="3">
-        <f>IF(OutOfPlane!$A$201=1,IF(OutOfPlane!$C$201="boom_local",OutOfPlane!$B$17,1),0)</f>
-        <v/>
-      </c>
-      <c r="I201" s="3">
-        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$201*OutOfPlane!$G$201*OutOfPlane!$H$201</f>
+        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$201*OutOfPlane!$G$201</f>
         <v/>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="3">
-        <f>Inputs!$A$123</f>
+        <f>Inputs!$A$124</f>
         <v/>
       </c>
       <c r="B202" s="3">
-        <f>Loads!$B$110</f>
+        <f>Loads!$B$111</f>
         <v/>
       </c>
       <c r="C202" s="3">
-        <f>IF(OutOfPlane!$A$202=1,Inputs!$D$123&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$202=1,Inputs!$D$124&amp;"","")</f>
         <v/>
       </c>
       <c r="D202" s="3">
-        <f>Loads!$C$110</f>
+        <f>Loads!$C$111</f>
         <v/>
       </c>
       <c r="E202" s="3">
-        <f>Loads!$D$110</f>
+        <f>Loads!$D$111</f>
         <v/>
       </c>
       <c r="F202" s="3">
-        <f>IF(OutOfPlane!$A$202=1,Inputs!$E$123+0,0)</f>
+        <f>IF(OutOfPlane!$A$202=1,Inputs!$E$124+0,0)</f>
         <v/>
       </c>
       <c r="G202" s="3">
-        <f>IF(OutOfPlane!$A$202=1,Inputs!$G$123+0,0)</f>
+        <f>IF(OutOfPlane!$A$202=1,Inputs!$G$124+0,0)</f>
         <v/>
       </c>
       <c r="H202" s="3">
-        <f>IF(OutOfPlane!$A$202=1,IF(OutOfPlane!$C$202="boom_local",OutOfPlane!$B$17,1),0)</f>
-        <v/>
-      </c>
-      <c r="I202" s="3">
-        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$202*OutOfPlane!$G$202*OutOfPlane!$H$202</f>
+        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$202*OutOfPlane!$G$202</f>
         <v/>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="3">
-        <f>Inputs!$A$124</f>
+        <f>Inputs!$A$125</f>
         <v/>
       </c>
       <c r="B203" s="3">
-        <f>Loads!$B$111</f>
+        <f>Loads!$B$112</f>
         <v/>
       </c>
       <c r="C203" s="3">
-        <f>IF(OutOfPlane!$A$203=1,Inputs!$D$124&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$203=1,Inputs!$D$125&amp;"","")</f>
         <v/>
       </c>
       <c r="D203" s="3">
-        <f>Loads!$C$111</f>
+        <f>Loads!$C$112</f>
         <v/>
       </c>
       <c r="E203" s="3">
-        <f>Loads!$D$111</f>
+        <f>Loads!$D$112</f>
         <v/>
       </c>
       <c r="F203" s="3">
-        <f>IF(OutOfPlane!$A$203=1,Inputs!$E$124+0,0)</f>
+        <f>IF(OutOfPlane!$A$203=1,Inputs!$E$125+0,0)</f>
         <v/>
       </c>
       <c r="G203" s="3">
-        <f>IF(OutOfPlane!$A$203=1,Inputs!$G$124+0,0)</f>
+        <f>IF(OutOfPlane!$A$203=1,Inputs!$G$125+0,0)</f>
         <v/>
       </c>
       <c r="H203" s="3">
-        <f>IF(OutOfPlane!$A$203=1,IF(OutOfPlane!$C$203="boom_local",OutOfPlane!$B$17,1),0)</f>
-        <v/>
-      </c>
-      <c r="I203" s="3">
-        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$203*OutOfPlane!$G$203*OutOfPlane!$H$203</f>
+        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$203*OutOfPlane!$G$203</f>
         <v/>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="3">
-        <f>Inputs!$A$125</f>
+        <f>Inputs!$A$126</f>
         <v/>
       </c>
       <c r="B204" s="3">
-        <f>Loads!$B$112</f>
+        <f>Loads!$B$113</f>
         <v/>
       </c>
       <c r="C204" s="3">
-        <f>IF(OutOfPlane!$A$204=1,Inputs!$D$125&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$204=1,Inputs!$D$126&amp;"","")</f>
         <v/>
       </c>
       <c r="D204" s="3">
-        <f>Loads!$C$112</f>
+        <f>Loads!$C$113</f>
         <v/>
       </c>
       <c r="E204" s="3">
-        <f>Loads!$D$112</f>
+        <f>Loads!$D$113</f>
         <v/>
       </c>
       <c r="F204" s="3">
-        <f>IF(OutOfPlane!$A$204=1,Inputs!$E$125+0,0)</f>
+        <f>IF(OutOfPlane!$A$204=1,Inputs!$E$126+0,0)</f>
         <v/>
       </c>
       <c r="G204" s="3">
-        <f>IF(OutOfPlane!$A$204=1,Inputs!$G$125+0,0)</f>
+        <f>IF(OutOfPlane!$A$204=1,Inputs!$G$126+0,0)</f>
         <v/>
       </c>
       <c r="H204" s="3">
-        <f>IF(OutOfPlane!$A$204=1,IF(OutOfPlane!$C$204="boom_local",OutOfPlane!$B$17,1),0)</f>
-        <v/>
-      </c>
-      <c r="I204" s="3">
-        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$204*OutOfPlane!$G$204*OutOfPlane!$H$204</f>
+        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$204*OutOfPlane!$G$204</f>
         <v/>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="3">
-        <f>Inputs!$A$126</f>
+        <f>Inputs!$A$127</f>
         <v/>
       </c>
       <c r="B205" s="3">
-        <f>Loads!$B$113</f>
+        <f>Loads!$B$114</f>
         <v/>
       </c>
       <c r="C205" s="3">
-        <f>IF(OutOfPlane!$A$205=1,Inputs!$D$126&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$205=1,Inputs!$D$127&amp;"","")</f>
         <v/>
       </c>
       <c r="D205" s="3">
-        <f>Loads!$C$113</f>
+        <f>Loads!$C$114</f>
         <v/>
       </c>
       <c r="E205" s="3">
-        <f>Loads!$D$113</f>
+        <f>Loads!$D$114</f>
         <v/>
       </c>
       <c r="F205" s="3">
-        <f>IF(OutOfPlane!$A$205=1,Inputs!$E$126+0,0)</f>
+        <f>IF(OutOfPlane!$A$205=1,Inputs!$E$127+0,0)</f>
         <v/>
       </c>
       <c r="G205" s="3">
-        <f>IF(OutOfPlane!$A$205=1,Inputs!$G$126+0,0)</f>
+        <f>IF(OutOfPlane!$A$205=1,Inputs!$G$127+0,0)</f>
         <v/>
       </c>
       <c r="H205" s="3">
-        <f>IF(OutOfPlane!$A$205=1,IF(OutOfPlane!$C$205="boom_local",OutOfPlane!$B$17,1),0)</f>
-        <v/>
-      </c>
-      <c r="I205" s="3">
-        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$205*OutOfPlane!$G$205*OutOfPlane!$H$205</f>
+        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$205*OutOfPlane!$G$205</f>
         <v/>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="3">
-        <f>Inputs!$A$127</f>
+        <f>Inputs!$A$128</f>
         <v/>
       </c>
       <c r="B206" s="3">
-        <f>Loads!$B$114</f>
+        <f>Loads!$B$115</f>
         <v/>
       </c>
       <c r="C206" s="3">
-        <f>IF(OutOfPlane!$A$206=1,Inputs!$D$127&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$206=1,Inputs!$D$128&amp;"","")</f>
         <v/>
       </c>
       <c r="D206" s="3">
-        <f>Loads!$C$114</f>
+        <f>Loads!$C$115</f>
         <v/>
       </c>
       <c r="E206" s="3">
-        <f>Loads!$D$114</f>
+        <f>Loads!$D$115</f>
         <v/>
       </c>
       <c r="F206" s="3">
-        <f>IF(OutOfPlane!$A$206=1,Inputs!$E$127+0,0)</f>
+        <f>IF(OutOfPlane!$A$206=1,Inputs!$E$128+0,0)</f>
         <v/>
       </c>
       <c r="G206" s="3">
-        <f>IF(OutOfPlane!$A$206=1,Inputs!$G$127+0,0)</f>
+        <f>IF(OutOfPlane!$A$206=1,Inputs!$G$128+0,0)</f>
         <v/>
       </c>
       <c r="H206" s="3">
-        <f>IF(OutOfPlane!$A$206=1,IF(OutOfPlane!$C$206="boom_local",OutOfPlane!$B$17,1),0)</f>
-        <v/>
-      </c>
-      <c r="I206" s="3">
-        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$206*OutOfPlane!$G$206*OutOfPlane!$H$206</f>
+        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$206*OutOfPlane!$G$206</f>
         <v/>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="3">
-        <f>Inputs!$A$128</f>
+        <f>Inputs!$A$129</f>
         <v/>
       </c>
       <c r="B207" s="3">
-        <f>Loads!$B$115</f>
+        <f>Loads!$B$116</f>
         <v/>
       </c>
       <c r="C207" s="3">
-        <f>IF(OutOfPlane!$A$207=1,Inputs!$D$128&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$207=1,Inputs!$D$129&amp;"","")</f>
         <v/>
       </c>
       <c r="D207" s="3">
-        <f>Loads!$C$115</f>
+        <f>Loads!$C$116</f>
         <v/>
       </c>
       <c r="E207" s="3">
-        <f>Loads!$D$115</f>
+        <f>Loads!$D$116</f>
         <v/>
       </c>
       <c r="F207" s="3">
-        <f>IF(OutOfPlane!$A$207=1,Inputs!$E$128+0,0)</f>
+        <f>IF(OutOfPlane!$A$207=1,Inputs!$E$129+0,0)</f>
         <v/>
       </c>
       <c r="G207" s="3">
-        <f>IF(OutOfPlane!$A$207=1,Inputs!$G$128+0,0)</f>
+        <f>IF(OutOfPlane!$A$207=1,Inputs!$G$129+0,0)</f>
         <v/>
       </c>
       <c r="H207" s="3">
-        <f>IF(OutOfPlane!$A$207=1,IF(OutOfPlane!$C$207="boom_local",OutOfPlane!$B$17,1),0)</f>
-        <v/>
-      </c>
-      <c r="I207" s="3">
-        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$207*OutOfPlane!$G$207*OutOfPlane!$H$207</f>
+        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$207*OutOfPlane!$G$207</f>
         <v/>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="3">
-        <f>Inputs!$A$129</f>
+        <f>Inputs!$A$130</f>
         <v/>
       </c>
       <c r="B208" s="3">
-        <f>Loads!$B$116</f>
+        <f>Loads!$B$117</f>
         <v/>
       </c>
       <c r="C208" s="3">
-        <f>IF(OutOfPlane!$A$208=1,Inputs!$D$129&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$208=1,Inputs!$D$130&amp;"","")</f>
         <v/>
       </c>
       <c r="D208" s="3">
-        <f>Loads!$C$116</f>
+        <f>Loads!$C$117</f>
         <v/>
       </c>
       <c r="E208" s="3">
-        <f>Loads!$D$116</f>
+        <f>Loads!$D$117</f>
         <v/>
       </c>
       <c r="F208" s="3">
-        <f>IF(OutOfPlane!$A$208=1,Inputs!$E$129+0,0)</f>
+        <f>IF(OutOfPlane!$A$208=1,Inputs!$E$130+0,0)</f>
         <v/>
       </c>
       <c r="G208" s="3">
-        <f>IF(OutOfPlane!$A$208=1,Inputs!$G$129+0,0)</f>
+        <f>IF(OutOfPlane!$A$208=1,Inputs!$G$130+0,0)</f>
         <v/>
       </c>
       <c r="H208" s="3">
-        <f>IF(OutOfPlane!$A$208=1,IF(OutOfPlane!$C$208="boom_local",OutOfPlane!$B$17,1),0)</f>
-        <v/>
-      </c>
-      <c r="I208" s="3">
-        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$208*OutOfPlane!$G$208*OutOfPlane!$H$208</f>
+        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$208*OutOfPlane!$G$208</f>
         <v/>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="3">
-        <f>Inputs!$A$130</f>
+        <f>Inputs!$A$131</f>
         <v/>
       </c>
       <c r="B209" s="3">
-        <f>Loads!$B$117</f>
+        <f>Loads!$B$118</f>
         <v/>
       </c>
       <c r="C209" s="3">
-        <f>IF(OutOfPlane!$A$209=1,Inputs!$D$130&amp;"","")</f>
+        <f>IF(OutOfPlane!$A$209=1,Inputs!$D$131&amp;"","")</f>
         <v/>
       </c>
       <c r="D209" s="3">
-        <f>Loads!$C$117</f>
+        <f>Loads!$C$118</f>
         <v/>
       </c>
       <c r="E209" s="3">
-        <f>Loads!$D$117</f>
+        <f>Loads!$D$118</f>
         <v/>
       </c>
       <c r="F209" s="3">
-        <f>IF(OutOfPlane!$A$209=1,Inputs!$E$130+0,0)</f>
+        <f>IF(OutOfPlane!$A$209=1,Inputs!$E$131+0,0)</f>
         <v/>
       </c>
       <c r="G209" s="3">
-        <f>IF(OutOfPlane!$A$209=1,Inputs!$G$130+0,0)</f>
+        <f>IF(OutOfPlane!$A$209=1,Inputs!$G$131+0,0)</f>
         <v/>
       </c>
       <c r="H209" s="3">
-        <f>IF(OutOfPlane!$A$209=1,IF(OutOfPlane!$C$209="boom_local",OutOfPlane!$B$17,1),0)</f>
-        <v/>
-      </c>
-      <c r="I209" s="3">
-        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$209*OutOfPlane!$G$209*OutOfPlane!$H$209</f>
-        <v/>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="3">
-        <f>Inputs!$A$131</f>
-        <v/>
-      </c>
-      <c r="B210" s="3">
-        <f>Loads!$B$118</f>
-        <v/>
-      </c>
-      <c r="C210" s="3">
-        <f>IF(OutOfPlane!$A$210=1,Inputs!$D$131&amp;"","")</f>
-        <v/>
-      </c>
-      <c r="D210" s="3">
-        <f>Loads!$C$118</f>
-        <v/>
-      </c>
-      <c r="E210" s="3">
-        <f>Loads!$D$118</f>
-        <v/>
-      </c>
-      <c r="F210" s="3">
-        <f>IF(OutOfPlane!$A$210=1,Inputs!$E$131+0,0)</f>
-        <v/>
-      </c>
-      <c r="G210" s="3">
-        <f>IF(OutOfPlane!$A$210=1,Inputs!$G$131+0,0)</f>
-        <v/>
-      </c>
-      <c r="H210" s="3">
-        <f>IF(OutOfPlane!$A$210=1,IF(OutOfPlane!$C$210="boom_local",OutOfPlane!$B$17,1),0)</f>
-        <v/>
-      </c>
-      <c r="I210" s="3">
-        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$210*OutOfPlane!$G$210*OutOfPlane!$H$210</f>
-        <v/>
+        <f>OutOfPlane!$B$15*OutOfPlane!$B$16*OutOfPlane!$F$209*OutOfPlane!$G$209</f>
+        <v/>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="6" t="inlineStr">
+        <is>
+          <t>Moments of the applied loads per support group</t>
+        </is>
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="6" t="inlineStr">
-        <is>
-          <t>Moments of the applied loads per support group</t>
+      <c r="A214" s="8" t="inlineStr">
+        <is>
+          <t>Support group</t>
+        </is>
+      </c>
+      <c r="B214" s="8" t="inlineStr">
+        <is>
+          <t>Origin node</t>
+        </is>
+      </c>
+      <c r="C214" s="8" t="inlineStr">
+        <is>
+          <t>Origin x [m]</t>
+        </is>
+      </c>
+      <c r="D214" s="8" t="inlineStr">
+        <is>
+          <t>Origin z [m]</t>
+        </is>
+      </c>
+      <c r="E214" s="8" t="inlineStr">
+        <is>
+          <t>Mx mass points = SUM(y Fz) - SUM((z - oz) Fy) [kNm]</t>
+        </is>
+      </c>
+      <c r="F214" s="8" t="inlineStr">
+        <is>
+          <t>Mx lumped masses = -SUM((z - oz) Fy) [kNm]</t>
+        </is>
+      </c>
+      <c r="G214" s="8" t="inlineStr">
+        <is>
+          <t>Mx wind = -SUM((z - oz) Fy) [kNm]</t>
+        </is>
+      </c>
+      <c r="H214" s="8" t="inlineStr">
+        <is>
+          <t>Mx side force = -(z - oz) Fy [kNm]</t>
+        </is>
+      </c>
+      <c r="I214" s="8" t="inlineStr">
+        <is>
+          <t>Mx total [kNm]</t>
+        </is>
+      </c>
+      <c r="J214" s="8" t="inlineStr">
+        <is>
+          <t>Mz mass points = SUM((x - ox) Fy) - SUM(y Fx) [kNm]</t>
+        </is>
+      </c>
+      <c r="K214" s="8" t="inlineStr">
+        <is>
+          <t>Mz lumped masses = SUM((x - ox) Fy) [kNm]</t>
+        </is>
+      </c>
+      <c r="L214" s="8" t="inlineStr">
+        <is>
+          <t>Mz wind = SUM((x - ox) Fy) [kNm]</t>
+        </is>
+      </c>
+      <c r="M214" s="8" t="inlineStr">
+        <is>
+          <t>Mz side force = (x - ox) Fy [kNm]</t>
+        </is>
+      </c>
+      <c r="N214" s="8" t="inlineStr">
+        <is>
+          <t>Mz total [kNm]</t>
         </is>
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="8" t="inlineStr">
-        <is>
-          <t>Support group</t>
-        </is>
-      </c>
-      <c r="B215" s="8" t="inlineStr">
-        <is>
-          <t>Origin node</t>
-        </is>
-      </c>
-      <c r="C215" s="8" t="inlineStr">
-        <is>
-          <t>Origin x [m]</t>
-        </is>
-      </c>
-      <c r="D215" s="8" t="inlineStr">
-        <is>
-          <t>Origin z [m]</t>
-        </is>
-      </c>
-      <c r="E215" s="8" t="inlineStr">
-        <is>
-          <t>Mx mass points = SUM(y Fz) - SUM((z - oz) Fy) [kNm]</t>
-        </is>
-      </c>
-      <c r="F215" s="8" t="inlineStr">
-        <is>
-          <t>Mx lumped masses = -SUM((z - oz) Fy) [kNm]</t>
-        </is>
-      </c>
-      <c r="G215" s="8" t="inlineStr">
-        <is>
-          <t>Mx wind = -SUM((z - oz) Fy) [kNm]</t>
-        </is>
-      </c>
-      <c r="H215" s="8" t="inlineStr">
-        <is>
-          <t>Mx side force = -(z - oz) Fy [kNm]</t>
-        </is>
-      </c>
-      <c r="I215" s="8" t="inlineStr">
-        <is>
-          <t>Mx total [kNm]</t>
-        </is>
-      </c>
-      <c r="J215" s="8" t="inlineStr">
-        <is>
-          <t>Mz mass points = SUM((x - ox) Fy) - SUM(y Fx) [kNm]</t>
-        </is>
-      </c>
-      <c r="K215" s="8" t="inlineStr">
-        <is>
-          <t>Mz lumped masses = SUM((x - ox) Fy) [kNm]</t>
-        </is>
-      </c>
-      <c r="L215" s="8" t="inlineStr">
-        <is>
-          <t>Mz wind = SUM((x - ox) Fy) [kNm]</t>
-        </is>
-      </c>
-      <c r="M215" s="8" t="inlineStr">
-        <is>
-          <t>Mz side force = (x - ox) Fy [kNm]</t>
-        </is>
-      </c>
-      <c r="N215" s="8" t="inlineStr">
-        <is>
-          <t>Mz total [kNm]</t>
+      <c r="A215" s="7" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="B215" s="7" t="inlineStr">
+        <is>
+          <t>node</t>
+        </is>
+      </c>
+      <c r="C215" s="7" t="inlineStr">
+        <is>
+          <t>ox_m (Statics structure nodes)</t>
+        </is>
+      </c>
+      <c r="D215" s="7" t="inlineStr">
+        <is>
+          <t>oz_m</t>
+        </is>
+      </c>
+      <c r="E215" s="7" t="inlineStr">
+        <is>
+          <t>mx_masses</t>
+        </is>
+      </c>
+      <c r="F215" s="7" t="inlineStr">
+        <is>
+          <t>mx_lumped</t>
+        </is>
+      </c>
+      <c r="G215" s="7" t="inlineStr">
+        <is>
+          <t>mx_wind</t>
+        </is>
+      </c>
+      <c r="H215" s="7" t="inlineStr">
+        <is>
+          <t>mx_side</t>
+        </is>
+      </c>
+      <c r="I215" s="7" t="inlineStr">
+        <is>
+          <t>mx</t>
+        </is>
+      </c>
+      <c r="J215" s="7" t="inlineStr">
+        <is>
+          <t>mz_masses</t>
+        </is>
+      </c>
+      <c r="K215" s="7" t="inlineStr">
+        <is>
+          <t>mz_lumped</t>
+        </is>
+      </c>
+      <c r="L215" s="7" t="inlineStr">
+        <is>
+          <t>mz_wind</t>
+        </is>
+      </c>
+      <c r="M215" s="7" t="inlineStr">
+        <is>
+          <t>mz_side</t>
+        </is>
+      </c>
+      <c r="N215" s="7" t="inlineStr">
+        <is>
+          <t>mz</t>
         </is>
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="7" t="inlineStr">
-        <is>
-          <t>group</t>
-        </is>
-      </c>
-      <c r="B216" s="7" t="inlineStr">
-        <is>
-          <t>node</t>
-        </is>
-      </c>
-      <c r="C216" s="7" t="inlineStr">
-        <is>
-          <t>ox_m (Statics structure nodes)</t>
-        </is>
-      </c>
-      <c r="D216" s="7" t="inlineStr">
-        <is>
-          <t>oz_m</t>
-        </is>
-      </c>
-      <c r="E216" s="7" t="inlineStr">
-        <is>
-          <t>mx_masses</t>
-        </is>
-      </c>
-      <c r="F216" s="7" t="inlineStr">
-        <is>
-          <t>mx_lumped</t>
-        </is>
-      </c>
-      <c r="G216" s="7" t="inlineStr">
-        <is>
-          <t>mx_wind</t>
-        </is>
-      </c>
-      <c r="H216" s="7" t="inlineStr">
-        <is>
-          <t>mx_side</t>
-        </is>
-      </c>
-      <c r="I216" s="7" t="inlineStr">
-        <is>
-          <t>mx</t>
-        </is>
-      </c>
-      <c r="J216" s="7" t="inlineStr">
-        <is>
-          <t>mz_masses</t>
-        </is>
-      </c>
-      <c r="K216" s="7" t="inlineStr">
-        <is>
-          <t>mz_lumped</t>
-        </is>
-      </c>
-      <c r="L216" s="7" t="inlineStr">
-        <is>
-          <t>mz_wind</t>
-        </is>
-      </c>
-      <c r="M216" s="7" t="inlineStr">
-        <is>
-          <t>mz_side</t>
-        </is>
-      </c>
-      <c r="N216" s="7" t="inlineStr">
-        <is>
-          <t>mz</t>
-        </is>
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>heel</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>boom_heel</t>
+        </is>
+      </c>
+      <c r="C216" s="3">
+        <f>Statics!$B$16</f>
+        <v/>
+      </c>
+      <c r="D216" s="3">
+        <f>Statics!$B$17</f>
+        <v/>
+      </c>
+      <c r="E216" s="3">
+        <f>SUMPRODUCT(OutOfPlane!$E$38:$E$77,OutOfPlane!$I$38:$I$77)-SUMPRODUCT(OutOfPlane!$F$38:$F$77-OutOfPlane!$D$216,OutOfPlane!$J$38:$J$77)</f>
+        <v/>
+      </c>
+      <c r="F216" s="3">
+        <f>-SUMPRODUCT(OutOfPlane!$D$84:$D$163-OutOfPlane!$D$216,OutOfPlane!$H$84:$H$163)</f>
+        <v/>
+      </c>
+      <c r="G216" s="3">
+        <f>-SUMPRODUCT(OutOfPlane!$E$170:$E$209-OutOfPlane!$D$216,OutOfPlane!$H$170:$H$209)</f>
+        <v/>
+      </c>
+      <c r="H216" s="3">
+        <f>-(OutOfPlane!$B$32-OutOfPlane!$D$216)*OutOfPlane!$B$33</f>
+        <v/>
+      </c>
+      <c r="I216" s="3">
+        <f>OutOfPlane!$E$216+OutOfPlane!$F$216+OutOfPlane!$G$216+OutOfPlane!$H$216</f>
+        <v/>
+      </c>
+      <c r="J216" s="3">
+        <f>SUMPRODUCT(OutOfPlane!$D$38:$D$77-OutOfPlane!$C$216,OutOfPlane!$J$38:$J$77)-SUMPRODUCT(OutOfPlane!$E$38:$E$77,OutOfPlane!$H$38:$H$77)</f>
+        <v/>
+      </c>
+      <c r="K216" s="3">
+        <f>SUMPRODUCT(OutOfPlane!$C$84:$C$163-OutOfPlane!$C$216,OutOfPlane!$H$84:$H$163)</f>
+        <v/>
+      </c>
+      <c r="L216" s="3">
+        <f>SUMPRODUCT(OutOfPlane!$D$170:$D$209-OutOfPlane!$C$216,OutOfPlane!$H$170:$H$209)</f>
+        <v/>
+      </c>
+      <c r="M216" s="3">
+        <f>(OutOfPlane!$B$31-OutOfPlane!$C$216)*OutOfPlane!$B$33</f>
+        <v/>
+      </c>
+      <c r="N216" s="3">
+        <f>OutOfPlane!$J$216+OutOfPlane!$K$216+OutOfPlane!$L$216+OutOfPlane!$M$216</f>
+        <v/>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>heel</t>
+          <t>front_leg</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>boom_heel</t>
+          <t>front_base</t>
         </is>
       </c>
       <c r="C217" s="3">
-        <f>Statics!$B$16</f>
+        <f>Statics!$B$22</f>
         <v/>
       </c>
       <c r="D217" s="3">
-        <f>Statics!$B$17</f>
+        <f>Statics!$B$23</f>
         <v/>
       </c>
       <c r="E217" s="3">
-        <f>SUMPRODUCT(OutOfPlane!$E$39:$E$78,OutOfPlane!$I$39:$I$78)-SUMPRODUCT(OutOfPlane!$F$39:$F$78-OutOfPlane!$D$217,OutOfPlane!$J$39:$J$78)</f>
+        <f>SUMPRODUCT(OutOfPlane!$E$38:$E$77,OutOfPlane!$I$38:$I$77)-SUMPRODUCT(OutOfPlane!$F$38:$F$77-OutOfPlane!$D$217,OutOfPlane!$J$38:$J$77)</f>
         <v/>
       </c>
       <c r="F217" s="3">
-        <f>-SUMPRODUCT(OutOfPlane!$D$85:$D$164-OutOfPlane!$D$217,OutOfPlane!$H$85:$H$164)</f>
+        <f>-SUMPRODUCT(OutOfPlane!$D$84:$D$163-OutOfPlane!$D$217,OutOfPlane!$H$84:$H$163)</f>
         <v/>
       </c>
       <c r="G217" s="3">
-        <f>-SUMPRODUCT(OutOfPlane!$E$171:$E$210-OutOfPlane!$D$217,OutOfPlane!$I$171:$I$210)</f>
+        <f>-SUMPRODUCT(OutOfPlane!$E$170:$E$209-OutOfPlane!$D$217,OutOfPlane!$H$170:$H$209)</f>
         <v/>
       </c>
       <c r="H217" s="3">
-        <f>-(OutOfPlane!$B$33-OutOfPlane!$D$217)*OutOfPlane!$B$34</f>
+        <f>-(OutOfPlane!$B$32-OutOfPlane!$D$217)*OutOfPlane!$B$33</f>
         <v/>
       </c>
       <c r="I217" s="3">
@@ -43451,19 +43313,19 @@
         <v/>
       </c>
       <c r="J217" s="3">
-        <f>SUMPRODUCT(OutOfPlane!$D$39:$D$78-OutOfPlane!$C$217,OutOfPlane!$J$39:$J$78)-SUMPRODUCT(OutOfPlane!$E$39:$E$78,OutOfPlane!$H$39:$H$78)</f>
+        <f>SUMPRODUCT(OutOfPlane!$D$38:$D$77-OutOfPlane!$C$217,OutOfPlane!$J$38:$J$77)-SUMPRODUCT(OutOfPlane!$E$38:$E$77,OutOfPlane!$H$38:$H$77)</f>
         <v/>
       </c>
       <c r="K217" s="3">
-        <f>SUMPRODUCT(OutOfPlane!$C$85:$C$164-OutOfPlane!$C$217,OutOfPlane!$H$85:$H$164)</f>
+        <f>SUMPRODUCT(OutOfPlane!$C$84:$C$163-OutOfPlane!$C$217,OutOfPlane!$H$84:$H$163)</f>
         <v/>
       </c>
       <c r="L217" s="3">
-        <f>SUMPRODUCT(OutOfPlane!$D$171:$D$210-OutOfPlane!$C$217,OutOfPlane!$I$171:$I$210)</f>
+        <f>SUMPRODUCT(OutOfPlane!$D$170:$D$209-OutOfPlane!$C$217,OutOfPlane!$H$170:$H$209)</f>
         <v/>
       </c>
       <c r="M217" s="3">
-        <f>(OutOfPlane!$B$32-OutOfPlane!$C$217)*OutOfPlane!$B$34</f>
+        <f>(OutOfPlane!$B$31-OutOfPlane!$C$217)*OutOfPlane!$B$33</f>
         <v/>
       </c>
       <c r="N217" s="3">
@@ -43474,36 +43336,36 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>front_leg</t>
+          <t>rear_leg</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>front_base</t>
+          <t>rear_base</t>
         </is>
       </c>
       <c r="C218" s="3">
-        <f>Statics!$B$22</f>
+        <f>Statics!$B$18</f>
         <v/>
       </c>
       <c r="D218" s="3">
-        <f>Statics!$B$23</f>
+        <f>Statics!$B$19</f>
         <v/>
       </c>
       <c r="E218" s="3">
-        <f>SUMPRODUCT(OutOfPlane!$E$39:$E$78,OutOfPlane!$I$39:$I$78)-SUMPRODUCT(OutOfPlane!$F$39:$F$78-OutOfPlane!$D$218,OutOfPlane!$J$39:$J$78)</f>
+        <f>SUMPRODUCT(OutOfPlane!$E$38:$E$77,OutOfPlane!$I$38:$I$77)-SUMPRODUCT(OutOfPlane!$F$38:$F$77-OutOfPlane!$D$218,OutOfPlane!$J$38:$J$77)</f>
         <v/>
       </c>
       <c r="F218" s="3">
-        <f>-SUMPRODUCT(OutOfPlane!$D$85:$D$164-OutOfPlane!$D$218,OutOfPlane!$H$85:$H$164)</f>
+        <f>-SUMPRODUCT(OutOfPlane!$D$84:$D$163-OutOfPlane!$D$218,OutOfPlane!$H$84:$H$163)</f>
         <v/>
       </c>
       <c r="G218" s="3">
-        <f>-SUMPRODUCT(OutOfPlane!$E$171:$E$210-OutOfPlane!$D$218,OutOfPlane!$I$171:$I$210)</f>
+        <f>-SUMPRODUCT(OutOfPlane!$E$170:$E$209-OutOfPlane!$D$218,OutOfPlane!$H$170:$H$209)</f>
         <v/>
       </c>
       <c r="H218" s="3">
-        <f>-(OutOfPlane!$B$33-OutOfPlane!$D$218)*OutOfPlane!$B$34</f>
+        <f>-(OutOfPlane!$B$32-OutOfPlane!$D$218)*OutOfPlane!$B$33</f>
         <v/>
       </c>
       <c r="I218" s="3">
@@ -43511,19 +43373,19 @@
         <v/>
       </c>
       <c r="J218" s="3">
-        <f>SUMPRODUCT(OutOfPlane!$D$39:$D$78-OutOfPlane!$C$218,OutOfPlane!$J$39:$J$78)-SUMPRODUCT(OutOfPlane!$E$39:$E$78,OutOfPlane!$H$39:$H$78)</f>
+        <f>SUMPRODUCT(OutOfPlane!$D$38:$D$77-OutOfPlane!$C$218,OutOfPlane!$J$38:$J$77)-SUMPRODUCT(OutOfPlane!$E$38:$E$77,OutOfPlane!$H$38:$H$77)</f>
         <v/>
       </c>
       <c r="K218" s="3">
-        <f>SUMPRODUCT(OutOfPlane!$C$85:$C$164-OutOfPlane!$C$218,OutOfPlane!$H$85:$H$164)</f>
+        <f>SUMPRODUCT(OutOfPlane!$C$84:$C$163-OutOfPlane!$C$218,OutOfPlane!$H$84:$H$163)</f>
         <v/>
       </c>
       <c r="L218" s="3">
-        <f>SUMPRODUCT(OutOfPlane!$D$171:$D$210-OutOfPlane!$C$218,OutOfPlane!$I$171:$I$210)</f>
+        <f>SUMPRODUCT(OutOfPlane!$D$170:$D$209-OutOfPlane!$C$218,OutOfPlane!$H$170:$H$209)</f>
         <v/>
       </c>
       <c r="M218" s="3">
-        <f>(OutOfPlane!$B$32-OutOfPlane!$C$218)*OutOfPlane!$B$34</f>
+        <f>(OutOfPlane!$B$31-OutOfPlane!$C$218)*OutOfPlane!$B$33</f>
         <v/>
       </c>
       <c r="N218" s="3">
@@ -43534,36 +43396,36 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>rear_leg</t>
+          <t>platform_base</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>rear_base</t>
+          <t>platform_heel</t>
         </is>
       </c>
       <c r="C219" s="3">
-        <f>Statics!$B$18</f>
+        <f>Statics!$B$26</f>
         <v/>
       </c>
       <c r="D219" s="3">
-        <f>Statics!$B$19</f>
+        <f>Statics!$B$27</f>
         <v/>
       </c>
       <c r="E219" s="3">
-        <f>SUMPRODUCT(OutOfPlane!$E$39:$E$78,OutOfPlane!$I$39:$I$78)-SUMPRODUCT(OutOfPlane!$F$39:$F$78-OutOfPlane!$D$219,OutOfPlane!$J$39:$J$78)</f>
+        <f>SUMPRODUCT(OutOfPlane!$E$38:$E$77,OutOfPlane!$I$38:$I$77)-SUMPRODUCT(OutOfPlane!$F$38:$F$77-OutOfPlane!$D$219,OutOfPlane!$J$38:$J$77)</f>
         <v/>
       </c>
       <c r="F219" s="3">
-        <f>-SUMPRODUCT(OutOfPlane!$D$85:$D$164-OutOfPlane!$D$219,OutOfPlane!$H$85:$H$164)</f>
+        <f>-SUMPRODUCT(OutOfPlane!$D$84:$D$163-OutOfPlane!$D$219,OutOfPlane!$H$84:$H$163)</f>
         <v/>
       </c>
       <c r="G219" s="3">
-        <f>-SUMPRODUCT(OutOfPlane!$E$171:$E$210-OutOfPlane!$D$219,OutOfPlane!$I$171:$I$210)</f>
+        <f>-SUMPRODUCT(OutOfPlane!$E$170:$E$209-OutOfPlane!$D$219,OutOfPlane!$H$170:$H$209)</f>
         <v/>
       </c>
       <c r="H219" s="3">
-        <f>-(OutOfPlane!$B$33-OutOfPlane!$D$219)*OutOfPlane!$B$34</f>
+        <f>-(OutOfPlane!$B$32-OutOfPlane!$D$219)*OutOfPlane!$B$33</f>
         <v/>
       </c>
       <c r="I219" s="3">
@@ -43571,19 +43433,19 @@
         <v/>
       </c>
       <c r="J219" s="3">
-        <f>SUMPRODUCT(OutOfPlane!$D$39:$D$78-OutOfPlane!$C$219,OutOfPlane!$J$39:$J$78)-SUMPRODUCT(OutOfPlane!$E$39:$E$78,OutOfPlane!$H$39:$H$78)</f>
+        <f>SUMPRODUCT(OutOfPlane!$D$38:$D$77-OutOfPlane!$C$219,OutOfPlane!$J$38:$J$77)-SUMPRODUCT(OutOfPlane!$E$38:$E$77,OutOfPlane!$H$38:$H$77)</f>
         <v/>
       </c>
       <c r="K219" s="3">
-        <f>SUMPRODUCT(OutOfPlane!$C$85:$C$164-OutOfPlane!$C$219,OutOfPlane!$H$85:$H$164)</f>
+        <f>SUMPRODUCT(OutOfPlane!$C$84:$C$163-OutOfPlane!$C$219,OutOfPlane!$H$84:$H$163)</f>
         <v/>
       </c>
       <c r="L219" s="3">
-        <f>SUMPRODUCT(OutOfPlane!$D$171:$D$210-OutOfPlane!$C$219,OutOfPlane!$I$171:$I$210)</f>
+        <f>SUMPRODUCT(OutOfPlane!$D$170:$D$209-OutOfPlane!$C$219,OutOfPlane!$H$170:$H$209)</f>
         <v/>
       </c>
       <c r="M219" s="3">
-        <f>(OutOfPlane!$B$32-OutOfPlane!$C$219)*OutOfPlane!$B$34</f>
+        <f>(OutOfPlane!$B$31-OutOfPlane!$C$219)*OutOfPlane!$B$33</f>
         <v/>
       </c>
       <c r="N219" s="3">
@@ -43591,181 +43453,165 @@
         <v/>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>platform_base</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>platform_heel</t>
-        </is>
-      </c>
-      <c r="C220" s="3">
-        <f>Statics!$B$26</f>
-        <v/>
-      </c>
-      <c r="D220" s="3">
-        <f>Statics!$B$27</f>
-        <v/>
-      </c>
-      <c r="E220" s="3">
-        <f>SUMPRODUCT(OutOfPlane!$E$39:$E$78,OutOfPlane!$I$39:$I$78)-SUMPRODUCT(OutOfPlane!$F$39:$F$78-OutOfPlane!$D$220,OutOfPlane!$J$39:$J$78)</f>
-        <v/>
-      </c>
-      <c r="F220" s="3">
-        <f>-SUMPRODUCT(OutOfPlane!$D$85:$D$164-OutOfPlane!$D$220,OutOfPlane!$H$85:$H$164)</f>
-        <v/>
-      </c>
-      <c r="G220" s="3">
-        <f>-SUMPRODUCT(OutOfPlane!$E$171:$E$210-OutOfPlane!$D$220,OutOfPlane!$I$171:$I$210)</f>
-        <v/>
-      </c>
-      <c r="H220" s="3">
-        <f>-(OutOfPlane!$B$33-OutOfPlane!$D$220)*OutOfPlane!$B$34</f>
-        <v/>
-      </c>
-      <c r="I220" s="3">
-        <f>OutOfPlane!$E$220+OutOfPlane!$F$220+OutOfPlane!$G$220+OutOfPlane!$H$220</f>
-        <v/>
-      </c>
-      <c r="J220" s="3">
-        <f>SUMPRODUCT(OutOfPlane!$D$39:$D$78-OutOfPlane!$C$220,OutOfPlane!$J$39:$J$78)-SUMPRODUCT(OutOfPlane!$E$39:$E$78,OutOfPlane!$H$39:$H$78)</f>
-        <v/>
-      </c>
-      <c r="K220" s="3">
-        <f>SUMPRODUCT(OutOfPlane!$C$85:$C$164-OutOfPlane!$C$220,OutOfPlane!$H$85:$H$164)</f>
-        <v/>
-      </c>
-      <c r="L220" s="3">
-        <f>SUMPRODUCT(OutOfPlane!$D$171:$D$210-OutOfPlane!$C$220,OutOfPlane!$I$171:$I$210)</f>
-        <v/>
-      </c>
-      <c r="M220" s="3">
-        <f>(OutOfPlane!$B$32-OutOfPlane!$C$220)*OutOfPlane!$B$34</f>
-        <v/>
-      </c>
-      <c r="N220" s="3">
-        <f>OutOfPlane!$J$220+OutOfPlane!$K$220+OutOfPlane!$L$220+OutOfPlane!$M$220</f>
-        <v/>
+    <row r="223">
+      <c r="A223" s="6" t="inlineStr">
+        <is>
+          <t>Left/right split</t>
+        </is>
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="6" t="inlineStr">
-        <is>
-          <t>Left/right split</t>
+      <c r="A224" s="8" t="inlineStr">
+        <is>
+          <t>Side support</t>
+        </is>
+      </c>
+      <c r="B224" s="8" t="inlineStr">
+        <is>
+          <t>Support group</t>
+        </is>
+      </c>
+      <c r="C224" s="8" t="inlineStr">
+        <is>
+          <t>In-plane total</t>
+        </is>
+      </c>
+      <c r="D224" s="8" t="inlineStr">
+        <is>
+          <t>Side sign [+1/-1]</t>
+        </is>
+      </c>
+      <c r="E224" s="8" t="inlineStr">
+        <is>
+          <t>Total Fx (in-plane reaction) [kN]</t>
+        </is>
+      </c>
+      <c r="F224" s="8" t="inlineStr">
+        <is>
+          <t>Total Fz (in-plane reaction) [kN]</t>
+        </is>
+      </c>
+      <c r="G224" s="8" t="inlineStr">
+        <is>
+          <t>Mz about the group [kNm]</t>
+        </is>
+      </c>
+      <c r="H224" s="8" t="inlineStr">
+        <is>
+          <t>Mx about the group [kNm]</t>
+        </is>
+      </c>
+      <c r="I224" s="8" t="inlineStr">
+        <is>
+          <t>Fx = 0.5 total Fx + side Mz / width [kN]</t>
+        </is>
+      </c>
+      <c r="J224" s="8" t="inlineStr">
+        <is>
+          <t>Fz = 0.5 total Fz + side Mx / width [kN]</t>
         </is>
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="8" t="inlineStr">
-        <is>
-          <t>Side support</t>
-        </is>
-      </c>
-      <c r="B225" s="8" t="inlineStr">
-        <is>
-          <t>Support group</t>
-        </is>
-      </c>
-      <c r="C225" s="8" t="inlineStr">
-        <is>
-          <t>In-plane total</t>
-        </is>
-      </c>
-      <c r="D225" s="8" t="inlineStr">
-        <is>
-          <t>Side sign [+1/-1]</t>
-        </is>
-      </c>
-      <c r="E225" s="8" t="inlineStr">
-        <is>
-          <t>Total Fx (in-plane reaction) [kN]</t>
-        </is>
-      </c>
-      <c r="F225" s="8" t="inlineStr">
-        <is>
-          <t>Total Fz (in-plane reaction) [kN]</t>
-        </is>
-      </c>
-      <c r="G225" s="8" t="inlineStr">
-        <is>
-          <t>Mz about the group [kNm]</t>
-        </is>
-      </c>
-      <c r="H225" s="8" t="inlineStr">
-        <is>
-          <t>Mx about the group [kNm]</t>
-        </is>
-      </c>
-      <c r="I225" s="8" t="inlineStr">
-        <is>
-          <t>Fx = 0.5 total Fx + side Mz / width [kN]</t>
-        </is>
-      </c>
-      <c r="J225" s="8" t="inlineStr">
-        <is>
-          <t>Fz = 0.5 total Fz + side Mx / width [kN]</t>
+      <c r="A225" s="7" t="inlineStr">
+        <is>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="B225" s="7" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="C225" s="7" t="inlineStr">
+        <is>
+          <t>total_entity</t>
+        </is>
+      </c>
+      <c r="D225" s="7" t="inlineStr">
+        <is>
+          <t>side (-1 left (+Y, port), +1 right (-Y))</t>
+        </is>
+      </c>
+      <c r="E225" s="7" t="inlineStr">
+        <is>
+          <t>total_fx (Statics)</t>
+        </is>
+      </c>
+      <c r="F225" s="7" t="inlineStr">
+        <is>
+          <t>total_fz (Statics)</t>
+        </is>
+      </c>
+      <c r="G225" s="7" t="inlineStr">
+        <is>
+          <t>mz</t>
+        </is>
+      </c>
+      <c r="H225" s="7" t="inlineStr">
+        <is>
+          <t>mx</t>
+        </is>
+      </c>
+      <c r="I225" s="7" t="inlineStr">
+        <is>
+          <t>fx (0 if width &lt;= 0)</t>
+        </is>
+      </c>
+      <c r="J225" s="7" t="inlineStr">
+        <is>
+          <t>fz (0 if width &lt;= 0)</t>
         </is>
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="7" t="inlineStr">
-        <is>
-          <t>entity</t>
-        </is>
-      </c>
-      <c r="B226" s="7" t="inlineStr">
-        <is>
-          <t>group</t>
-        </is>
-      </c>
-      <c r="C226" s="7" t="inlineStr">
-        <is>
-          <t>total_entity</t>
-        </is>
-      </c>
-      <c r="D226" s="7" t="inlineStr">
-        <is>
-          <t>side (+1 left, -1 right)</t>
-        </is>
-      </c>
-      <c r="E226" s="7" t="inlineStr">
-        <is>
-          <t>total_fx (Statics)</t>
-        </is>
-      </c>
-      <c r="F226" s="7" t="inlineStr">
-        <is>
-          <t>total_fz (Statics)</t>
-        </is>
-      </c>
-      <c r="G226" s="7" t="inlineStr">
-        <is>
-          <t>mz</t>
-        </is>
-      </c>
-      <c r="H226" s="7" t="inlineStr">
-        <is>
-          <t>mx</t>
-        </is>
-      </c>
-      <c r="I226" s="7" t="inlineStr">
-        <is>
-          <t>fx (0 if width &lt;= 0)</t>
-        </is>
-      </c>
-      <c r="J226" s="7" t="inlineStr">
-        <is>
-          <t>fz (0 if width &lt;= 0)</t>
-        </is>
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>heel_left</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>heel</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>heel_point</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E226" s="3">
+        <f>Statics!$H$35</f>
+        <v/>
+      </c>
+      <c r="F226" s="3">
+        <f>Statics!$H$36</f>
+        <v/>
+      </c>
+      <c r="G226" s="3">
+        <f>OutOfPlane!$N$216</f>
+        <v/>
+      </c>
+      <c r="H226" s="3">
+        <f>OutOfPlane!$I$216</f>
+        <v/>
+      </c>
+      <c r="I226" s="3">
+        <f>IF(OutOfPlane!$B$20=1,0.5*OutOfPlane!$E$226+OutOfPlane!$D$226*OutOfPlane!$G$226/OutOfPlane!$B$19,0)</f>
+        <v/>
+      </c>
+      <c r="J226" s="3">
+        <f>IF(OutOfPlane!$B$20=1,0.5*OutOfPlane!$F$226+OutOfPlane!$D$226*OutOfPlane!$H$226/OutOfPlane!$B$19,0)</f>
+        <v/>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>heel_left</t>
+          <t>heel_right</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -43790,47 +43636,47 @@
         <v/>
       </c>
       <c r="G227" s="3">
-        <f>OutOfPlane!$N$217</f>
+        <f>OutOfPlane!$N$216</f>
         <v/>
       </c>
       <c r="H227" s="3">
-        <f>OutOfPlane!$I$217</f>
+        <f>OutOfPlane!$I$216</f>
         <v/>
       </c>
       <c r="I227" s="3">
-        <f>IF(OutOfPlane!$B$21=1,0.5*OutOfPlane!$E$227+OutOfPlane!$D$227*OutOfPlane!$G$227/OutOfPlane!$B$20,0)</f>
+        <f>IF(OutOfPlane!$B$20=1,0.5*OutOfPlane!$E$227+OutOfPlane!$D$227*OutOfPlane!$G$227/OutOfPlane!$B$19,0)</f>
         <v/>
       </c>
       <c r="J227" s="3">
-        <f>IF(OutOfPlane!$B$21=1,0.5*OutOfPlane!$F$227+OutOfPlane!$D$227*OutOfPlane!$H$227/OutOfPlane!$B$20,0)</f>
+        <f>IF(OutOfPlane!$B$20=1,0.5*OutOfPlane!$F$227+OutOfPlane!$D$227*OutOfPlane!$H$227/OutOfPlane!$B$19,0)</f>
         <v/>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>heel_right</t>
+          <t>front_leg_left</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>heel</t>
+          <t>front_leg</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>heel_point</t>
+          <t>front_hinge</t>
         </is>
       </c>
       <c r="D228" t="n">
         <v>-1</v>
       </c>
       <c r="E228" s="3">
-        <f>Statics!$H$35</f>
+        <f>Statics!$K$55</f>
         <v/>
       </c>
       <c r="F228" s="3">
-        <f>Statics!$H$36</f>
+        <f>Statics!$K$56</f>
         <v/>
       </c>
       <c r="G228" s="3">
@@ -43842,18 +43688,18 @@
         <v/>
       </c>
       <c r="I228" s="3">
-        <f>IF(OutOfPlane!$B$21=1,0.5*OutOfPlane!$E$228+OutOfPlane!$D$228*OutOfPlane!$G$228/OutOfPlane!$B$20,0)</f>
+        <f>IF(OutOfPlane!$B$20=1,0.5*OutOfPlane!$E$228+OutOfPlane!$D$228*OutOfPlane!$G$228/OutOfPlane!$B$19,0)</f>
         <v/>
       </c>
       <c r="J228" s="3">
-        <f>IF(OutOfPlane!$B$21=1,0.5*OutOfPlane!$F$228+OutOfPlane!$D$228*OutOfPlane!$H$228/OutOfPlane!$B$20,0)</f>
+        <f>IF(OutOfPlane!$B$20=1,0.5*OutOfPlane!$F$228+OutOfPlane!$D$228*OutOfPlane!$H$228/OutOfPlane!$B$19,0)</f>
         <v/>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>front_leg_left</t>
+          <t>front_leg_right</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -43878,47 +43724,47 @@
         <v/>
       </c>
       <c r="G229" s="3">
-        <f>OutOfPlane!$N$218</f>
+        <f>OutOfPlane!$N$217</f>
         <v/>
       </c>
       <c r="H229" s="3">
-        <f>OutOfPlane!$I$218</f>
+        <f>OutOfPlane!$I$217</f>
         <v/>
       </c>
       <c r="I229" s="3">
-        <f>IF(OutOfPlane!$B$21=1,0.5*OutOfPlane!$E$229+OutOfPlane!$D$229*OutOfPlane!$G$229/OutOfPlane!$B$20,0)</f>
+        <f>IF(OutOfPlane!$B$20=1,0.5*OutOfPlane!$E$229+OutOfPlane!$D$229*OutOfPlane!$G$229/OutOfPlane!$B$19,0)</f>
         <v/>
       </c>
       <c r="J229" s="3">
-        <f>IF(OutOfPlane!$B$21=1,0.5*OutOfPlane!$F$229+OutOfPlane!$D$229*OutOfPlane!$H$229/OutOfPlane!$B$20,0)</f>
+        <f>IF(OutOfPlane!$B$20=1,0.5*OutOfPlane!$F$229+OutOfPlane!$D$229*OutOfPlane!$H$229/OutOfPlane!$B$19,0)</f>
         <v/>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>front_leg_right</t>
+          <t>rear_leg_left</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>front_leg</t>
+          <t>rear_leg</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>front_hinge</t>
+          <t>rear_hinge</t>
         </is>
       </c>
       <c r="D230" t="n">
         <v>-1</v>
       </c>
       <c r="E230" s="3">
-        <f>Statics!$K$55</f>
+        <f>Statics!$K$53</f>
         <v/>
       </c>
       <c r="F230" s="3">
-        <f>Statics!$K$56</f>
+        <f>Statics!$K$54</f>
         <v/>
       </c>
       <c r="G230" s="3">
@@ -43930,18 +43776,18 @@
         <v/>
       </c>
       <c r="I230" s="3">
-        <f>IF(OutOfPlane!$B$21=1,0.5*OutOfPlane!$E$230+OutOfPlane!$D$230*OutOfPlane!$G$230/OutOfPlane!$B$20,0)</f>
+        <f>IF(OutOfPlane!$B$20=1,0.5*OutOfPlane!$E$230+OutOfPlane!$D$230*OutOfPlane!$G$230/OutOfPlane!$B$19,0)</f>
         <v/>
       </c>
       <c r="J230" s="3">
-        <f>IF(OutOfPlane!$B$21=1,0.5*OutOfPlane!$F$230+OutOfPlane!$D$230*OutOfPlane!$H$230/OutOfPlane!$B$20,0)</f>
+        <f>IF(OutOfPlane!$B$20=1,0.5*OutOfPlane!$F$230+OutOfPlane!$D$230*OutOfPlane!$H$230/OutOfPlane!$B$19,0)</f>
         <v/>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>rear_leg_left</t>
+          <t>rear_leg_right</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -43966,81 +43812,58 @@
         <v/>
       </c>
       <c r="G231" s="3">
-        <f>OutOfPlane!$N$219</f>
+        <f>OutOfPlane!$N$218</f>
         <v/>
       </c>
       <c r="H231" s="3">
-        <f>OutOfPlane!$I$219</f>
+        <f>OutOfPlane!$I$218</f>
         <v/>
       </c>
       <c r="I231" s="3">
-        <f>IF(OutOfPlane!$B$21=1,0.5*OutOfPlane!$E$231+OutOfPlane!$D$231*OutOfPlane!$G$231/OutOfPlane!$B$20,0)</f>
+        <f>IF(OutOfPlane!$B$20=1,0.5*OutOfPlane!$E$231+OutOfPlane!$D$231*OutOfPlane!$G$231/OutOfPlane!$B$19,0)</f>
         <v/>
       </c>
       <c r="J231" s="3">
-        <f>IF(OutOfPlane!$B$21=1,0.5*OutOfPlane!$F$231+OutOfPlane!$D$231*OutOfPlane!$H$231/OutOfPlane!$B$20,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>rear_leg_right</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>rear_leg</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>rear_hinge</t>
-        </is>
-      </c>
-      <c r="D232" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E232" s="3">
-        <f>Statics!$K$53</f>
-        <v/>
-      </c>
-      <c r="F232" s="3">
-        <f>Statics!$K$54</f>
-        <v/>
-      </c>
-      <c r="G232" s="3">
-        <f>OutOfPlane!$N$219</f>
-        <v/>
-      </c>
-      <c r="H232" s="3">
-        <f>OutOfPlane!$I$219</f>
-        <v/>
-      </c>
-      <c r="I232" s="3">
-        <f>IF(OutOfPlane!$B$21=1,0.5*OutOfPlane!$E$232+OutOfPlane!$D$232*OutOfPlane!$G$232/OutOfPlane!$B$20,0)</f>
-        <v/>
-      </c>
-      <c r="J232" s="3">
-        <f>IF(OutOfPlane!$B$21=1,0.5*OutOfPlane!$F$232+OutOfPlane!$D$232*OutOfPlane!$H$232/OutOfPlane!$B$20,0)</f>
-        <v/>
+        <f>IF(OutOfPlane!$B$20=1,0.5*OutOfPlane!$F$231+OutOfPlane!$D$231*OutOfPlane!$H$231/OutOfPlane!$B$19,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="6" t="inlineStr">
+        <is>
+          <t>Platform base Fy and Mx</t>
+        </is>
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="6" t="inlineStr">
-        <is>
-          <t>Platform base Fy and Mx</t>
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Applied Fy of the mass points</t>
+        </is>
+      </c>
+      <c r="B236" s="3">
+        <f>SUM(OutOfPlane!$J$38:$J$77)</f>
+        <v/>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>kN</t>
+        </is>
+      </c>
+      <c r="D236" s="7" t="inlineStr">
+        <is>
+          <t>fy_masses</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Fy of the mass points</t>
+          <t>Applied Fy of the lumped masses</t>
         </is>
       </c>
       <c r="B237" s="3">
-        <f>SUM(OutOfPlane!$J$39:$J$78)</f>
+        <f>SUM(OutOfPlane!$H$84:$H$163)</f>
         <v/>
       </c>
       <c r="C237" t="inlineStr">
@@ -44050,18 +43873,18 @@
       </c>
       <c r="D237" s="7" t="inlineStr">
         <is>
-          <t>fy_masses</t>
+          <t>fy_lumped</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Fy of the lumped masses</t>
+          <t>Applied Fy of the Y wind</t>
         </is>
       </c>
       <c r="B238" s="3">
-        <f>SUM(OutOfPlane!$H$85:$H$164)</f>
+        <f>SUM(OutOfPlane!$H$170:$H$209)</f>
         <v/>
       </c>
       <c r="C238" t="inlineStr">
@@ -44071,18 +43894,18 @@
       </c>
       <c r="D238" s="7" t="inlineStr">
         <is>
-          <t>fy_lumped</t>
+          <t>fy_wind</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Fy of the Y wind</t>
+          <t>Applied side force</t>
         </is>
       </c>
       <c r="B239" s="3">
-        <f>SUM(OutOfPlane!$I$171:$I$210)</f>
+        <f>OutOfPlane!$B$33</f>
         <v/>
       </c>
       <c r="C239" t="inlineStr">
@@ -44092,18 +43915,18 @@
       </c>
       <c r="D239" s="7" t="inlineStr">
         <is>
-          <t>fy_wind</t>
+          <t>fy_side</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Side force</t>
+          <t>Platform base Fy = -(sum of applied Fy)</t>
         </is>
       </c>
       <c r="B240" s="3">
-        <f>OutOfPlane!$B$34</f>
+        <f>-(OutOfPlane!$B$236+OutOfPlane!$B$237+OutOfPlane!$B$238+OutOfPlane!$B$239)</f>
         <v/>
       </c>
       <c r="C240" t="inlineStr">
@@ -44113,49 +43936,28 @@
       </c>
       <c r="D240" s="7" t="inlineStr">
         <is>
-          <t>fy_side</t>
+          <t>fy_kN  -- reaction.platform_base.fy</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Platform base Fy = sum of applied Fy</t>
+          <t>Platform base Mx = -(applied Mx about platform_heel)</t>
         </is>
       </c>
       <c r="B241" s="3">
-        <f>OutOfPlane!$B$237+OutOfPlane!$B$238+OutOfPlane!$B$239+OutOfPlane!$B$240</f>
+        <f>-OutOfPlane!$I$219</f>
         <v/>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>kN</t>
+          <t>kNm</t>
         </is>
       </c>
       <c r="D241" s="7" t="inlineStr">
         <is>
-          <t>fy_kN  -- reaction.platform_base.fy</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>Platform base Mx = Mx about platform_heel</t>
-        </is>
-      </c>
-      <c r="B242" s="3">
-        <f>OutOfPlane!$I$220</f>
-        <v/>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>kNm</t>
-        </is>
-      </c>
-      <c r="D242" s="7" t="inlineStr">
-        <is>
-          <t>mx_kNm  -- platform_base.mx</t>
+          <t>mx_kNm  -- reaction.platform_base.mx</t>
         </is>
       </c>
     </row>
@@ -44226,7 +44028,7 @@
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>Out-of-plane rows (OutOfPlane sheet, calculation/engine.py _out_of_plane_variants): heel_left/heel_right = 0.5 heel_point +/- M_heel / boom width (the app's split), platform base Fy/Mx with the sign of the applied loads; fradial = sqrt(Fx^2 + Fy^2), mradial = sqrt(Mx^2 + My^2), bearing line loads Fz/(pi D) +/- 4 mradial/(pi D^2) (min shows uplift only, core/demand_extraction.py); n/a without a bearing diameter (the app hides them).</t>
+          <t>Out-of-plane rows (OutOfPlane sheet, calculation/engine.py _out_of_plane_variants): heel_left/heel_right = 0.5 heel_point -/+ M_heel / boom width (left = +Y = port), platform base Fy/Mx as support reactions (minus the applied loads); fradial = sqrt(Fx^2 + Fy^2), mradial = sqrt(Mx^2 + My^2), bearing line loads Fz/(pi D) +/- 4 mradial/(pi D^2) (min shows uplift only, core/demand_extraction.py); n/a without a bearing diameter (the app hides them).</t>
         </is>
       </c>
     </row>
@@ -44244,7 +44046,7 @@
         </is>
       </c>
       <c r="B12" s="3">
-        <f>IF(AND(Statics!$B$13=1,OutOfPlane!$B$21=1),1,0)</f>
+        <f>IF(AND(Statics!$B$13=1,OutOfPlane!$B$20=1),1,0)</f>
         <v/>
       </c>
       <c r="C12" t="inlineStr">
@@ -44265,7 +44067,7 @@
         </is>
       </c>
       <c r="B13" s="3">
-        <f>IF(Results!$B$12=1,"",IF(Statics!$B$10=0,"no solve rope",IF(OR(Statics!$B$11=1,Statics!$B$12=1),"singular matrix",IF(OutOfPlane!$B$21&lt;&gt;1,"boom width must be &gt; 0","no solution"))))</f>
+        <f>IF(Results!$B$12=1,"",IF(Statics!$B$10=0,"no solve rope",IF(OR(Statics!$B$11=1,Statics!$B$12=1),"singular matrix",IF(OutOfPlane!$B$20&lt;&gt;1,"boom width must be &gt; 0","no solution"))))</f>
         <v/>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -44281,7 +44083,7 @@
         </is>
       </c>
       <c r="B14" s="3">
-        <f>IF(Results!$B$12=1,"OK",IF(Statics!$B$10=0,"No solve rope: no active rope has role solve (Inputs ropes), so the boom matrix is singular and the app shows no results",IF(OR(Statics!$B$11=1,Statics!$B$12=1),"Singular matrix on Statics (boom 3x3 or leg frame 6x6): the app finds no solution and shows no results",IF(OutOfPlane!$B$21&lt;&gt;1,"Boom width (Inputs structure) must be &gt; 0: the app rejects it and its out-of-plane split divides by it, so it shows no results","No solution"))))</f>
+        <f>IF(Results!$B$12=1,"OK",IF(Statics!$B$10=0,"No solve rope: no active rope has role solve (Inputs ropes), so the boom matrix is singular and the app shows no results",IF(OR(Statics!$B$11=1,Statics!$B$12=1),"Singular matrix on Statics (boom 3x3 or leg frame 6x6): the app finds no solution and shows no results",IF(OutOfPlane!$B$20&lt;&gt;1,"Boom width (Inputs structure) must be &gt; 0: the app rejects it and its out-of-plane split divides by it, so it shows no results","No solution"))))</f>
         <v/>
       </c>
       <c r="D14" s="7" t="inlineStr">
@@ -45204,7 +45006,7 @@
         </is>
       </c>
       <c r="D52" s="3">
-        <f>IF(Results!$B$12&lt;&gt;1,Results!$B$13,OutOfPlane!$I$227)</f>
+        <f>IF(Results!$B$12&lt;&gt;1,Results!$B$13,OutOfPlane!$I$226)</f>
         <v/>
       </c>
       <c r="E52" t="inlineStr">
@@ -45214,7 +45016,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>OutOfPlane split: 0.5 Hx + Mz_heel / width</t>
+          <t>OutOfPlane split: 0.5 Hx - Mz_heel / width (+Y side)</t>
         </is>
       </c>
     </row>
@@ -45235,7 +45037,7 @@
         </is>
       </c>
       <c r="D53" s="3">
-        <f>IF(Results!$B$12&lt;&gt;1,Results!$B$13,OutOfPlane!$J$227)</f>
+        <f>IF(Results!$B$12&lt;&gt;1,Results!$B$13,OutOfPlane!$J$226)</f>
         <v/>
       </c>
       <c r="E53" t="inlineStr">
@@ -45245,7 +45047,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>OutOfPlane split: 0.5 Hz + Mx_heel / width</t>
+          <t>OutOfPlane split: 0.5 Hz - Mx_heel / width (+Y side)</t>
         </is>
       </c>
     </row>
@@ -45266,7 +45068,7 @@
         </is>
       </c>
       <c r="D54" s="3">
-        <f>IF(Results!$B$12&lt;&gt;1,Results!$B$13,SQRT(OutOfPlane!$I$227^2+OutOfPlane!$J$227^2))</f>
+        <f>IF(Results!$B$12&lt;&gt;1,Results!$B$13,SQRT(OutOfPlane!$I$226^2+OutOfPlane!$J$226^2))</f>
         <v/>
       </c>
       <c r="E54" t="inlineStr">
@@ -45297,7 +45099,7 @@
         </is>
       </c>
       <c r="D55" s="3">
-        <f>IF(Results!$B$12&lt;&gt;1,Results!$B$13,OutOfPlane!$I$228)</f>
+        <f>IF(Results!$B$12&lt;&gt;1,Results!$B$13,OutOfPlane!$I$227)</f>
         <v/>
       </c>
       <c r="E55" t="inlineStr">
@@ -45307,7 +45109,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>OutOfPlane split: 0.5 Hx - Mz_heel / width</t>
+          <t>OutOfPlane split: 0.5 Hx + Mz_heel / width (-Y side)</t>
         </is>
       </c>
     </row>
@@ -45328,7 +45130,7 @@
         </is>
       </c>
       <c r="D56" s="3">
-        <f>IF(Results!$B$12&lt;&gt;1,Results!$B$13,OutOfPlane!$J$228)</f>
+        <f>IF(Results!$B$12&lt;&gt;1,Results!$B$13,OutOfPlane!$J$227)</f>
         <v/>
       </c>
       <c r="E56" t="inlineStr">
@@ -45338,7 +45140,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>OutOfPlane split: 0.5 Hz - Mx_heel / width</t>
+          <t>OutOfPlane split: 0.5 Hz + Mx_heel / width (-Y side)</t>
         </is>
       </c>
     </row>
@@ -45359,7 +45161,7 @@
         </is>
       </c>
       <c r="D57" s="3">
-        <f>IF(Results!$B$12&lt;&gt;1,Results!$B$13,SQRT(OutOfPlane!$I$228^2+OutOfPlane!$J$228^2))</f>
+        <f>IF(Results!$B$12&lt;&gt;1,Results!$B$13,SQRT(OutOfPlane!$I$227^2+OutOfPlane!$J$227^2))</f>
         <v/>
       </c>
       <c r="E57" t="inlineStr">
@@ -45390,7 +45192,7 @@
         </is>
       </c>
       <c r="D58" s="3">
-        <f>IF(Results!$B$12&lt;&gt;1,Results!$B$13,OutOfPlane!$B$241)</f>
+        <f>IF(Results!$B$12&lt;&gt;1,Results!$B$13,OutOfPlane!$B$240)</f>
         <v/>
       </c>
       <c r="E58" t="inlineStr">
@@ -45400,7 +45202,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>OutOfPlane: sum of applied Fy (load sign)</t>
+          <t>OutOfPlane: -(sum of applied Fy), reaction</t>
         </is>
       </c>
     </row>
@@ -45421,7 +45223,7 @@
         </is>
       </c>
       <c r="D59" s="3">
-        <f>IF(Results!$B$12&lt;&gt;1,Results!$B$13,OutOfPlane!$B$242)</f>
+        <f>IF(Results!$B$12&lt;&gt;1,Results!$B$13,OutOfPlane!$B$241)</f>
         <v/>
       </c>
       <c r="E59" t="inlineStr">
@@ -45431,7 +45233,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>OutOfPlane: applied Mx about platform_heel (load sign)</t>
+          <t>OutOfPlane: -(applied Mx about platform_heel), reaction</t>
         </is>
       </c>
     </row>
@@ -45452,7 +45254,7 @@
         </is>
       </c>
       <c r="D60" s="3">
-        <f>IF(Results!$B$12&lt;&gt;1,Results!$B$13,SQRT(Statics!$B$71^2+OutOfPlane!$B$241^2))</f>
+        <f>IF(Results!$B$12&lt;&gt;1,Results!$B$13,SQRT(Statics!$B$71^2+OutOfPlane!$B$240^2))</f>
         <v/>
       </c>
       <c r="E60" t="inlineStr">
@@ -45483,7 +45285,7 @@
         </is>
       </c>
       <c r="D61" s="3">
-        <f>IF(Results!$B$12&lt;&gt;1,Results!$B$13,SQRT(OutOfPlane!$B$242^2+Statics!$B$73^2))</f>
+        <f>IF(Results!$B$12&lt;&gt;1,Results!$B$13,SQRT(OutOfPlane!$B$241^2+Statics!$B$73^2))</f>
         <v/>
       </c>
       <c r="E61" t="inlineStr">
@@ -45514,7 +45316,7 @@
         </is>
       </c>
       <c r="D62" s="3">
-        <f>IF(Results!$B$12&lt;&gt;1,Results!$B$13,IF(OutOfPlane!$B$23=1,Statics!$B$72/(PI()*OutOfPlane!$B$22)+4*SQRT(OutOfPlane!$B$242^2+Statics!$B$73^2)/(PI()*OutOfPlane!$B$22^2),"n/a (no bearing diameter)"))</f>
+        <f>IF(Results!$B$12&lt;&gt;1,Results!$B$13,IF(OutOfPlane!$B$22=1,Statics!$B$72/(PI()*OutOfPlane!$B$21)+4*SQRT(OutOfPlane!$B$241^2+Statics!$B$73^2)/(PI()*OutOfPlane!$B$21^2),"n/a (no bearing diameter)"))</f>
         <v/>
       </c>
       <c r="E62" t="inlineStr">
@@ -45545,7 +45347,7 @@
         </is>
       </c>
       <c r="D63" s="3">
-        <f>IF(Results!$B$12&lt;&gt;1,Results!$B$13,IF(OutOfPlane!$B$23=1,MAX(0,4*SQRT(OutOfPlane!$B$242^2+Statics!$B$73^2)/(PI()*OutOfPlane!$B$22^2)-Statics!$B$72/(PI()*OutOfPlane!$B$22)),"n/a (no bearing diameter)"))</f>
+        <f>IF(Results!$B$12&lt;&gt;1,Results!$B$13,IF(OutOfPlane!$B$22=1,MAX(0,4*SQRT(OutOfPlane!$B$241^2+Statics!$B$73^2)/(PI()*OutOfPlane!$B$21^2)-Statics!$B$72/(PI()*OutOfPlane!$B$21)),"n/a (no bearing diameter)"))</f>
         <v/>
       </c>
       <c r="E63" t="inlineStr">
@@ -45655,7 +45457,7 @@
         </is>
       </c>
       <c r="C7" s="3">
-        <f>IFERROR(1*(ROWS(Inputs!$A$46:$A$85)&lt;&gt;40)+1*(SUM(Inputs!$A$46:$A$85)&lt;&gt;SUM(Loads!$A$33:$A$72)),1)+IFERROR(1*(ROWS(Inputs!$A$46:$A$85)&lt;&gt;40)+1*(SUM(Inputs!$A$46:$A$85)&lt;&gt;SUM(OutOfPlane!$A$39:$A$78)),1)+IFERROR(1*(ROWS(Inputs!$A$92:$A$131)&lt;&gt;40)+1*(SUM(Inputs!$A$92:$A$131)&lt;&gt;SUM(Loads!$A$79:$A$118)),1)+IFERROR(1*(ROWS(Inputs!$A$92:$A$131)&lt;&gt;40)+1*(SUM(Inputs!$A$92:$A$131)&lt;&gt;SUM(OutOfPlane!$A$171:$A$210)),1)+IFERROR(1*(ROWS(Inputs!$A$138:$A$217)&lt;&gt;80)+1*(SUM(Inputs!$A$138:$A$217)&lt;&gt;SUM(Geometry!$A$58:$A$137)),1)+IFERROR(1*(ROWS(Inputs!$A$138:$A$217)&lt;&gt;80)+1*(SUM(Inputs!$A$138:$A$217)&lt;&gt;SUM(Loads!$A$219:$A$298)),1)+IFERROR(1*(ROWS(Inputs!$A$138:$A$217)&lt;&gt;80)+1*(SUM(Inputs!$A$138:$A$217)&lt;&gt;SUM(OutOfPlane!$A$85:$A$164)),1)+IFERROR(1*(ROWS(Inputs!$A$224:$A$283)&lt;&gt;60)+1*(SUM(Inputs!$A$224:$A$283)&lt;&gt;SUM(Loads!$A$153:$A$212)),1)+IFERROR(1*(ROWS(Inputs!$A$290:$A$297)&lt;&gt;8)+1*(SUM(Inputs!$A$290:$A$297)&lt;&gt;SUM(Loads!$A$125:$A$132)),1)+IFERROR(1*(ROWS(Inputs!$A$304:$A$311)&lt;&gt;8)+1*(SUM(Inputs!$A$304:$A$311)&lt;&gt;SUM(Loads!$A$139:$A$146)),1)+IFERROR(1*(ROWS(Inputs!$A$304:$A$311)&lt;&gt;8)+1*(SUM(Inputs!$A$304:$A$311)&lt;&gt;SUM(Results!$A$19:$A$26)),1)</f>
+        <f>IFERROR(1*(ROWS(Inputs!$A$46:$A$85)&lt;&gt;40)+1*(SUM(Inputs!$A$46:$A$85)&lt;&gt;SUM(Loads!$A$33:$A$72)),1)+IFERROR(1*(ROWS(Inputs!$A$46:$A$85)&lt;&gt;40)+1*(SUM(Inputs!$A$46:$A$85)&lt;&gt;SUM(OutOfPlane!$A$38:$A$77)),1)+IFERROR(1*(ROWS(Inputs!$A$92:$A$131)&lt;&gt;40)+1*(SUM(Inputs!$A$92:$A$131)&lt;&gt;SUM(Loads!$A$79:$A$118)),1)+IFERROR(1*(ROWS(Inputs!$A$92:$A$131)&lt;&gt;40)+1*(SUM(Inputs!$A$92:$A$131)&lt;&gt;SUM(OutOfPlane!$A$170:$A$209)),1)+IFERROR(1*(ROWS(Inputs!$A$138:$A$217)&lt;&gt;80)+1*(SUM(Inputs!$A$138:$A$217)&lt;&gt;SUM(Geometry!$A$58:$A$137)),1)+IFERROR(1*(ROWS(Inputs!$A$138:$A$217)&lt;&gt;80)+1*(SUM(Inputs!$A$138:$A$217)&lt;&gt;SUM(Loads!$A$219:$A$298)),1)+IFERROR(1*(ROWS(Inputs!$A$138:$A$217)&lt;&gt;80)+1*(SUM(Inputs!$A$138:$A$217)&lt;&gt;SUM(OutOfPlane!$A$84:$A$163)),1)+IFERROR(1*(ROWS(Inputs!$A$224:$A$283)&lt;&gt;60)+1*(SUM(Inputs!$A$224:$A$283)&lt;&gt;SUM(Loads!$A$153:$A$212)),1)+IFERROR(1*(ROWS(Inputs!$A$290:$A$297)&lt;&gt;8)+1*(SUM(Inputs!$A$290:$A$297)&lt;&gt;SUM(Loads!$A$125:$A$132)),1)+IFERROR(1*(ROWS(Inputs!$A$304:$A$311)&lt;&gt;8)+1*(SUM(Inputs!$A$304:$A$311)&lt;&gt;SUM(Loads!$A$139:$A$146)),1)+IFERROR(1*(ROWS(Inputs!$A$304:$A$311)&lt;&gt;8)+1*(SUM(Inputs!$A$304:$A$311)&lt;&gt;SUM(Results!$A$19:$A$26)),1)</f>
         <v/>
       </c>
       <c r="D7" s="3">
@@ -45935,7 +45737,7 @@
         </is>
       </c>
       <c r="C21" s="3">
-        <f>IF(OutOfPlane!$B$21=1,0,1)</f>
+        <f>IF(OutOfPlane!$B$20=1,0,1)</f>
         <v/>
       </c>
       <c r="D21" s="3">

--- a/docs/crane-statics-validation-22689.xlsx
+++ b/docs/crane-statics-validation-22689.xlsx
@@ -6989,7 +6989,10 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="16">
+  <dataValidations count="17">
+    <dataValidation sqref="B13" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not an allowed value" error="Type a number &gt; 0, or leave the cell blank." type="decimal" errorStyle="stop" operator="greaterThan">
+      <formula1>0</formula1>
+    </dataValidation>
     <dataValidation sqref="B33" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not an allowed value" error="Pick one of: +X, -X, +Y, -Y" type="list" errorStyle="stop">
       <formula1>"+X,-X,+Y,-Y"</formula1>
     </dataValidation>
@@ -45372,7 +45375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -45395,7 +45398,7 @@
         </is>
       </c>
       <c r="C3" s="3">
-        <f>SUM(C6:C22)</f>
+        <f>SUM(C6:C23)</f>
         <v/>
       </c>
       <c r="D3" s="3">
@@ -45437,7 +45440,7 @@
         </is>
       </c>
       <c r="C6" s="3">
-        <f>SUM($D$27:$D$32)</f>
+        <f>SUM($D$28:$D$33)</f>
         <v/>
       </c>
       <c r="D6" s="3">
@@ -45453,11 +45456,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Inputs tables with rows inserted or deleted (never do that: use spare rows), or a calculation sheet whose rows no longer follow the Inputs rows</t>
+          <t>Inputs tables with rows inserted or deleted (never do that: use spare rows), including a row inserted above the first data row or above the guard row, or a calculation sheet whose rows no longer follow the Inputs rows</t>
         </is>
       </c>
       <c r="C7" s="3">
-        <f>IFERROR(1*(ROWS(Inputs!$A$46:$A$85)&lt;&gt;40)+1*(SUM(Inputs!$A$46:$A$85)&lt;&gt;SUM(Loads!$A$33:$A$72)),1)+IFERROR(1*(ROWS(Inputs!$A$46:$A$85)&lt;&gt;40)+1*(SUM(Inputs!$A$46:$A$85)&lt;&gt;SUM(OutOfPlane!$A$38:$A$77)),1)+IFERROR(1*(ROWS(Inputs!$A$92:$A$131)&lt;&gt;40)+1*(SUM(Inputs!$A$92:$A$131)&lt;&gt;SUM(Loads!$A$79:$A$118)),1)+IFERROR(1*(ROWS(Inputs!$A$92:$A$131)&lt;&gt;40)+1*(SUM(Inputs!$A$92:$A$131)&lt;&gt;SUM(OutOfPlane!$A$170:$A$209)),1)+IFERROR(1*(ROWS(Inputs!$A$138:$A$217)&lt;&gt;80)+1*(SUM(Inputs!$A$138:$A$217)&lt;&gt;SUM(Geometry!$A$58:$A$137)),1)+IFERROR(1*(ROWS(Inputs!$A$138:$A$217)&lt;&gt;80)+1*(SUM(Inputs!$A$138:$A$217)&lt;&gt;SUM(Loads!$A$219:$A$298)),1)+IFERROR(1*(ROWS(Inputs!$A$138:$A$217)&lt;&gt;80)+1*(SUM(Inputs!$A$138:$A$217)&lt;&gt;SUM(OutOfPlane!$A$84:$A$163)),1)+IFERROR(1*(ROWS(Inputs!$A$224:$A$283)&lt;&gt;60)+1*(SUM(Inputs!$A$224:$A$283)&lt;&gt;SUM(Loads!$A$153:$A$212)),1)+IFERROR(1*(ROWS(Inputs!$A$290:$A$297)&lt;&gt;8)+1*(SUM(Inputs!$A$290:$A$297)&lt;&gt;SUM(Loads!$A$125:$A$132)),1)+IFERROR(1*(ROWS(Inputs!$A$304:$A$311)&lt;&gt;8)+1*(SUM(Inputs!$A$304:$A$311)&lt;&gt;SUM(Loads!$A$139:$A$146)),1)+IFERROR(1*(ROWS(Inputs!$A$304:$A$311)&lt;&gt;8)+1*(SUM(Inputs!$A$304:$A$311)&lt;&gt;SUM(Results!$A$19:$A$26)),1)</f>
+        <f>IFERROR(1*(ROWS(Inputs!$A$46:$A$85)&lt;&gt;40)+1*(SUM(Inputs!$A$46:$A$85)&lt;&gt;SUM(Loads!$A$33:$A$72)),1)+IFERROR(1*(ROWS(Inputs!$A$46:$A$85)&lt;&gt;40)+1*(SUM(Inputs!$A$46:$A$85)&lt;&gt;SUM(OutOfPlane!$A$38:$A$77)),1)+IFERROR(1*(ROWS(Inputs!$A$92:$A$131)&lt;&gt;40)+1*(SUM(Inputs!$A$92:$A$131)&lt;&gt;SUM(Loads!$A$79:$A$118)),1)+IFERROR(1*(ROWS(Inputs!$A$92:$A$131)&lt;&gt;40)+1*(SUM(Inputs!$A$92:$A$131)&lt;&gt;SUM(OutOfPlane!$A$170:$A$209)),1)+IFERROR(1*(ROWS(Inputs!$A$138:$A$217)&lt;&gt;80)+1*(SUM(Inputs!$A$138:$A$217)&lt;&gt;SUM(Geometry!$A$58:$A$137)),1)+IFERROR(1*(ROWS(Inputs!$A$138:$A$217)&lt;&gt;80)+1*(SUM(Inputs!$A$138:$A$217)&lt;&gt;SUM(Loads!$A$219:$A$298)),1)+IFERROR(1*(ROWS(Inputs!$A$138:$A$217)&lt;&gt;80)+1*(SUM(Inputs!$A$138:$A$217)&lt;&gt;SUM(OutOfPlane!$A$84:$A$163)),1)+IFERROR(1*(ROWS(Inputs!$A$224:$A$283)&lt;&gt;60)+1*(SUM(Inputs!$A$224:$A$283)&lt;&gt;SUM(Loads!$A$153:$A$212)),1)+IFERROR(1*(ROWS(Inputs!$A$290:$A$297)&lt;&gt;8)+1*(SUM(Inputs!$A$290:$A$297)&lt;&gt;SUM(Loads!$A$125:$A$132)),1)+IFERROR(1*(ROWS(Inputs!$A$304:$A$311)&lt;&gt;8)+1*(SUM(Inputs!$A$304:$A$311)&lt;&gt;SUM(Loads!$A$139:$A$146)),1)+IFERROR(1*(ROWS(Inputs!$A$304:$A$311)&lt;&gt;8)+1*(SUM(Inputs!$A$304:$A$311)&lt;&gt;SUM(Results!$A$19:$A$26)),1)+IFERROR(1*(ROW(Inputs!$A$86)-ROW(Inputs!$A$45)&lt;&gt;41),1)+IFERROR(1*(ROW(Inputs!$A$132)-ROW(Inputs!$A$91)&lt;&gt;41),1)+IFERROR(1*(ROW(Inputs!$A$218)-ROW(Inputs!$A$137)&lt;&gt;81),1)+IFERROR(1*(ROW(Inputs!$A$284)-ROW(Inputs!$A$223)&lt;&gt;61),1)+IFERROR(1*(ROW(Inputs!$A$298)-ROW(Inputs!$A$289)&lt;&gt;9),1)+IFERROR(1*(ROW(Inputs!$A$312)-ROW(Inputs!$A$303)&lt;&gt;9),1)</f>
         <v/>
       </c>
       <c r="D7" s="3">
@@ -45528,16 +45531,16 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>node_references</t>
+          <t>boom_local_non_boom</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>References to a missing or inactive node (segment ends, hoist hook/support nodes, hanging nodes' parent)</t>
+          <t>Active mass-point, wind-area or node rows with frame boom_local on a body other than boom (the app ignores u/v/w there and uses x/z)</t>
         </is>
       </c>
       <c r="C11" s="3">
-        <f>SUMPRODUCT((Inputs!$A$224:$A$283=1)*(COUNTIFS(Inputs!$B$138:$B$217,Inputs!$C$224:$C$283,Inputs!$A$138:$A$217,1)=0))+SUMPRODUCT((Inputs!$A$224:$A$283=1)*(COUNTIFS(Inputs!$B$138:$B$217,Inputs!$D$224:$D$283,Inputs!$A$138:$A$217,1)=0))+SUMPRODUCT((Inputs!$A$304:$A$311=1)*(COUNTIFS(Inputs!$B$138:$B$217,Inputs!$D$304:$D$311,Inputs!$A$138:$A$217,1)=0))+SUMPRODUCT((Inputs!$A$304:$A$311=1)*(Inputs!$E$304:$E$311&lt;&gt;"")*(COUNTIFS(Inputs!$B$138:$B$217,Inputs!$E$304:$E$311,Inputs!$A$138:$A$217,1)=0))+SUMPRODUCT((Inputs!$A$138:$A$217=1)*(Inputs!$D$138:$D$217="hanging")*(COUNTIFS(Inputs!$B$138:$B$217,Inputs!$I$138:$I$217,Inputs!$A$138:$A$217,1)=0))</f>
+        <f>SUMPRODUCT((Inputs!$A$46:$A$85=1)*(Inputs!$D$46:$D$85="boom_local")*(Inputs!$C$46:$C$85&lt;&gt;"boom"))+SUMPRODUCT((Inputs!$A$92:$A$131=1)*(Inputs!$D$92:$D$131="boom_local")*(Inputs!$C$92:$C$131&lt;&gt;"boom"))+SUMPRODUCT((Inputs!$A$138:$A$217=1)*(Inputs!$D$138:$D$217="boom_local")*(Inputs!$C$138:$C$217&lt;&gt;"boom"))</f>
         <v/>
       </c>
       <c r="D11" s="3">
@@ -45548,16 +45551,16 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>rope_references</t>
+          <t>node_references</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Segments or hoists referencing a missing or inactive rope</t>
+          <t>References to a missing or inactive node (segment ends, hoist hook/support nodes, hanging nodes' parent)</t>
         </is>
       </c>
       <c r="C12" s="3">
-        <f>SUMPRODUCT((Inputs!$A$224:$A$283=1)*(COUNTIFS(Inputs!$B$290:$B$297,Inputs!$B$224:$B$283,Inputs!$A$290:$A$297,1)=0))+SUMPRODUCT((Inputs!$A$304:$A$311=1)*(COUNTIFS(Inputs!$B$290:$B$297,Inputs!$C$304:$C$311,Inputs!$A$290:$A$297,1)=0))</f>
+        <f>SUMPRODUCT((Inputs!$A$224:$A$283=1)*(COUNTIFS(Inputs!$B$138:$B$217,Inputs!$C$224:$C$283,Inputs!$A$138:$A$217,1)=0))+SUMPRODUCT((Inputs!$A$224:$A$283=1)*(COUNTIFS(Inputs!$B$138:$B$217,Inputs!$D$224:$D$283,Inputs!$A$138:$A$217,1)=0))+SUMPRODUCT((Inputs!$A$304:$A$311=1)*(COUNTIFS(Inputs!$B$138:$B$217,Inputs!$D$304:$D$311,Inputs!$A$138:$A$217,1)=0))+SUMPRODUCT((Inputs!$A$304:$A$311=1)*(Inputs!$E$304:$E$311&lt;&gt;"")*(COUNTIFS(Inputs!$B$138:$B$217,Inputs!$E$304:$E$311,Inputs!$A$138:$A$217,1)=0))+SUMPRODUCT((Inputs!$A$138:$A$217=1)*(Inputs!$D$138:$D$217="hanging")*(COUNTIFS(Inputs!$B$138:$B$217,Inputs!$I$138:$I$217,Inputs!$A$138:$A$217,1)=0))</f>
         <v/>
       </c>
       <c r="D12" s="3">
@@ -45568,16 +45571,16 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>hoist_without_segments</t>
+          <t>rope_references</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Active hoists whose rope has no active segment</t>
+          <t>Segments or hoists referencing a missing or inactive rope</t>
         </is>
       </c>
       <c r="C13" s="3">
-        <f>SUMPRODUCT((Inputs!$A$304:$A$311=1)*(COUNTIFS(Inputs!$B$224:$B$283,Inputs!$C$304:$C$311,Inputs!$A$224:$A$283,1)=0))</f>
+        <f>SUMPRODUCT((Inputs!$A$224:$A$283=1)*(COUNTIFS(Inputs!$B$290:$B$297,Inputs!$B$224:$B$283,Inputs!$A$290:$A$297,1)=0))+SUMPRODUCT((Inputs!$A$304:$A$311=1)*(COUNTIFS(Inputs!$B$290:$B$297,Inputs!$C$304:$C$311,Inputs!$A$290:$A$297,1)=0))</f>
         <v/>
       </c>
       <c r="D13" s="3">
@@ -45588,16 +45591,16 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>multiple_solve_ropes</t>
+          <t>hoist_without_segments</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Active solve ropes beyond the first (exactly one is allowed)</t>
+          <t>Active hoists whose rope has no active segment</t>
         </is>
       </c>
       <c r="C14" s="3">
-        <f>MAX(0,COUNTIFS(Inputs!$A$290:$A$297,1,Inputs!$C$290:$C$297,"solve")-1)</f>
+        <f>SUMPRODUCT((Inputs!$A$304:$A$311=1)*(COUNTIFS(Inputs!$B$224:$B$283,Inputs!$C$304:$C$311,Inputs!$A$224:$A$283,1)=0))</f>
         <v/>
       </c>
       <c r="D14" s="3">
@@ -45608,16 +45611,16 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>no_solve_rope</t>
+          <t>multiple_solve_ropes</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1 if no active rope has role solve (the app shows no results then)</t>
+          <t>Active solve ropes beyond the first (exactly one is allowed)</t>
         </is>
       </c>
       <c r="C15" s="3">
-        <f>IF(COUNTIFS(Inputs!$A$290:$A$297,1,Inputs!$C$290:$C$297,"solve")=0,1,0)</f>
+        <f>MAX(0,COUNTIFS(Inputs!$A$290:$A$297,1,Inputs!$C$290:$C$297,"solve")-1)</f>
         <v/>
       </c>
       <c r="D15" s="3">
@@ -45628,16 +45631,16 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>scene_hoist</t>
+          <t>no_solve_rope</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1 if the scene hoist is not an active hoist with a fixed rope</t>
+          <t>1 if no active rope has role solve (the app shows no results then)</t>
         </is>
       </c>
       <c r="C16" s="3">
-        <f>IF(COUNTIFS(Inputs!$B$304:$B$311,Inputs!$B$26,Inputs!$A$304:$A$311,1)=0,1,IF(COUNTIFS(Inputs!$B$290:$B$297,IFERROR(INDEX(Inputs!$C$304:$C$311,MATCH(Inputs!$B$26&amp;"",Loads!$B$139:$B$146,0)),""),Inputs!$A$290:$A$297,1,Inputs!$C$290:$C$297,"fixed")=0,1,0))</f>
+        <f>IF(COUNTIFS(Inputs!$A$290:$A$297,1,Inputs!$C$290:$C$297,"solve")=0,1,0)</f>
         <v/>
       </c>
       <c r="D16" s="3">
@@ -45648,16 +45651,16 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>wind_direction</t>
+          <t>scene_hoist</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1 if the scene wind direction is not +X, -X, +Y or -Y</t>
+          <t>1 if the scene hoist is not an active hoist with a fixed rope</t>
         </is>
       </c>
       <c r="C17" s="3">
-        <f>IF(OR(Inputs!$B$33="+X",Inputs!$B$33="-X",Inputs!$B$33="+Y",Inputs!$B$33="-Y"),0,1)</f>
+        <f>IF(COUNTIFS(Inputs!$B$304:$B$311,Inputs!$B$26,Inputs!$A$304:$A$311,1)=0,1,IF(COUNTIFS(Inputs!$B$290:$B$297,IFERROR(INDEX(Inputs!$C$304:$C$311,MATCH(Inputs!$B$26&amp;"",Loads!$B$139:$B$146,0)),""),Inputs!$A$290:$A$297,1,Inputs!$C$290:$C$297,"fixed")=0,1,0))</f>
         <v/>
       </c>
       <c r="D17" s="3">
@@ -45668,16 +45671,16 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>fixed_nodes_missing</t>
+          <t>wind_direction</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fixed structure node ids with no active node row</t>
+          <t>1 if the scene wind direction is not +X, -X, +Y or -Y</t>
         </is>
       </c>
       <c r="C18" s="3">
-        <f>COUNTIF($B$36:$B$44,0)</f>
+        <f>IF(OR(Inputs!$B$33="+X",Inputs!$B$33="-X",Inputs!$B$33="+Y",Inputs!$B$33="-Y"),0,1)</f>
         <v/>
       </c>
       <c r="D18" s="3">
@@ -45688,16 +45691,16 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>hanging_chain</t>
+          <t>fixed_nodes_missing</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hanging nodes whose parent is itself hanging (only one level is resolved)</t>
+          <t>Fixed structure node ids with no active node row</t>
         </is>
       </c>
       <c r="C19" s="3">
-        <f>SUMPRODUCT((Inputs!$A$138:$A$217=1)*(Inputs!$D$138:$D$217="hanging")*(COUNTIFS(Inputs!$B$138:$B$217,Inputs!$I$138:$I$217,Inputs!$D$138:$D$217,"hanging",Inputs!$A$138:$A$217,1)&gt;0))</f>
+        <f>COUNTIF($B$37:$B$45,0)</f>
         <v/>
       </c>
       <c r="D19" s="3">
@@ -45708,16 +45711,16 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>singular_matrix</t>
+          <t>hanging_chain</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Singular Statics systems (boom 3x3, leg frame 6x6); the boom one is singular without a solve rope</t>
+          <t>Hanging nodes whose parent is itself hanging (only one level is resolved)</t>
         </is>
       </c>
       <c r="C20" s="3">
-        <f>Statics!$B$41+Statics!$B$62</f>
+        <f>SUMPRODUCT((Inputs!$A$138:$A$217=1)*(Inputs!$D$138:$D$217="hanging")*(COUNTIFS(Inputs!$B$138:$B$217,Inputs!$I$138:$I$217,Inputs!$D$138:$D$217,"hanging",Inputs!$A$138:$A$217,1)&gt;0))</f>
         <v/>
       </c>
       <c r="D20" s="3">
@@ -45728,16 +45731,16 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>zero_boom_width</t>
+          <t>singular_matrix</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1 if the boom width is not &gt; 0 (the app rejects it; the out-of-plane split divides by it, so Results shows a message)</t>
+          <t>Singular Statics systems (boom 3x3, leg frame 6x6); the boom one is singular without a solve rope</t>
         </is>
       </c>
       <c r="C21" s="3">
-        <f>IF(OutOfPlane!$B$20=1,0,1)</f>
+        <f>Statics!$B$41+Statics!$B$62</f>
         <v/>
       </c>
       <c r="D21" s="3">
@@ -45748,16 +45751,16 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>invalid_bearing_diameter</t>
+          <t>zero_boom_width</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1 if the slewing bearing diameter is typed but not a number &gt; 0 (blank is allowed and hides the bearing line-load rows)</t>
+          <t>1 if the boom width is not &gt; 0 (the app rejects it; the out-of-plane split divides by it, so Results shows a message)</t>
         </is>
       </c>
       <c r="C22" s="3">
-        <f>IF(Inputs!$B$13="",0,IF(ISNUMBER(Inputs!$B$13),IF(Inputs!$B$13&gt;0,0,1),1))</f>
+        <f>IF(OutOfPlane!$B$20=1,0,1)</f>
         <v/>
       </c>
       <c r="D22" s="3">
@@ -45765,66 +45768,67 @@
         <v/>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>invalid_bearing_diameter</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1 if the slewing bearing diameter is typed but not a number &gt; 0 (blank is allowed and hides the bearing line-load rows)</t>
+        </is>
+      </c>
+      <c r="C23" s="3">
+        <f>IF(Inputs!$B$13="",0,IF(ISNUMBER(Inputs!$B$13),IF(Inputs!$B$13&gt;0,0,1),1))</f>
+        <v/>
+      </c>
+      <c r="D23" s="3">
+        <f>IF(C23=0,"OK","CHECK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>Overflow per table</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>Table</t>
         </is>
       </c>
-      <c r="B26" s="10" t="inlineStr">
+      <c r="B27" s="10" t="inlineStr">
         <is>
           <t>Not written</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C27" s="10" t="inlineStr">
         <is>
           <t>Typed in guard row</t>
         </is>
       </c>
-      <c r="D26" s="10" t="inlineStr">
+      <c r="D27" s="10" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>mass_points</t>
-        </is>
-      </c>
-      <c r="B27" s="3">
-        <f>Inputs!$G$43</f>
-        <v/>
-      </c>
-      <c r="C27" s="3">
-        <f>COUNTA(Inputs!$A$86:$K$86)</f>
-        <v/>
-      </c>
-      <c r="D27" s="3">
-        <f>B27+C27</f>
-        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>wind_areas</t>
+          <t>mass_points</t>
         </is>
       </c>
       <c r="B28" s="3">
-        <f>Inputs!$G$89</f>
+        <f>Inputs!$G$43</f>
         <v/>
       </c>
       <c r="C28" s="3">
-        <f>COUNTA(Inputs!$A$132:$K$132)</f>
+        <f>COUNTA(Inputs!$A$86:$K$86)</f>
         <v/>
       </c>
       <c r="D28" s="3">
@@ -45835,15 +45839,15 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>nodes</t>
+          <t>wind_areas</t>
         </is>
       </c>
       <c r="B29" s="3">
-        <f>Inputs!$G$135</f>
+        <f>Inputs!$G$89</f>
         <v/>
       </c>
       <c r="C29" s="3">
-        <f>COUNTA(Inputs!$A$218:$K$218)</f>
+        <f>COUNTA(Inputs!$A$132:$K$132)</f>
         <v/>
       </c>
       <c r="D29" s="3">
@@ -45854,15 +45858,15 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>segments</t>
+          <t>nodes</t>
         </is>
       </c>
       <c r="B30" s="3">
-        <f>Inputs!$G$221</f>
+        <f>Inputs!$G$135</f>
         <v/>
       </c>
       <c r="C30" s="3">
-        <f>COUNTA(Inputs!$A$284:$E$284)</f>
+        <f>COUNTA(Inputs!$A$218:$K$218)</f>
         <v/>
       </c>
       <c r="D30" s="3">
@@ -45873,15 +45877,15 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ropes</t>
+          <t>segments</t>
         </is>
       </c>
       <c r="B31" s="3">
-        <f>Inputs!$G$287</f>
+        <f>Inputs!$G$221</f>
         <v/>
       </c>
       <c r="C31" s="3">
-        <f>COUNTA(Inputs!$A$298:$C$298)</f>
+        <f>COUNTA(Inputs!$A$284:$E$284)</f>
         <v/>
       </c>
       <c r="D31" s="3">
@@ -45892,15 +45896,15 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>hoists</t>
+          <t>ropes</t>
         </is>
       </c>
       <c r="B32" s="3">
-        <f>Inputs!$G$301</f>
+        <f>Inputs!$G$287</f>
         <v/>
       </c>
       <c r="C32" s="3">
-        <f>COUNTA(Inputs!$A$312:$Q$312)</f>
+        <f>COUNTA(Inputs!$A$298:$C$298)</f>
         <v/>
       </c>
       <c r="D32" s="3">
@@ -45908,28 +45912,36 @@
         <v/>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>hoists</t>
+        </is>
+      </c>
+      <c r="B33" s="3">
+        <f>Inputs!$G$301</f>
+        <v/>
+      </c>
+      <c r="C33" s="3">
+        <f>COUNTA(Inputs!$A$312:$Q$312)</f>
+        <v/>
+      </c>
+      <c r="D33" s="3">
+        <f>B33+C33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>Fixed structure nodes (active rows with this id)</t>
         </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>boom_heel</t>
-        </is>
-      </c>
-      <c r="B36" s="3">
-        <f>COUNTIFS(Inputs!$B$138:$B$217,A36,Inputs!$A$138:$A$217,1)</f>
-        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>platform_heel</t>
+          <t>boom_heel</t>
         </is>
       </c>
       <c r="B37" s="3">
@@ -45940,7 +45952,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>rear_top</t>
+          <t>platform_heel</t>
         </is>
       </c>
       <c r="B38" s="3">
@@ -45951,7 +45963,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>front_top</t>
+          <t>rear_top</t>
         </is>
       </c>
       <c r="B39" s="3">
@@ -45962,7 +45974,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>rear_base</t>
+          <t>front_top</t>
         </is>
       </c>
       <c r="B40" s="3">
@@ -45973,7 +45985,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>platform_rear</t>
+          <t>rear_base</t>
         </is>
       </c>
       <c r="B41" s="3">
@@ -45984,7 +45996,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>front_base</t>
+          <t>platform_rear</t>
         </is>
       </c>
       <c r="B42" s="3">
@@ -45995,7 +46007,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>platform_front</t>
+          <t>front_base</t>
         </is>
       </c>
       <c r="B43" s="3">
@@ -46006,7 +46018,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>platform_base</t>
+          <t>platform_front</t>
         </is>
       </c>
       <c r="B44" s="3">
@@ -46014,8 +46026,19 @@
         <v/>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>platform_base</t>
+        </is>
+      </c>
+      <c r="B45" s="3">
+        <f>COUNTIFS(Inputs!$B$138:$B$217,A45,Inputs!$A$138:$A$217,1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="C6:C22">
+  <conditionalFormatting sqref="C6:C23">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
